--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JMO/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fe3a1c706bd23a2/Documents/GMU/PHD GMU/RRCHNM/Pepys Network/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6BCC07-490A-644F-8F9F-AA21E9C98385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1235" documentId="8_{4B430F15-E1CA-4049-9D9B-CA6F2179900D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31485B27-EBDB-4835-872C-990BC9193F98}"/>
   <bookViews>
-    <workbookView xWindow="3320" yWindow="7220" windowWidth="27640" windowHeight="16940" xr2:uid="{0359A14D-4663-C54E-9F35-189F654C99ED}"/>
+    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{0359A14D-4663-C54E-9F35-189F654C99ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -62,13 +62,412 @@
   </si>
   <si>
     <t>day</t>
+  </si>
+  <si>
+    <t>1659/60</t>
+  </si>
+  <si>
+    <t>home_axe_yard</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>exeter_house_chapel</t>
+  </si>
+  <si>
+    <t>Elizabeth Pepys</t>
+  </si>
+  <si>
+    <t>office_exchequer</t>
+  </si>
+  <si>
+    <t>westminster_hall</t>
+  </si>
+  <si>
+    <t>Mr Moore; unknown man</t>
+  </si>
+  <si>
+    <t>the_new_market</t>
+  </si>
+  <si>
+    <t>fleet_street</t>
+  </si>
+  <si>
+    <t>wills_ale_house</t>
+  </si>
+  <si>
+    <t>Mr Moore</t>
+  </si>
+  <si>
+    <t>turner_house</t>
+  </si>
+  <si>
+    <t>Elizabeth Pepys; Theophila Turner; Madam Morrice</t>
+  </si>
+  <si>
+    <t>sandwich_lodgings</t>
+  </si>
+  <si>
+    <t>Mr Hawly</t>
+  </si>
+  <si>
+    <t>Jemimah Montagu</t>
+  </si>
+  <si>
+    <t>whitehall_palace</t>
+  </si>
+  <si>
+    <t>Mr Vanley's man</t>
+  </si>
+  <si>
+    <t>swan_inn</t>
+  </si>
+  <si>
+    <t>Clerk of Sandwich Troop; Quartermaster of Sandwich Troop</t>
+  </si>
+  <si>
+    <t>Elizabeth Pepys; Mrs Sheply</t>
+  </si>
+  <si>
+    <t>harpers_tavern</t>
+  </si>
+  <si>
+    <t>John Pepys</t>
+  </si>
+  <si>
+    <t>thomas_pepys_house</t>
+  </si>
+  <si>
+    <t>stradwick_house</t>
+  </si>
+  <si>
+    <t>Elizabeth Pepys; Jane Birch</t>
+  </si>
+  <si>
+    <t>Jane Birch</t>
+  </si>
+  <si>
+    <t>Jane Turner; Theophila Turner; Madame Morris; Joyce Norton</t>
+  </si>
+  <si>
+    <t>Mr Hawley; Jane Turner; Theophila Turner; Madame Morris; Joyce Norton</t>
+  </si>
+  <si>
+    <t>dr_hoares_house</t>
+  </si>
+  <si>
+    <t>mr_mossum_church</t>
+  </si>
+  <si>
+    <t>Elizabeth Pepys; Mr Shepley</t>
+  </si>
+  <si>
+    <t>William Symons; Henry Muddiman; Jack Price</t>
+  </si>
+  <si>
+    <t>turks_head_coffee_house</t>
+  </si>
+  <si>
+    <t>Henry Muddiman</t>
+  </si>
+  <si>
+    <t>Clerk of Sandwich troop; Quartermaster of Sandwich Troop</t>
+  </si>
+  <si>
+    <t>Ralph Greatorex</t>
+  </si>
+  <si>
+    <t>Quartermaster of Sandwich Troop; Mr Jennings; Captain William Rider</t>
+  </si>
+  <si>
+    <t>Mr Jennings</t>
+  </si>
+  <si>
+    <t>city_of_london</t>
+  </si>
+  <si>
+    <t>star_tavern</t>
+  </si>
+  <si>
+    <t>Thomas Doling</t>
+  </si>
+  <si>
+    <t>mother_lams</t>
+  </si>
+  <si>
+    <t>the_half_moon</t>
+  </si>
+  <si>
+    <t>Mr Fage</t>
+  </si>
+  <si>
+    <t>Mr Pinkney</t>
+  </si>
+  <si>
+    <t>kate_petit_house</t>
+  </si>
+  <si>
+    <t>cookshop_unknown_1</t>
+  </si>
+  <si>
+    <t>Captain Richard Barker</t>
+  </si>
+  <si>
+    <t>william_joyce_house</t>
+  </si>
+  <si>
+    <t>tower_menagerie</t>
+  </si>
+  <si>
+    <t>tower_of_menagerie</t>
+  </si>
+  <si>
+    <t>mr_stevens_house</t>
+  </si>
+  <si>
+    <t>coffee_house_unknown_1</t>
+  </si>
+  <si>
+    <t>john_pepys_house</t>
+  </si>
+  <si>
+    <t>john_crews_house</t>
+  </si>
+  <si>
+    <t>lestrange_calthorpe_chamber</t>
+  </si>
+  <si>
+    <t>george_vines_house</t>
+  </si>
+  <si>
+    <t>john_hunt_house</t>
+  </si>
+  <si>
+    <t>valentine_fage_house</t>
+  </si>
+  <si>
+    <t>thomas_wade_house</t>
+  </si>
+  <si>
+    <t>market_unknown_1</t>
+  </si>
+  <si>
+    <t>alehouse_unknown_3</t>
+  </si>
+  <si>
+    <t>alehouse_unknown_2</t>
+  </si>
+  <si>
+    <t>alehouse_unknown_1</t>
+  </si>
+  <si>
+    <t>salisbury_court</t>
+  </si>
+  <si>
+    <t>coach</t>
+  </si>
+  <si>
+    <t>Harry Ethall; Thomas Mallard</t>
+  </si>
+  <si>
+    <t>parish_clerks_hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Ethall </t>
+  </si>
+  <si>
+    <t>green_dragon_pub</t>
+  </si>
+  <si>
+    <t>golden_lion_pub</t>
+  </si>
+  <si>
+    <t>Mr Sheply; Mr Harrison</t>
+  </si>
+  <si>
+    <t>Edward Montagu</t>
+  </si>
+  <si>
+    <t>Edward Montagu; John Crew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Montagu </t>
+  </si>
+  <si>
+    <t>Mr Woodfine</t>
+  </si>
+  <si>
+    <t>twickenham</t>
+  </si>
+  <si>
+    <t>Edward Montagu; Elizabeth Pepys</t>
+  </si>
+  <si>
+    <t>william_fuller_lodgings</t>
+  </si>
+  <si>
+    <t>william_fuller_lodging</t>
+  </si>
+  <si>
+    <t>brentford</t>
+  </si>
+  <si>
+    <t>wilkinsons_cookshop</t>
+  </si>
+  <si>
+    <t>Mr Talbot; Henry Adams; George Pinkney; William Fuller</t>
+  </si>
+  <si>
+    <t>george_downings_lodging</t>
+  </si>
+  <si>
+    <t>george_downings_lodgings</t>
+  </si>
+  <si>
+    <t>Mr Sheply</t>
+  </si>
+  <si>
+    <t>harp_and_ball_tavern</t>
+  </si>
+  <si>
+    <t>Mr Sheply; James Pearse</t>
+  </si>
+  <si>
+    <t>Mr Sheply; Henry Moore</t>
+  </si>
+  <si>
+    <t>french_ordinary</t>
+  </si>
+  <si>
+    <t>Henry Moore</t>
+  </si>
+  <si>
+    <t>james_marsh_lodgings</t>
+  </si>
+  <si>
+    <t>the_sun_pub</t>
+  </si>
+  <si>
+    <t>Thomas Mallard; Thomas Hailes</t>
+  </si>
+  <si>
+    <t>the_swan_pub</t>
+  </si>
+  <si>
+    <t>coffee_house_unknown_2</t>
+  </si>
+  <si>
+    <t>mr_sheply_lodgings</t>
+  </si>
+  <si>
+    <t>John Hawley</t>
+  </si>
+  <si>
+    <t>mr_vernon_lodging</t>
+  </si>
+  <si>
+    <t>mitre_tavern</t>
+  </si>
+  <si>
+    <t>clerks_room_whitehall</t>
+  </si>
+  <si>
+    <t>st_brides_church</t>
+  </si>
+  <si>
+    <t>Jane Turner</t>
+  </si>
+  <si>
+    <t>axe_brewhouse</t>
+  </si>
+  <si>
+    <t>James Pearse</t>
+  </si>
+  <si>
+    <t>stone_gallery_whitehall</t>
+  </si>
+  <si>
+    <t>cockpit_whitehall</t>
+  </si>
+  <si>
+    <t>William Symons; Peter Llewellyn</t>
+  </si>
+  <si>
+    <t>james_pearse_house</t>
+  </si>
+  <si>
+    <t>thomas_pepys_shop</t>
+  </si>
+  <si>
+    <t>william_wight_house</t>
+  </si>
+  <si>
+    <t>st_pauls_churchyard</t>
+  </si>
+  <si>
+    <t>william_jessop_lodging</t>
+  </si>
+  <si>
+    <t>Tom Newton</t>
+  </si>
+  <si>
+    <t>crown_pub</t>
+  </si>
+  <si>
+    <t>george_montagu_house</t>
+  </si>
+  <si>
+    <t>John Hawley; Arthur Squibb</t>
+  </si>
+  <si>
+    <t>royal_exchange</t>
+  </si>
+  <si>
+    <t>heaven_alehouse</t>
+  </si>
+  <si>
+    <t>st_clements_church</t>
+  </si>
+  <si>
+    <t>Mr Walton</t>
+  </si>
+  <si>
+    <t>anne_wright_house</t>
+  </si>
+  <si>
+    <t>peter_gunning_church</t>
+  </si>
+  <si>
+    <t>Thomas Ruddiard</t>
+  </si>
+  <si>
+    <t>mr_torriano_house</t>
+  </si>
+  <si>
+    <t>richard_matthews_house</t>
+  </si>
+  <si>
+    <t>Nick Bartlet</t>
+  </si>
+  <si>
+    <t>star_chamber_westminster</t>
+  </si>
+  <si>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>richard_sherwin_office</t>
+  </si>
+  <si>
+    <t>Unclear if Downing is at office or lodging</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -76,13 +475,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -97,8 +508,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -116,10 +528,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +573,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -263,7 +679,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -405,7 +821,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -413,13 +829,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AACE75DE-CC34-C24E-A1EF-A8AC857886EC}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I294"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <cols>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,7 +866,6984 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A2">
+        <v>100001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A3">
+        <v>100002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A4">
+        <v>100003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A5">
+        <v>100004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A6">
+        <v>100005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A7">
+        <v>100006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A8">
+        <v>100007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A9">
+        <v>100008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A10">
+        <v>100009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A11">
+        <v>100010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A12">
+        <v>100011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A13">
+        <v>100012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A14">
+        <v>100013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A15">
+        <v>100014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A16">
+        <v>100015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A17">
+        <v>100016</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A18">
+        <v>100017</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A19">
+        <v>100018</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A20">
+        <v>100019</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A21">
+        <v>100020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A22">
+        <v>100021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A23">
+        <v>100022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A24">
+        <v>100023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A25">
+        <v>100024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A26">
+        <v>100025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A27">
+        <v>100026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A28">
+        <v>100027</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A29">
+        <v>100028</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A30">
+        <v>100029</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A31">
+        <v>100030</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A32">
+        <v>100031</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A33">
+        <v>100032</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A34">
+        <v>100033</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A35">
+        <v>100034</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A36">
+        <v>100035</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A37">
+        <v>100036</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A38">
+        <v>100037</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A39">
+        <v>100038</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A40">
+        <v>100039</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A41">
+        <v>100040</v>
+      </c>
+      <c r="B41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A42">
+        <v>100041</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A43">
+        <v>100042</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A44">
+        <v>100043</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A45">
+        <v>100044</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A46">
+        <v>100045</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A47">
+        <v>100046</v>
+      </c>
+      <c r="B47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A48">
+        <v>100047</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A49">
+        <v>100048</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A50">
+        <v>100049</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A51">
+        <v>100050</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>6</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A52">
+        <v>100051</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A53">
+        <v>100052</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>6</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A54">
+        <v>100053</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A55">
+        <v>100054</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A56">
+        <v>100055</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>6</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A57">
+        <v>100056</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A58">
+        <v>100057</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>6</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A59">
+        <v>100058</v>
+      </c>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A60">
+        <v>100059</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>7</v>
+      </c>
+      <c r="G60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A61">
+        <v>100060</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>7</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A62">
+        <v>100061</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>7</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A63">
+        <v>100062</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A64">
+        <v>100063</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A65">
+        <v>100064</v>
+      </c>
+      <c r="B65" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A66">
+        <v>100065</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>7</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A67">
+        <v>100066</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>8</v>
+      </c>
+      <c r="G67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A68">
+        <v>100067</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A69">
+        <v>100068</v>
+      </c>
+      <c r="B69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A70">
+        <v>100069</v>
+      </c>
+      <c r="B70" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>8</v>
+      </c>
+      <c r="G70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A71">
+        <v>100070</v>
+      </c>
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s">
+        <v>64</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
+      </c>
+      <c r="G71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A72">
+        <v>100071</v>
+      </c>
+      <c r="B72" t="s">
+        <v>64</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>8</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A73">
+        <v>100072</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>9</v>
+      </c>
+      <c r="G73" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A74">
+        <v>100073</v>
+      </c>
+      <c r="B74" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" t="s">
+        <v>43</v>
+      </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>9</v>
+      </c>
+      <c r="G74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A75">
+        <v>100074</v>
+      </c>
+      <c r="B75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>9</v>
+      </c>
+      <c r="G75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A76">
+        <v>100075</v>
+      </c>
+      <c r="B76" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>9</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A77">
+        <v>100076</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A78">
+        <v>100077</v>
+      </c>
+      <c r="B78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" t="s">
+        <v>65</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78">
+        <v>10</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A79">
+        <v>100078</v>
+      </c>
+      <c r="B79" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A80">
+        <v>100079</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A81">
+        <v>100080</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A82">
+        <v>100081</v>
+      </c>
+      <c r="B82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A83">
+        <v>100082</v>
+      </c>
+      <c r="B83" t="s">
+        <v>49</v>
+      </c>
+      <c r="C83" t="s">
+        <v>50</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A84">
+        <v>100083</v>
+      </c>
+      <c r="B84" t="s">
+        <v>50</v>
+      </c>
+      <c r="C84" t="s">
+        <v>43</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A85">
+        <v>100084</v>
+      </c>
+      <c r="B85" t="s">
+        <v>43</v>
+      </c>
+      <c r="C85" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A86">
+        <v>100085</v>
+      </c>
+      <c r="B86" t="s">
+        <v>52</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A87">
+        <v>100086</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A88">
+        <v>100087</v>
+      </c>
+      <c r="B88" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>10</v>
+      </c>
+      <c r="G88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A89">
+        <v>100088</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>11</v>
+      </c>
+      <c r="G89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A90">
+        <v>100089</v>
+      </c>
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>11</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A91">
+        <v>100090</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" t="s">
+        <v>59</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <v>11</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A92">
+        <v>100091</v>
+      </c>
+      <c r="B92" t="s">
+        <v>59</v>
+      </c>
+      <c r="C92" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>11</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A93">
+        <v>100092</v>
+      </c>
+      <c r="B93" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>11</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A94">
+        <v>100093</v>
+      </c>
+      <c r="B94" t="s">
+        <v>59</v>
+      </c>
+      <c r="C94" t="s">
+        <v>73</v>
+      </c>
+      <c r="D94" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>11</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A95">
+        <v>100094</v>
+      </c>
+      <c r="B95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A96">
+        <v>100095</v>
+      </c>
+      <c r="B96" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96" t="s">
+        <v>62</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>11</v>
+      </c>
+      <c r="G96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A97">
+        <v>100096</v>
+      </c>
+      <c r="B97" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <v>11</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A98">
+        <v>100097</v>
+      </c>
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>11</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A99">
+        <v>100098</v>
+      </c>
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>11</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A100">
+        <v>100099</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" t="s">
+        <v>63</v>
+      </c>
+      <c r="D100" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>11</v>
+      </c>
+      <c r="G100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A101">
+        <v>100100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>63</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>11</v>
+      </c>
+      <c r="G101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A102">
+        <v>100101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" t="s">
+        <v>31</v>
+      </c>
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>12</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A103">
+        <v>100102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A104">
+        <v>100103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104">
+        <v>12</v>
+      </c>
+      <c r="G104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A105">
+        <v>100104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105">
+        <v>12</v>
+      </c>
+      <c r="G105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A106">
+        <v>100105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" t="s">
+        <v>53</v>
+      </c>
+      <c r="D106" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <v>12</v>
+      </c>
+      <c r="G106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A107">
+        <v>100106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>53</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107">
+        <v>12</v>
+      </c>
+      <c r="G107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A108">
+        <v>100107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A109">
+        <v>100108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" t="s">
+        <v>28</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+      <c r="F109">
+        <v>13</v>
+      </c>
+      <c r="G109" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A110">
+        <v>100109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="F110">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A111">
+        <v>100110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111">
+        <v>13</v>
+      </c>
+      <c r="G111" t="s">
+        <v>11</v>
+      </c>
+      <c r="H111" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A112">
+        <v>100111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+      <c r="F112">
+        <v>13</v>
+      </c>
+      <c r="G112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A113">
+        <v>100112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" t="s">
+        <v>70</v>
+      </c>
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>11</v>
+      </c>
+      <c r="H113" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A114">
+        <v>100113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>70</v>
+      </c>
+      <c r="C114" t="s">
+        <v>56</v>
+      </c>
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>11</v>
+      </c>
+      <c r="H114" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A115">
+        <v>100114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115">
+        <v>13</v>
+      </c>
+      <c r="G115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A116">
+        <v>100115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>10</v>
+      </c>
+      <c r="C116" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>11</v>
+      </c>
+      <c r="H116" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A117">
+        <v>100116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117">
+        <v>13</v>
+      </c>
+      <c r="G117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A118">
+        <v>100117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" t="s">
+        <v>67</v>
+      </c>
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A119">
+        <v>100118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>67</v>
+      </c>
+      <c r="C119" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119">
+        <v>13</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A120">
+        <v>100119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A121">
+        <v>100120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121">
+        <v>14</v>
+      </c>
+      <c r="G121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A122">
+        <v>100121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122">
+        <v>14</v>
+      </c>
+      <c r="G122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A123">
+        <v>100122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" t="s">
+        <v>71</v>
+      </c>
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123">
+        <v>14</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
+      </c>
+      <c r="H123" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A124">
+        <v>100123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>71</v>
+      </c>
+      <c r="C124" t="s">
+        <v>43</v>
+      </c>
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124">
+        <v>14</v>
+      </c>
+      <c r="G124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A125">
+        <v>100124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>43</v>
+      </c>
+      <c r="C125" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125">
+        <v>14</v>
+      </c>
+      <c r="G125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A126">
+        <v>100125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" t="s">
+        <v>65</v>
+      </c>
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A127">
+        <v>100126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>65</v>
+      </c>
+      <c r="C127" t="s">
+        <v>72</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127">
+        <v>16</v>
+      </c>
+      <c r="G127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A128">
+        <v>100127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>72</v>
+      </c>
+      <c r="C128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A129">
+        <v>100128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129" t="s">
+        <v>75</v>
+      </c>
+      <c r="D129" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
+        <v>76</v>
+      </c>
+      <c r="H129" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A130">
+        <v>100129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>75</v>
+      </c>
+      <c r="C130" t="s">
+        <v>78</v>
+      </c>
+      <c r="D130" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>16</v>
+      </c>
+      <c r="G130" t="s">
+        <v>11</v>
+      </c>
+      <c r="H130" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A131">
+        <v>100130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>78</v>
+      </c>
+      <c r="C131" t="s">
+        <v>80</v>
+      </c>
+      <c r="D131" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131">
+        <v>16</v>
+      </c>
+      <c r="G131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A132">
+        <v>100131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>80</v>
+      </c>
+      <c r="C132" t="s">
+        <v>81</v>
+      </c>
+      <c r="D132" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132">
+        <v>16</v>
+      </c>
+      <c r="G132" t="s">
+        <v>11</v>
+      </c>
+      <c r="H132" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A133">
+        <v>100132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>81</v>
+      </c>
+      <c r="C133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133">
+        <v>16</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A134">
+        <v>100133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="s">
+        <v>65</v>
+      </c>
+      <c r="D134" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A135">
+        <v>100134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>65</v>
+      </c>
+      <c r="C135" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135">
+        <v>17</v>
+      </c>
+      <c r="G135" t="s">
+        <v>76</v>
+      </c>
+      <c r="H135" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A136">
+        <v>100135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s">
+        <v>11</v>
+      </c>
+      <c r="H136" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A137">
+        <v>100136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="F137">
+        <v>17</v>
+      </c>
+      <c r="G137" t="s">
+        <v>11</v>
+      </c>
+      <c r="H137" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A138">
+        <v>100137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>19</v>
+      </c>
+      <c r="C138" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+      <c r="F138">
+        <v>17</v>
+      </c>
+      <c r="G138" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A139">
+        <v>100138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
+        <v>87</v>
+      </c>
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="F139">
+        <v>17</v>
+      </c>
+      <c r="G139" t="s">
+        <v>76</v>
+      </c>
+      <c r="H139" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A140">
+        <v>100139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>87</v>
+      </c>
+      <c r="C140" t="s">
+        <v>89</v>
+      </c>
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+      <c r="F140">
+        <v>17</v>
+      </c>
+      <c r="G140" t="s">
+        <v>76</v>
+      </c>
+      <c r="H140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A141">
+        <v>100140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>90</v>
+      </c>
+      <c r="C141" t="s">
+        <v>91</v>
+      </c>
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <v>17</v>
+      </c>
+      <c r="G141" t="s">
+        <v>76</v>
+      </c>
+      <c r="H141" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A142">
+        <v>100141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>91</v>
+      </c>
+      <c r="C142" t="s">
+        <v>65</v>
+      </c>
+      <c r="D142" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>17</v>
+      </c>
+      <c r="G142" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A143">
+        <v>100142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>65</v>
+      </c>
+      <c r="C143" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143">
+        <v>17</v>
+      </c>
+      <c r="G143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A144">
+        <v>100143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" t="s">
+        <v>43</v>
+      </c>
+      <c r="D144" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144">
+        <v>17</v>
+      </c>
+      <c r="G144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A145">
+        <v>100144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>43</v>
+      </c>
+      <c r="C145" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145">
+        <v>17</v>
+      </c>
+      <c r="G145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A146">
+        <v>100145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="F146">
+        <v>17</v>
+      </c>
+      <c r="G146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A147">
+        <v>100146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" t="s">
+        <v>26</v>
+      </c>
+      <c r="D147" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147">
+        <v>1</v>
+      </c>
+      <c r="F147">
+        <v>17</v>
+      </c>
+      <c r="G147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A148">
+        <v>100147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>31</v>
+      </c>
+      <c r="D148" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148">
+        <v>17</v>
+      </c>
+      <c r="G148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A149">
+        <v>100148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>31</v>
+      </c>
+      <c r="C149" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+      <c r="F149">
+        <v>17</v>
+      </c>
+      <c r="G149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A150">
+        <v>100149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" t="s">
+        <v>14</v>
+      </c>
+      <c r="D150" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+      <c r="F150">
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A151">
+        <v>100150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>14</v>
+      </c>
+      <c r="C151" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151">
+        <v>18</v>
+      </c>
+      <c r="G151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A152">
+        <v>100151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+      <c r="F152">
+        <v>18</v>
+      </c>
+      <c r="G152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A153">
+        <v>100152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" t="s">
+        <v>92</v>
+      </c>
+      <c r="D153" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="F153">
+        <v>18</v>
+      </c>
+      <c r="G153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A154">
+        <v>100153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>92</v>
+      </c>
+      <c r="C154" t="s">
+        <v>23</v>
+      </c>
+      <c r="D154" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+      <c r="F154">
+        <v>18</v>
+      </c>
+      <c r="G154" t="s">
+        <v>11</v>
+      </c>
+      <c r="H154" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A155">
+        <v>100154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>23</v>
+      </c>
+      <c r="C155" t="s">
+        <v>10</v>
+      </c>
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A156">
+        <v>100155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A157">
+        <v>100156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>23</v>
+      </c>
+      <c r="C157" t="s">
+        <v>65</v>
+      </c>
+      <c r="D157" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A158">
+        <v>100157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>65</v>
+      </c>
+      <c r="C158" t="s">
+        <v>10</v>
+      </c>
+      <c r="D158" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A159">
+        <v>100158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" t="s">
+        <v>94</v>
+      </c>
+      <c r="D159" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159">
+        <v>19</v>
+      </c>
+      <c r="G159" t="s">
+        <v>11</v>
+      </c>
+      <c r="H159" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A160">
+        <v>100159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>95</v>
+      </c>
+      <c r="C160" t="s">
+        <v>97</v>
+      </c>
+      <c r="D160" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160">
+        <v>19</v>
+      </c>
+      <c r="G160" t="s">
+        <v>11</v>
+      </c>
+      <c r="H160" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A161">
+        <v>100160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>97</v>
+      </c>
+      <c r="C161" t="s">
+        <v>26</v>
+      </c>
+      <c r="D161" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161">
+        <v>19</v>
+      </c>
+      <c r="G161" t="s">
+        <v>11</v>
+      </c>
+      <c r="H161" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A162">
+        <v>100161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" t="s">
+        <v>94</v>
+      </c>
+      <c r="D162" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="F162">
+        <v>19</v>
+      </c>
+      <c r="G162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A163">
+        <v>100162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>95</v>
+      </c>
+      <c r="C163" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <v>19</v>
+      </c>
+      <c r="G163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A164">
+        <v>100163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>14</v>
+      </c>
+      <c r="C164" t="s">
+        <v>23</v>
+      </c>
+      <c r="D164" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>11</v>
+      </c>
+      <c r="H164" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A165">
+        <v>100164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>23</v>
+      </c>
+      <c r="C165" t="s">
+        <v>100</v>
+      </c>
+      <c r="D165" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+      <c r="F165">
+        <v>19</v>
+      </c>
+      <c r="G165" t="s">
+        <v>11</v>
+      </c>
+      <c r="H165" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A166">
+        <v>100165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>100</v>
+      </c>
+      <c r="C166" t="s">
+        <v>102</v>
+      </c>
+      <c r="D166" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+      <c r="F166">
+        <v>19</v>
+      </c>
+      <c r="G166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A167">
+        <v>100166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>102</v>
+      </c>
+      <c r="C167" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+      <c r="F167">
+        <v>19</v>
+      </c>
+      <c r="G167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A168">
+        <v>100167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" t="s">
+        <v>94</v>
+      </c>
+      <c r="D168" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+      <c r="F168">
+        <v>20</v>
+      </c>
+      <c r="G168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A169">
+        <v>100168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>95</v>
+      </c>
+      <c r="C169" t="s">
+        <v>66</v>
+      </c>
+      <c r="D169" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+      <c r="F169">
+        <v>20</v>
+      </c>
+      <c r="G169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A170">
+        <v>100169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>66</v>
+      </c>
+      <c r="C170" t="s">
+        <v>103</v>
+      </c>
+      <c r="D170" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170">
+        <v>20</v>
+      </c>
+      <c r="G170" t="s">
+        <v>11</v>
+      </c>
+      <c r="H170" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A171">
+        <v>100170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>103</v>
+      </c>
+      <c r="C171" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+      <c r="F171">
+        <v>20</v>
+      </c>
+      <c r="G171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A172">
+        <v>100171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>20</v>
+      </c>
+      <c r="G172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A173">
+        <v>100172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>14</v>
+      </c>
+      <c r="C173" t="s">
+        <v>105</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>11</v>
+      </c>
+      <c r="H173" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A174">
+        <v>100173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>105</v>
+      </c>
+      <c r="C174" t="s">
+        <v>106</v>
+      </c>
+      <c r="D174" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A175">
+        <v>100174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>106</v>
+      </c>
+      <c r="C175" t="s">
+        <v>15</v>
+      </c>
+      <c r="D175" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A176">
+        <v>100175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" t="s">
+        <v>107</v>
+      </c>
+      <c r="D176" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A177">
+        <v>100176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>107</v>
+      </c>
+      <c r="C177" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>11</v>
+      </c>
+      <c r="H177" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A178">
+        <v>100177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>10</v>
+      </c>
+      <c r="C178" t="s">
+        <v>23</v>
+      </c>
+      <c r="D178" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178">
+        <v>21</v>
+      </c>
+      <c r="G178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A179">
+        <v>100178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>23</v>
+      </c>
+      <c r="C179" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179">
+        <v>21</v>
+      </c>
+      <c r="G179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A180">
+        <v>100179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180" t="s">
+        <v>94</v>
+      </c>
+      <c r="D180" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="F180">
+        <v>21</v>
+      </c>
+      <c r="G180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A181">
+        <v>100180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>95</v>
+      </c>
+      <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181">
+        <v>21</v>
+      </c>
+      <c r="G181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A182">
+        <v>100181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" t="s">
+        <v>65</v>
+      </c>
+      <c r="D182" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>11</v>
+      </c>
+      <c r="H182" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A183">
+        <v>100182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>65</v>
+      </c>
+      <c r="C183" t="s">
+        <v>109</v>
+      </c>
+      <c r="D183" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>11</v>
+      </c>
+      <c r="H183" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A184">
+        <v>100183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>109</v>
+      </c>
+      <c r="C184" t="s">
+        <v>69</v>
+      </c>
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>11</v>
+      </c>
+      <c r="H184" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A185">
+        <v>100184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>69</v>
+      </c>
+      <c r="C185" t="s">
+        <v>110</v>
+      </c>
+      <c r="D185" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>11</v>
+      </c>
+      <c r="H185" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A186">
+        <v>100185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>110</v>
+      </c>
+      <c r="C186" t="s">
+        <v>23</v>
+      </c>
+      <c r="D186" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A187">
+        <v>100186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>23</v>
+      </c>
+      <c r="C187" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A188">
+        <v>100187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" t="s">
+        <v>102</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A189">
+        <v>100188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>102</v>
+      </c>
+      <c r="C189" t="s">
+        <v>111</v>
+      </c>
+      <c r="D189" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A190">
+        <v>100189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>111</v>
+      </c>
+      <c r="C190" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A191">
+        <v>100190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>40</v>
+      </c>
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A192">
+        <v>100191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>40</v>
+      </c>
+      <c r="C192" t="s">
+        <v>64</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>11</v>
+      </c>
+      <c r="H192" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A193">
+        <v>100192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>64</v>
+      </c>
+      <c r="C193" t="s">
+        <v>112</v>
+      </c>
+      <c r="D193" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A194">
+        <v>100193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>112</v>
+      </c>
+      <c r="C194" t="s">
+        <v>21</v>
+      </c>
+      <c r="D194" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>11</v>
+      </c>
+      <c r="H194" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A195">
+        <v>100194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>21</v>
+      </c>
+      <c r="C195" t="s">
+        <v>64</v>
+      </c>
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A196">
+        <v>100195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>64</v>
+      </c>
+      <c r="C196" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A197">
+        <v>100196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" t="s">
+        <v>94</v>
+      </c>
+      <c r="D197" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="F197">
+        <v>23</v>
+      </c>
+      <c r="G197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A198">
+        <v>100197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>95</v>
+      </c>
+      <c r="C198" t="s">
+        <v>114</v>
+      </c>
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+      <c r="F198">
+        <v>23</v>
+      </c>
+      <c r="G198" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A199">
+        <v>100198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>114</v>
+      </c>
+      <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+      <c r="F199">
+        <v>23</v>
+      </c>
+      <c r="G199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A200">
+        <v>100199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>14</v>
+      </c>
+      <c r="C200" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A201">
+        <v>100200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201" t="s">
+        <v>92</v>
+      </c>
+      <c r="D201" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A202">
+        <v>100201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>92</v>
+      </c>
+      <c r="C202" t="s">
+        <v>10</v>
+      </c>
+      <c r="D202" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A203">
+        <v>100202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203" t="s">
+        <v>103</v>
+      </c>
+      <c r="D203" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A204">
+        <v>100203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>103</v>
+      </c>
+      <c r="C204" t="s">
+        <v>23</v>
+      </c>
+      <c r="D204" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A205">
+        <v>100204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>23</v>
+      </c>
+      <c r="C205" t="s">
+        <v>15</v>
+      </c>
+      <c r="D205" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A206">
+        <v>100205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" t="s">
+        <v>116</v>
+      </c>
+      <c r="D206" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A207">
+        <v>100206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>116</v>
+      </c>
+      <c r="C207" t="s">
+        <v>111</v>
+      </c>
+      <c r="D207" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A208">
+        <v>100207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>111</v>
+      </c>
+      <c r="C208" t="s">
+        <v>117</v>
+      </c>
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>11</v>
+      </c>
+      <c r="H208" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A209">
+        <v>100208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>117</v>
+      </c>
+      <c r="C209" t="s">
+        <v>10</v>
+      </c>
+      <c r="D209" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+      <c r="F209">
+        <v>23</v>
+      </c>
+      <c r="G209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A210">
+        <v>100209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210" t="s">
+        <v>14</v>
+      </c>
+      <c r="D210" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A211">
+        <v>100210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>14</v>
+      </c>
+      <c r="C211" t="s">
+        <v>19</v>
+      </c>
+      <c r="D211" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A212">
+        <v>100211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>19</v>
+      </c>
+      <c r="C212" t="s">
+        <v>14</v>
+      </c>
+      <c r="D212" t="s">
+        <v>9</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A213">
+        <v>100212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" t="s">
+        <v>10</v>
+      </c>
+      <c r="D213" t="s">
+        <v>9</v>
+      </c>
+      <c r="E213">
+        <v>1</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A214">
+        <v>100213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214" t="s">
+        <v>119</v>
+      </c>
+      <c r="D214" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A215">
+        <v>100214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>119</v>
+      </c>
+      <c r="C215" t="s">
+        <v>64</v>
+      </c>
+      <c r="D215" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>11</v>
+      </c>
+      <c r="H215" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A216">
+        <v>100215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>64</v>
+      </c>
+      <c r="C216" t="s">
+        <v>120</v>
+      </c>
+      <c r="D216" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A217">
+        <v>100216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>120</v>
+      </c>
+      <c r="C217" t="s">
+        <v>64</v>
+      </c>
+      <c r="D217" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217">
+        <v>1</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>11</v>
+      </c>
+      <c r="H217" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A218">
+        <v>100217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>64</v>
+      </c>
+      <c r="C218" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+      <c r="F218">
+        <v>24</v>
+      </c>
+      <c r="G218" t="s">
+        <v>11</v>
+      </c>
+      <c r="H218" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A219">
+        <v>100218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" t="s">
+        <v>102</v>
+      </c>
+      <c r="D219" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219">
+        <v>1</v>
+      </c>
+      <c r="F219">
+        <v>24</v>
+      </c>
+      <c r="G219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A220">
+        <v>100219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>102</v>
+      </c>
+      <c r="C220" t="s">
+        <v>10</v>
+      </c>
+      <c r="D220" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+      <c r="F220">
+        <v>24</v>
+      </c>
+      <c r="G220" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A221">
+        <v>100220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221" t="s">
+        <v>94</v>
+      </c>
+      <c r="D221" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A222">
+        <v>100221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>95</v>
+      </c>
+      <c r="C222" t="s">
+        <v>14</v>
+      </c>
+      <c r="D222" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A223">
+        <v>100222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223" t="s">
+        <v>10</v>
+      </c>
+      <c r="D223" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A224">
+        <v>100223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>10</v>
+      </c>
+      <c r="C224" t="s">
+        <v>121</v>
+      </c>
+      <c r="D224" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224">
+        <v>1</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A225">
+        <v>100224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>121</v>
+      </c>
+      <c r="C225" t="s">
+        <v>10</v>
+      </c>
+      <c r="D225" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225">
+        <v>1</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A226">
+        <v>100225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>10</v>
+      </c>
+      <c r="C226" t="s">
+        <v>122</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A227">
+        <v>100226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>122</v>
+      </c>
+      <c r="C227" t="s">
+        <v>64</v>
+      </c>
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227">
+        <v>1</v>
+      </c>
+      <c r="F227">
+        <v>25</v>
+      </c>
+      <c r="G227" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A228">
+        <v>100227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>64</v>
+      </c>
+      <c r="C228" t="s">
+        <v>65</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228">
+        <v>1</v>
+      </c>
+      <c r="F228">
+        <v>25</v>
+      </c>
+      <c r="G228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A229">
+        <v>100228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>65</v>
+      </c>
+      <c r="C229" t="s">
+        <v>23</v>
+      </c>
+      <c r="D229" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229">
+        <v>1</v>
+      </c>
+      <c r="F229">
+        <v>25</v>
+      </c>
+      <c r="G229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A230">
+        <v>100229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>23</v>
+      </c>
+      <c r="C230" t="s">
+        <v>94</v>
+      </c>
+      <c r="D230" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+      <c r="F230">
+        <v>25</v>
+      </c>
+      <c r="G230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A231">
+        <v>100230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>95</v>
+      </c>
+      <c r="C231" t="s">
+        <v>123</v>
+      </c>
+      <c r="D231" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231">
+        <v>25</v>
+      </c>
+      <c r="G231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A232">
+        <v>100231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>123</v>
+      </c>
+      <c r="C232" t="s">
+        <v>23</v>
+      </c>
+      <c r="D232" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
+      <c r="F232">
+        <v>25</v>
+      </c>
+      <c r="G232" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A233">
+        <v>100232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>23</v>
+      </c>
+      <c r="C233" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
+      <c r="F233">
+        <v>25</v>
+      </c>
+      <c r="G233" t="s">
+        <v>11</v>
+      </c>
+      <c r="H233" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A234">
+        <v>100233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>10</v>
+      </c>
+      <c r="C234" t="s">
+        <v>14</v>
+      </c>
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234">
+        <v>1</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A235">
+        <v>100234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235" t="s">
+        <v>94</v>
+      </c>
+      <c r="D235" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A236">
+        <v>100235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>95</v>
+      </c>
+      <c r="C236" t="s">
+        <v>26</v>
+      </c>
+      <c r="D236" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236">
+        <v>26</v>
+      </c>
+      <c r="G236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A237">
+        <v>100236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>26</v>
+      </c>
+      <c r="C237" t="s">
+        <v>14</v>
+      </c>
+      <c r="D237" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+      <c r="F237">
+        <v>26</v>
+      </c>
+      <c r="G237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A238">
+        <v>100237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>14</v>
+      </c>
+      <c r="C238" t="s">
+        <v>10</v>
+      </c>
+      <c r="D238" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+      <c r="F238">
+        <v>26</v>
+      </c>
+      <c r="G238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A239">
+        <v>100238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>10</v>
+      </c>
+      <c r="C239" t="s">
+        <v>23</v>
+      </c>
+      <c r="D239" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+      <c r="F239">
+        <v>26</v>
+      </c>
+      <c r="G239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A240">
+        <v>100239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>23</v>
+      </c>
+      <c r="C240" t="s">
+        <v>94</v>
+      </c>
+      <c r="D240" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240">
+        <v>1</v>
+      </c>
+      <c r="F240">
+        <v>26</v>
+      </c>
+      <c r="G240" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A241">
+        <v>100240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>95</v>
+      </c>
+      <c r="C241" t="s">
+        <v>23</v>
+      </c>
+      <c r="D241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+      <c r="F241">
+        <v>26</v>
+      </c>
+      <c r="G241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A242">
+        <v>100241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>23</v>
+      </c>
+      <c r="C242" t="s">
+        <v>10</v>
+      </c>
+      <c r="D242" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="F242">
+        <v>26</v>
+      </c>
+      <c r="G242" t="s">
+        <v>11</v>
+      </c>
+      <c r="H242" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A243">
+        <v>100242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>10</v>
+      </c>
+      <c r="C243" t="s">
+        <v>14</v>
+      </c>
+      <c r="D243" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A244">
+        <v>100243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244" t="s">
+        <v>125</v>
+      </c>
+      <c r="D244" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>11</v>
+      </c>
+      <c r="H244" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A245">
+        <v>100244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>125</v>
+      </c>
+      <c r="C245" t="s">
+        <v>15</v>
+      </c>
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245">
+        <v>1</v>
+      </c>
+      <c r="F245">
+        <v>27</v>
+      </c>
+      <c r="G245" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A246">
+        <v>100245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>15</v>
+      </c>
+      <c r="C246" t="s">
+        <v>126</v>
+      </c>
+      <c r="D246" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+      <c r="F246">
+        <v>27</v>
+      </c>
+      <c r="G246" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A247">
+        <v>100246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>126</v>
+      </c>
+      <c r="C247" t="s">
+        <v>10</v>
+      </c>
+      <c r="D247" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247">
+        <v>1</v>
+      </c>
+      <c r="F247">
+        <v>27</v>
+      </c>
+      <c r="G247" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A248">
+        <v>100247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>10</v>
+      </c>
+      <c r="C248" t="s">
+        <v>23</v>
+      </c>
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+      <c r="F248">
+        <v>27</v>
+      </c>
+      <c r="G248" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A249">
+        <v>100248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>23</v>
+      </c>
+      <c r="C249" t="s">
+        <v>10</v>
+      </c>
+      <c r="D249" t="s">
+        <v>9</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+      <c r="F249">
+        <v>27</v>
+      </c>
+      <c r="G249" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A250">
+        <v>100249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>10</v>
+      </c>
+      <c r="C250" t="s">
+        <v>94</v>
+      </c>
+      <c r="D250" t="s">
+        <v>9</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
+      <c r="F250">
+        <v>27</v>
+      </c>
+      <c r="G250" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A251">
+        <v>100250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>95</v>
+      </c>
+      <c r="C251" t="s">
+        <v>140</v>
+      </c>
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+      <c r="F251">
+        <v>27</v>
+      </c>
+      <c r="G251" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A252">
+        <v>100251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>140</v>
+      </c>
+      <c r="C252" t="s">
+        <v>94</v>
+      </c>
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+      <c r="F252">
+        <v>27</v>
+      </c>
+      <c r="G252" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A253">
+        <v>100252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>95</v>
+      </c>
+      <c r="C253" t="s">
+        <v>10</v>
+      </c>
+      <c r="D253" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253">
+        <v>1</v>
+      </c>
+      <c r="F253">
+        <v>27</v>
+      </c>
+      <c r="G253" t="s">
+        <v>11</v>
+      </c>
+      <c r="I253" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A254">
+        <v>100253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>10</v>
+      </c>
+      <c r="C254" t="s">
+        <v>94</v>
+      </c>
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254">
+        <v>1</v>
+      </c>
+      <c r="F254">
+        <v>28</v>
+      </c>
+      <c r="G254" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A255">
+        <v>100254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>95</v>
+      </c>
+      <c r="C255" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+      <c r="F255">
+        <v>28</v>
+      </c>
+      <c r="G255" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A256">
+        <v>100255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256" t="s">
+        <v>94</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256">
+        <v>1</v>
+      </c>
+      <c r="F256">
+        <v>28</v>
+      </c>
+      <c r="G256" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A257">
+        <v>100256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>95</v>
+      </c>
+      <c r="C257" t="s">
+        <v>14</v>
+      </c>
+      <c r="D257" t="s">
+        <v>9</v>
+      </c>
+      <c r="E257">
+        <v>1</v>
+      </c>
+      <c r="F257">
+        <v>28</v>
+      </c>
+      <c r="G257" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A258">
+        <v>100257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>14</v>
+      </c>
+      <c r="C258" t="s">
+        <v>94</v>
+      </c>
+      <c r="D258" t="s">
+        <v>9</v>
+      </c>
+      <c r="E258">
+        <v>1</v>
+      </c>
+      <c r="F258">
+        <v>28</v>
+      </c>
+      <c r="G258" t="s">
+        <v>76</v>
+      </c>
+      <c r="H258" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A259">
+        <v>100258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>95</v>
+      </c>
+      <c r="C259" t="s">
+        <v>15</v>
+      </c>
+      <c r="D259" t="s">
+        <v>9</v>
+      </c>
+      <c r="E259">
+        <v>1</v>
+      </c>
+      <c r="F259">
+        <v>28</v>
+      </c>
+      <c r="G259" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A260">
+        <v>100259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>15</v>
+      </c>
+      <c r="C260" t="s">
+        <v>128</v>
+      </c>
+      <c r="D260" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260">
+        <v>1</v>
+      </c>
+      <c r="F260">
+        <v>28</v>
+      </c>
+      <c r="G260" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A261">
+        <v>100260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>128</v>
+      </c>
+      <c r="C261" t="s">
+        <v>129</v>
+      </c>
+      <c r="D261" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261">
+        <v>1</v>
+      </c>
+      <c r="F261">
+        <v>28</v>
+      </c>
+      <c r="G261" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A262">
+        <v>100261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>129</v>
+      </c>
+      <c r="C262" t="s">
+        <v>14</v>
+      </c>
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+      <c r="F262">
+        <v>28</v>
+      </c>
+      <c r="G262" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A263">
+        <v>100262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>14</v>
+      </c>
+      <c r="C263" t="s">
+        <v>130</v>
+      </c>
+      <c r="D263" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263">
+        <v>1</v>
+      </c>
+      <c r="F263">
+        <v>28</v>
+      </c>
+      <c r="G263" t="s">
+        <v>76</v>
+      </c>
+      <c r="H263" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A264">
+        <v>100263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>130</v>
+      </c>
+      <c r="C264" t="s">
+        <v>65</v>
+      </c>
+      <c r="D264" t="s">
+        <v>9</v>
+      </c>
+      <c r="E264">
+        <v>1</v>
+      </c>
+      <c r="F264">
+        <v>28</v>
+      </c>
+      <c r="G264" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A265">
+        <v>100264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>65</v>
+      </c>
+      <c r="C265" t="s">
+        <v>132</v>
+      </c>
+      <c r="D265" t="s">
+        <v>9</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+      <c r="F265">
+        <v>28</v>
+      </c>
+      <c r="G265" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A266">
+        <v>100265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>132</v>
+      </c>
+      <c r="C266" t="s">
+        <v>10</v>
+      </c>
+      <c r="D266" t="s">
+        <v>9</v>
+      </c>
+      <c r="E266">
+        <v>1</v>
+      </c>
+      <c r="F266">
+        <v>28</v>
+      </c>
+      <c r="G266" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A267">
+        <v>100266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>10</v>
+      </c>
+      <c r="C267" t="s">
+        <v>19</v>
+      </c>
+      <c r="D267" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267">
+        <v>1</v>
+      </c>
+      <c r="F267">
+        <v>28</v>
+      </c>
+      <c r="G267" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A268">
+        <v>100267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>19</v>
+      </c>
+      <c r="C268" t="s">
+        <v>10</v>
+      </c>
+      <c r="D268" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268">
+        <v>1</v>
+      </c>
+      <c r="F268">
+        <v>28</v>
+      </c>
+      <c r="G268" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A269">
+        <v>100268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>10</v>
+      </c>
+      <c r="C269" t="s">
+        <v>26</v>
+      </c>
+      <c r="D269" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="F269">
+        <v>28</v>
+      </c>
+      <c r="G269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A270">
+        <v>100269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>26</v>
+      </c>
+      <c r="C270" t="s">
+        <v>10</v>
+      </c>
+      <c r="D270" t="s">
+        <v>9</v>
+      </c>
+      <c r="E270">
+        <v>1</v>
+      </c>
+      <c r="F270">
+        <v>28</v>
+      </c>
+      <c r="G270" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A271">
+        <v>100270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>10</v>
+      </c>
+      <c r="C271" t="s">
+        <v>133</v>
+      </c>
+      <c r="D271" t="s">
+        <v>9</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+      <c r="F271">
+        <v>29</v>
+      </c>
+      <c r="G271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A272">
+        <v>100271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>133</v>
+      </c>
+      <c r="C272" t="s">
+        <v>65</v>
+      </c>
+      <c r="D272" t="s">
+        <v>9</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+      <c r="F272">
+        <v>29</v>
+      </c>
+      <c r="G272" t="s">
+        <v>11</v>
+      </c>
+      <c r="H272" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A273">
+        <v>100272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>65</v>
+      </c>
+      <c r="C273" t="s">
+        <v>10</v>
+      </c>
+      <c r="D273" t="s">
+        <v>9</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="F273">
+        <v>29</v>
+      </c>
+      <c r="G273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A274">
+        <v>100273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>10</v>
+      </c>
+      <c r="C274" t="s">
+        <v>64</v>
+      </c>
+      <c r="D274" t="s">
+        <v>9</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+      <c r="F274">
+        <v>29</v>
+      </c>
+      <c r="G274" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A275">
+        <v>100274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>64</v>
+      </c>
+      <c r="C275" t="s">
+        <v>10</v>
+      </c>
+      <c r="D275" t="s">
+        <v>9</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="F275">
+        <v>29</v>
+      </c>
+      <c r="G275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A276">
+        <v>100275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>10</v>
+      </c>
+      <c r="C276" t="s">
+        <v>14</v>
+      </c>
+      <c r="D276" t="s">
+        <v>9</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+      <c r="F276">
+        <v>30</v>
+      </c>
+      <c r="G276" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A277">
+        <v>100276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>14</v>
+      </c>
+      <c r="C277" t="s">
+        <v>19</v>
+      </c>
+      <c r="D277" t="s">
+        <v>9</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+      <c r="F277">
+        <v>30</v>
+      </c>
+      <c r="G277" t="s">
+        <v>11</v>
+      </c>
+      <c r="H277" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A278">
+        <v>100277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>19</v>
+      </c>
+      <c r="C278" t="s">
+        <v>135</v>
+      </c>
+      <c r="D278" t="s">
+        <v>9</v>
+      </c>
+      <c r="E278">
+        <v>1</v>
+      </c>
+      <c r="F278">
+        <v>30</v>
+      </c>
+      <c r="G278" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A279">
+        <v>100278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>135</v>
+      </c>
+      <c r="C279" t="s">
+        <v>136</v>
+      </c>
+      <c r="D279" t="s">
+        <v>9</v>
+      </c>
+      <c r="E279">
+        <v>1</v>
+      </c>
+      <c r="F279">
+        <v>30</v>
+      </c>
+      <c r="G279" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A280">
+        <v>100279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>136</v>
+      </c>
+      <c r="C280" t="s">
+        <v>10</v>
+      </c>
+      <c r="D280" t="s">
+        <v>9</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+      <c r="F280">
+        <v>30</v>
+      </c>
+      <c r="G280" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A281">
+        <v>100280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>10</v>
+      </c>
+      <c r="C281" t="s">
+        <v>23</v>
+      </c>
+      <c r="D281" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="F281">
+        <v>30</v>
+      </c>
+      <c r="G281" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A282">
+        <v>100281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>23</v>
+      </c>
+      <c r="C282" t="s">
+        <v>97</v>
+      </c>
+      <c r="D282" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+      <c r="F282">
+        <v>30</v>
+      </c>
+      <c r="G282" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A283">
+        <v>100282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>97</v>
+      </c>
+      <c r="C283" t="s">
+        <v>10</v>
+      </c>
+      <c r="D283" t="s">
+        <v>9</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
+      <c r="F283">
+        <v>30</v>
+      </c>
+      <c r="G283" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A284">
+        <v>100283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" t="s">
+        <v>23</v>
+      </c>
+      <c r="D284" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+      <c r="F284">
+        <v>31</v>
+      </c>
+      <c r="G284" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A285">
+        <v>100284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>23</v>
+      </c>
+      <c r="C285" t="s">
+        <v>31</v>
+      </c>
+      <c r="D285" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285">
+        <v>31</v>
+      </c>
+      <c r="G285" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A286">
+        <v>100285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>31</v>
+      </c>
+      <c r="C286" t="s">
+        <v>14</v>
+      </c>
+      <c r="D286" t="s">
+        <v>9</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+      <c r="F286">
+        <v>31</v>
+      </c>
+      <c r="G286" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A287">
+        <v>100286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>14</v>
+      </c>
+      <c r="C287" t="s">
+        <v>19</v>
+      </c>
+      <c r="D287" t="s">
+        <v>9</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+      <c r="F287">
+        <v>31</v>
+      </c>
+      <c r="G287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A288">
+        <v>100287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>19</v>
+      </c>
+      <c r="C288" t="s">
+        <v>10</v>
+      </c>
+      <c r="D288" t="s">
+        <v>9</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+      <c r="F288">
+        <v>31</v>
+      </c>
+      <c r="G288" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A289">
+        <v>100288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289" t="s">
+        <v>138</v>
+      </c>
+      <c r="D289" t="s">
+        <v>9</v>
+      </c>
+      <c r="E289">
+        <v>1</v>
+      </c>
+      <c r="F289">
+        <v>31</v>
+      </c>
+      <c r="G289" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A290">
+        <v>100289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>138</v>
+      </c>
+      <c r="C290" t="s">
+        <v>19</v>
+      </c>
+      <c r="D290" t="s">
+        <v>9</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290">
+        <v>31</v>
+      </c>
+      <c r="G290" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A291">
+        <v>100290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>19</v>
+      </c>
+      <c r="C291" t="s">
+        <v>23</v>
+      </c>
+      <c r="D291" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291">
+        <v>1</v>
+      </c>
+      <c r="F291">
+        <v>31</v>
+      </c>
+      <c r="G291" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A292">
+        <v>100291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>23</v>
+      </c>
+      <c r="C292" t="s">
+        <v>10</v>
+      </c>
+      <c r="D292" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292">
+        <v>1</v>
+      </c>
+      <c r="F292">
+        <v>31</v>
+      </c>
+      <c r="G292" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A293">
+        <v>100292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" t="s">
+        <v>31</v>
+      </c>
+      <c r="D293" t="s">
+        <v>9</v>
+      </c>
+      <c r="E293">
+        <v>1</v>
+      </c>
+      <c r="F293">
+        <v>31</v>
+      </c>
+      <c r="G293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A294">
+        <v>100293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>31</v>
+      </c>
+      <c r="C294" t="s">
+        <v>10</v>
+      </c>
+      <c r="D294" t="s">
+        <v>9</v>
+      </c>
+      <c r="E294">
+        <v>1</v>
+      </c>
+      <c r="F294">
+        <v>31</v>
+      </c>
+      <c r="G294" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="edges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$479</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I295"/>
+  <dimension ref="A1:I479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11097,8 +11097,6976 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>100295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>2</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>100296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>2</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>100297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>2</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>100298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>downings_counsellor_chamber</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>2</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>100299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>downings_counsellor_chamber</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>lincolns_inn</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>2</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>100300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>lincolns_inn</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>2</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>"Sir Harry Wright's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>100301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>2</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>100302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>2</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>100303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>2</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Gammer East; James the porter</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>"took Gammer East, and James the porter, a soldier, to my Lord's lodgings"</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>100304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>2</v>
+      </c>
+      <c r="F305" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>100305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>2</v>
+      </c>
+      <c r="F306" t="n">
+        <v>1</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>100306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>2</v>
+      </c>
+      <c r="F307" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>100307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>2</v>
+      </c>
+      <c r="F308" t="n">
+        <v>2</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>100308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>2</v>
+      </c>
+      <c r="F309" t="n">
+        <v>2</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>100309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>2</v>
+      </c>
+      <c r="F310" t="n">
+        <v>2</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>100310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>2</v>
+      </c>
+      <c r="F311" t="n">
+        <v>2</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Thomas Doling</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Luellin met on the way</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>100311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>lestrange_calthorpe_chamber</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>2</v>
+      </c>
+      <c r="F312" t="n">
+        <v>2</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Thomas Doling</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>100312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>lestrange_calthorpe_chamber</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>calthrop_grocer_house</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>2</v>
+      </c>
+      <c r="F313" t="n">
+        <v>2</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Thomas Doling; Mr Calthrop's man</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>waterman White</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>100313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>calthrop_grocer_house</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>bridge_tavern</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>2</v>
+      </c>
+      <c r="F314" t="n">
+        <v>2</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Thomas Doling; Mr Calthrop's man</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>100314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>bridge_tavern</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>the_strand</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>2</v>
+      </c>
+      <c r="F315" t="n">
+        <v>2</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Thomas Doling; Mr Calthrop's man (set down at the Temple)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>"over against Somerset House, hearing the noise of guns, we landed"</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>100315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>the_strand</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>mrs_johnson_house</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>2</v>
+      </c>
+      <c r="F316" t="n">
+        <v>2</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Thomas Doling</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>100316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>mrs_johnson_house</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>2</v>
+      </c>
+      <c r="F317" t="n">
+        <v>2</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>"went home on foot"</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>100317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>2</v>
+      </c>
+      <c r="F318" t="n">
+        <v>2</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>100318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>2</v>
+      </c>
+      <c r="F319" t="n">
+        <v>2</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>100319</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>2</v>
+      </c>
+      <c r="F320" t="n">
+        <v>3</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>100320</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>2</v>
+      </c>
+      <c r="F321" t="n">
+        <v>3</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>100321</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>guard_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>2</v>
+      </c>
+      <c r="F322" t="n">
+        <v>3</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>100322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>guard_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>2</v>
+      </c>
+      <c r="F323" t="n">
+        <v>3</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>100323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>house_of_commons</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>2</v>
+      </c>
+      <c r="F324" t="n">
+        <v>3</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Jane Turner; Joyce Norton</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>"shewed them the manner of the Houses sitting"</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>100324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>house_of_commons</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>2</v>
+      </c>
+      <c r="F325" t="n">
+        <v>3</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Jane Turner; Joyce Norton</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>"we took him out of the Hall"</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>100325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>2</v>
+      </c>
+      <c r="F326" t="n">
+        <v>3</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Jane Turner; Joyce Norton; Roger Pepys</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>100326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>wilkinsons_cookshop</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>2</v>
+      </c>
+      <c r="F327" t="n">
+        <v>3</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Jane Turner; Joyce Norton</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>100327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>wilkinsons_cookshop</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>2</v>
+      </c>
+      <c r="F328" t="n">
+        <v>3</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Jane Turner; Joyce Norton</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>100328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>2</v>
+      </c>
+      <c r="F329" t="n">
+        <v>3</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Jane Turner; Joyce Norton</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>100329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>palace_yard_westminster</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>2</v>
+      </c>
+      <c r="F330" t="n">
+        <v>3</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>"went to hear news"</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>100330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>palace_yard_westminster</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>2</v>
+      </c>
+      <c r="F331" t="n">
+        <v>3</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>"I returned"</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>100331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>2</v>
+      </c>
+      <c r="F332" t="n">
+        <v>3</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Jane Turner; Joyce Norton; Theophila Turner</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>100332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>charing_cross</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>2</v>
+      </c>
+      <c r="F333" t="n">
+        <v>3</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Jane Turner; Joyce Norton; Theophila Turner</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>"I set them as far as Charing Cross, and there left them and my wife"</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>100333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>charing_cross</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>2</v>
+      </c>
+      <c r="F334" t="n">
+        <v>3</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>"I went to see Mrs. Ann" - Mrs Ann taken to be at my Lord's lodgings, cf. 1 Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>100334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>2</v>
+      </c>
+      <c r="F335" t="n">
+        <v>3</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>100335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>2</v>
+      </c>
+      <c r="F336" t="n">
+        <v>4</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>100336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>2</v>
+      </c>
+      <c r="F337" t="n">
+        <v>4</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>100337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>2</v>
+      </c>
+      <c r="F338" t="n">
+        <v>4</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Mr Swan; Captain Stone</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>100338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>swan_house</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>2</v>
+      </c>
+      <c r="F339" t="n">
+        <v>4</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>100339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>swan_house</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>stephens_chamber_temple</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>2</v>
+      </c>
+      <c r="F340" t="n">
+        <v>4</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>"took him out by water to the Counsellor at the Temple"</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>100340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>stephens_chamber_temple</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>grays_inn</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>2</v>
+      </c>
+      <c r="F341" t="n">
+        <v>4</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>100341</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>grays_inn</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_4</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>2</v>
+      </c>
+      <c r="F342" t="n">
+        <v>4</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Mr Swan; acquaintance of Sotherton Ellis</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>100342</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_4</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>lord_widdrington_house</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>2</v>
+      </c>
+      <c r="F343" t="n">
+        <v>4</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>"leaving Swan at his master's, my Lord Widdrington"</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>100343</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>lord_widdrington_house</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>lincolns_inn</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>2</v>
+      </c>
+      <c r="F344" t="n">
+        <v>4</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>"I met with Spicer, Washington, and D. Vines in Lincoln's Inn Court"</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>100344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>lincolns_inn</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>2</v>
+      </c>
+      <c r="F345" t="n">
+        <v>4</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>"to Mrs. Crew's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>100345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>2</v>
+      </c>
+      <c r="F346" t="n">
+        <v>4</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>"Sir Harry Wright's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>100346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>2</v>
+      </c>
+      <c r="F347" t="n">
+        <v>4</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>link boy</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>100347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>2</v>
+      </c>
+      <c r="F348" t="n">
+        <v>4</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>100348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>2</v>
+      </c>
+      <c r="F349" t="n">
+        <v>5</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>"to Mr. Gunning" - see DECISIONS.md open question 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>2</v>
+      </c>
+      <c r="F350" t="n">
+        <v>5</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>100350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>2</v>
+      </c>
+      <c r="F351" t="n">
+        <v>5</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>"I returned and called at the Chequers"</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>100351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>2</v>
+      </c>
+      <c r="F352" t="n">
+        <v>5</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>100352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>st_brides_church</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>2</v>
+      </c>
+      <c r="F353" t="n">
+        <v>5</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>"To their church in the afternoon"</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>100353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>st_brides_church</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>2</v>
+      </c>
+      <c r="F354" t="n">
+        <v>5</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Jane Turner</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>100354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>2</v>
+      </c>
+      <c r="F355" t="n">
+        <v>5</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>100355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>2</v>
+      </c>
+      <c r="F356" t="n">
+        <v>5</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>100356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>2</v>
+      </c>
+      <c r="F357" t="n">
+        <v>6</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>100357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>palace_yard_westminster</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>2</v>
+      </c>
+      <c r="F358" t="n">
+        <v>6</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Mr Andrews</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>"So back to Westminster and walked with him thither"</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>100358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>palace_yard_westminster</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>2</v>
+      </c>
+      <c r="F359" t="n">
+        <v>6</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Mr Andrews</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>"At the Hall we parted"</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>100359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>2</v>
+      </c>
+      <c r="F360" t="n">
+        <v>6</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>100360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>2</v>
+      </c>
+      <c r="F361" t="n">
+        <v>6</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>100361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>2</v>
+      </c>
+      <c r="F362" t="n">
+        <v>6</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>100362</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>bull_head_tavern</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>2</v>
+      </c>
+      <c r="F363" t="n">
+        <v>6</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>John Pepys</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>100363</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>bull_head_tavern</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>2</v>
+      </c>
+      <c r="F364" t="n">
+        <v>6</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>"I to Mrs. Ann"</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>100364</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>2</v>
+      </c>
+      <c r="F365" t="n">
+        <v>6</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>100365</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>2</v>
+      </c>
+      <c r="F366" t="n">
+        <v>6</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>100366</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>2</v>
+      </c>
+      <c r="F367" t="n">
+        <v>7</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>"to give Mr. Hawly notice of my being forced to go into London"</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>100367</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>the_temple</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>2</v>
+      </c>
+      <c r="F368" t="n">
+        <v>7</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Mr Hawly</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>"he and I walked as far as the Temple"</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>100368</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>the_temple</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>st_pauls_school</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>2</v>
+      </c>
+      <c r="F369" t="n">
+        <v>7</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>100369</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>st_pauls_school</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>thomas_pepys_shop</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>2</v>
+      </c>
+      <c r="F370" t="n">
+        <v>7</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>"it being too soon, went and drank my morning draft with my cozen Tom Pepys the turner, and saw his house and shop"</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>100370</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>thomas_pepys_shop</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>st_pauls_school</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>2</v>
+      </c>
+      <c r="F371" t="n">
+        <v>7</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>"thence to school"</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>100371</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>st_pauls_school</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>2</v>
+      </c>
+      <c r="F372" t="n">
+        <v>7</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>"I went straight home and dined"</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>100372</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>2</v>
+      </c>
+      <c r="F373" t="n">
+        <v>7</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>100373</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>captain_stone_lodgings</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>2</v>
+      </c>
+      <c r="F374" t="n">
+        <v>7</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>100374</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>captain_stone_lodgings</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>temple_gardens</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>2</v>
+      </c>
+      <c r="F375" t="n">
+        <v>7</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Captain Stone</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>100375</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>temple_gardens</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>2</v>
+      </c>
+      <c r="F376" t="n">
+        <v>7</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>"Thence back on foot home"</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>100376</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>2</v>
+      </c>
+      <c r="F377" t="n">
+        <v>7</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>100377</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>2</v>
+      </c>
+      <c r="F378" t="n">
+        <v>7</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>"calling upon Mrs. Ann"</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>100378</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>2</v>
+      </c>
+      <c r="F379" t="n">
+        <v>7</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>100379</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>2</v>
+      </c>
+      <c r="F380" t="n">
+        <v>8</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Mr Fossan</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>"the Swan in the Palace yard"</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>100380</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>2</v>
+      </c>
+      <c r="F381" t="n">
+        <v>8</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>100381</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>2</v>
+      </c>
+      <c r="F382" t="n">
+        <v>8</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Mr Carter; Captain Lidcott</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>"in the way I met with Captain Lidcott"</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>100382</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>captain_stone_lodgings</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>2</v>
+      </c>
+      <c r="F383" t="n">
+        <v>8</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>100383</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>captain_stone_lodgings</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>2</v>
+      </c>
+      <c r="F384" t="n">
+        <v>8</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>"I returned to Mr. Carter"</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>100384</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>2</v>
+      </c>
+      <c r="F385" t="n">
+        <v>8</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Mr Carter; Mr Butler</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>100385</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>2</v>
+      </c>
+      <c r="F386" t="n">
+        <v>8</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Mr Carter; Mr Butler</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>"a Rhenish wine house" - taken to be Prior's, cf. 3 Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>100386</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>wheeler_house</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>2</v>
+      </c>
+      <c r="F387" t="n">
+        <v>8</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>"in my way delivering a letter ... to Sir N. Wheeler"</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>100387</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>wheeler_house</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>2</v>
+      </c>
+      <c r="F388" t="n">
+        <v>8</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>100388</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>2</v>
+      </c>
+      <c r="F389" t="n">
+        <v>8</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>"I called in my way upon Mrs. Jem"</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>100389</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>the_temple</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>2</v>
+      </c>
+      <c r="F390" t="n">
+        <v>8</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>100390</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>the_temple</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>2</v>
+      </c>
+      <c r="F391" t="n">
+        <v>8</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>100391</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>fleet_street</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>2</v>
+      </c>
+      <c r="F392" t="n">
+        <v>8</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>"in Fleet Street, received a great jostle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>100392</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>fleet_street</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>2</v>
+      </c>
+      <c r="F393" t="n">
+        <v>8</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>100393</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>2</v>
+      </c>
+      <c r="F394" t="n">
+        <v>9</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>100394</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>phelps_house</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>2</v>
+      </c>
+      <c r="F395" t="n">
+        <v>9</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>100395</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>phelps_house</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>2</v>
+      </c>
+      <c r="F396" t="n">
+        <v>9</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>100396</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>upper_bench_court</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>2</v>
+      </c>
+      <c r="F397" t="n">
+        <v>9</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>100397</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>upper_bench_court</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>2</v>
+      </c>
+      <c r="F398" t="n">
+        <v>9</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>"I went to my office ... after I had been at the Upper Bench"</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>100398</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>2</v>
+      </c>
+      <c r="F399" t="n">
+        <v>9</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>100399</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>2</v>
+      </c>
+      <c r="F400" t="n">
+        <v>9</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>"her Aunt Wright's, but she was gone, so I went thither"</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>100400</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>2</v>
+      </c>
+      <c r="F401" t="n">
+        <v>9</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>100401</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>james_pearse_house</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>2</v>
+      </c>
+      <c r="F402" t="n">
+        <v>9</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Mr Pierce</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>"Mr. Pierce the surgeon, who would needs take me home"</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>100402</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>james_pearse_house</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>2</v>
+      </c>
+      <c r="F403" t="n">
+        <v>9</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>100403</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>2</v>
+      </c>
+      <c r="F404" t="n">
+        <v>9</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>100404</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>stephens_chamber_temple</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>2</v>
+      </c>
+      <c r="F405" t="n">
+        <v>9</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>"by water to the Temple to our Counsel"</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>100405</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>stephens_chamber_temple</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>2</v>
+      </c>
+      <c r="F406" t="n">
+        <v>9</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>100406</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>sugar_loaf_tavern</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>2</v>
+      </c>
+      <c r="F407" t="n">
+        <v>9</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>"a drinking-house near Temple Bar" - named the Sugar Loaf on 10 Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>100407</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>sugar_loaf_tavern</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>2</v>
+      </c>
+      <c r="F408" t="n">
+        <v>9</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>"so by coach home. I called at Mr. Harper's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>100408</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>2</v>
+      </c>
+      <c r="F409" t="n">
+        <v>9</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>100409</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>swan_house</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>2</v>
+      </c>
+      <c r="F410" t="n">
+        <v>10</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>100410</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>swan_house</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>court_of_wards</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>2</v>
+      </c>
+      <c r="F411" t="n">
+        <v>10</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>100411</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>court_of_wards</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>exchequer_court</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>2</v>
+      </c>
+      <c r="F412" t="n">
+        <v>10</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Mr Swan</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>100412</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>exchequer_court</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>2</v>
+      </c>
+      <c r="F413" t="n">
+        <v>10</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>100413</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>2</v>
+      </c>
+      <c r="F414" t="n">
+        <v>10</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Mr Lenard</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>100414</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>2</v>
+      </c>
+      <c r="F415" t="n">
+        <v>10</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>100415</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>exchequer_court</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>2</v>
+      </c>
+      <c r="F416" t="n">
+        <v>10</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>100416</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>exchequer_court</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>2</v>
+      </c>
+      <c r="F417" t="n">
+        <v>10</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>100417</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>valentine_fage_house</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>2</v>
+      </c>
+      <c r="F418" t="n">
+        <v>10</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Mr Moore</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>"with him went into London to Mr. Fage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>100418</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>valentine_fage_house</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>sugar_loaf_tavern</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>2</v>
+      </c>
+      <c r="F419" t="n">
+        <v>10</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Mr Moore</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>100419</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>sugar_loaf_tavern</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>2</v>
+      </c>
+      <c r="F420" t="n">
+        <v>10</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>100420</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>2</v>
+      </c>
+      <c r="F421" t="n">
+        <v>11</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>100421</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>2</v>
+      </c>
+      <c r="F422" t="n">
+        <v>11</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>100422</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>commons_lobby</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>2</v>
+      </c>
+      <c r="F423" t="n">
+        <v>11</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>100423</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>commons_lobby</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>2</v>
+      </c>
+      <c r="F424" t="n">
+        <v>11</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>"I went then down into the Hall"</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>100424</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>cookshop_unknown_2</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>2</v>
+      </c>
+      <c r="F425" t="n">
+        <v>11</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>"calling at two or three shops, but could have no dinner"</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>100425</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>cookshop_unknown_2</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>the_rolls</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>2</v>
+      </c>
+      <c r="F426" t="n">
+        <v>11</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>100426</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>the_rolls</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>chetwind_office</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>2</v>
+      </c>
+      <c r="F427" t="n">
+        <v>11</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>100427</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>chetwind_office</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>guildhall</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>2</v>
+      </c>
+      <c r="F428" t="n">
+        <v>11</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>100428</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>guildhall</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>three_tuns_tavern</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>2</v>
+      </c>
+      <c r="F429" t="n">
+        <v>11</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Mr Chetwind; friend of Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>100429</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>three_tuns_tavern</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_5</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>2</v>
+      </c>
+      <c r="F430" t="n">
+        <v>11</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Mr Chetwind; friend of Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>"not liking the wine we went to an alehouse"</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>100430</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_5</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>guildhall</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>2</v>
+      </c>
+      <c r="F431" t="n">
+        <v>11</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>"I went alone"</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>100431</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>guildhall</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_5</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>2</v>
+      </c>
+      <c r="F432" t="n">
+        <v>11</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Mr Lock</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>"took him to an alehouse" - taken to be the same alehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>100432</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_5</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>merchant_house_unknown_1</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>2</v>
+      </c>
+      <c r="F433" t="n">
+        <v>11</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Mr Lock; Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>"a merchant's house hard by"</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>100433</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>merchant_house_unknown_1</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>star_tavern</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>2</v>
+      </c>
+      <c r="F434" t="n">
+        <v>11</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Mr Lock; Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>100434</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>star_tavern</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>2</v>
+      </c>
+      <c r="F435" t="n">
+        <v>11</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Mr Chetwind</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>"we came to the Chequers at Charing Cross"</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>100435</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>chequers_inn</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>2</v>
+      </c>
+      <c r="F436" t="n">
+        <v>11</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>100436</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>new_exchange</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>2</v>
+      </c>
+      <c r="F437" t="n">
+        <v>11</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>"after walking as far as the Exchange" - read as the New Exchange in the Strand, not the Royal Exchange in the City, on the walking distance from Axe Yard; network4 reads it the same way. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>100437</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>new_exchange</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>2</v>
+      </c>
+      <c r="F438" t="n">
+        <v>11</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>100438</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>2</v>
+      </c>
+      <c r="F439" t="n">
+        <v>12</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Mr Pierce</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>100439</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>2</v>
+      </c>
+      <c r="F440" t="n">
+        <v>12</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>100440</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>2</v>
+      </c>
+      <c r="F441" t="n">
+        <v>12</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Thomas Pepys; partner of Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>"before dinner we went and took a walk round the park"</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>100441</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>st_jamess_park</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>2</v>
+      </c>
+      <c r="F442" t="n">
+        <v>12</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Thomas Pepys; partner of Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>100442</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>moorfields</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>2</v>
+      </c>
+      <c r="F443" t="n">
+        <v>12</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Thomas Pepys; partner of Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>"we three went into London together"</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>100443</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>moorfields</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>st_pauls_churchyard</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>2</v>
+      </c>
+      <c r="F444" t="n">
+        <v>12</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>"Here I took leave of them, and so to Paul's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>100444</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>st_pauls_churchyard</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>2</v>
+      </c>
+      <c r="F445" t="n">
+        <v>12</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>100445</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>2</v>
+      </c>
+      <c r="F446" t="n">
+        <v>12</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>100446</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>2</v>
+      </c>
+      <c r="F447" t="n">
+        <v>12</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>100447</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>2</v>
+      </c>
+      <c r="F448" t="n">
+        <v>13</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>100448</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>2</v>
+      </c>
+      <c r="F449" t="n">
+        <v>13</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>100449</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>2</v>
+      </c>
+      <c r="F450" t="n">
+        <v>13</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>"in the way met with Catan on foot in the street" - no node, met in passing</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>100450</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>2</v>
+      </c>
+      <c r="F451" t="n">
+        <v>13</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>100451</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>playfords_shop</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>2</v>
+      </c>
+      <c r="F452" t="n">
+        <v>13</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>100452</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>playfords_shop</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>2</v>
+      </c>
+      <c r="F453" t="n">
+        <v>13</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>100453</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>cumberland_lodgings</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>2</v>
+      </c>
+      <c r="F454" t="n">
+        <v>13</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>100454</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>cumberland_lodgings</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>2</v>
+      </c>
+      <c r="F455" t="n">
+        <v>13</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>"I returned"</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>100455</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>valentine_fage_house</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>2</v>
+      </c>
+      <c r="F456" t="n">
+        <v>13</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>"I went to Mr. Fage from my father's" - stated at the end of the entry, placed here on the sequence it describes</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>100456</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>valentine_fage_house</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>2</v>
+      </c>
+      <c r="F457" t="n">
+        <v>13</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>100457</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>2</v>
+      </c>
+      <c r="F458" t="n">
+        <v>13</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>100458</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>2</v>
+      </c>
+      <c r="F459" t="n">
+        <v>14</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Mr Moore</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>100459</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>2</v>
+      </c>
+      <c r="F460" t="n">
+        <v>14</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Mr Moore</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>100460</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>2</v>
+      </c>
+      <c r="F461" t="n">
+        <v>14</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>100461</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>2</v>
+      </c>
+      <c r="F462" t="n">
+        <v>14</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Mr Hill</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>100462</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>2</v>
+      </c>
+      <c r="F463" t="n">
+        <v>14</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>100463</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>2</v>
+      </c>
+      <c r="F464" t="n">
+        <v>14</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>100464</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>2</v>
+      </c>
+      <c r="F465" t="n">
+        <v>14</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>100465</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>2</v>
+      </c>
+      <c r="F466" t="n">
+        <v>14</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>100466</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>2</v>
+      </c>
+      <c r="F467" t="n">
+        <v>14</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>100467</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>2</v>
+      </c>
+      <c r="F468" t="n">
+        <v>14</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>100468</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>2</v>
+      </c>
+      <c r="F469" t="n">
+        <v>14</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>100469</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>2</v>
+      </c>
+      <c r="F470" t="n">
+        <v>15</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Captain Holland; Captain Cuttance</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>100470</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>2</v>
+      </c>
+      <c r="F471" t="n">
+        <v>15</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>100471</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>2</v>
+      </c>
+      <c r="F472" t="n">
+        <v>15</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Mr Hill</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>100472</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>2</v>
+      </c>
+      <c r="F473" t="n">
+        <v>15</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>100473</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>hering_house</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>2</v>
+      </c>
+      <c r="F474" t="n">
+        <v>15</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>100474</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>hering_house</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>st_pauls_churchyard</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>2</v>
+      </c>
+      <c r="F475" t="n">
+        <v>15</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>100475</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>st_pauls_churchyard</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>2</v>
+      </c>
+      <c r="F476" t="n">
+        <v>15</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>100476</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>2</v>
+      </c>
+      <c r="F477" t="n">
+        <v>15</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>"my Lady Wright's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>100477</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>anne_wright_house</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>2</v>
+      </c>
+      <c r="F478" t="n">
+        <v>15</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>100478</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>2</v>
+      </c>
+      <c r="F479" t="n">
+        <v>15</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I295"/>
+  <autoFilter ref="A1:I479"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="edges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$479</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$481</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I479"/>
+  <dimension ref="A1:I481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>the_sun_pub</t>
+          <t>the_sun_tavern</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>the_sun_pub</t>
+          <t>the_sun_tavern</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>the_sun_pub</t>
+          <t>the_sun_tavern</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>the_sun_pub</t>
+          <t>the_sun_tavern</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Thomas Doling</t>
+          <t>Thomas Doling; Peter Llewellyn</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>calthrop_grocer_house</t>
+          <t>edward_calthrop_grocer</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Thomas Doling; Mr Calthrop's man</t>
+          <t>Thomas Doling; Edward Calthorpe; Mr White</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>calthrop_grocer_house</t>
+          <t>edward_calthrop_grocer</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Thomas Doling; Mr Calthrop's man</t>
+          <t>Thomas Doling; Edward Calthorpe</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>100314</t>
+          <t>100482</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>the_strand</t>
+          <t>the_temple</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -11840,31 +11840,27 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Thomas Doling; Mr Calthrop's man (set down at the Temple)</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>"over against Somerset House, hearing the noise of guns, we landed"</t>
-        </is>
-      </c>
+          <t>Thomas Doling; Edward Calthorpe</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>100315</t>
+          <t>100314</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
+          <t>the_temple</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
           <t>the_strand</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>mrs_johnson_house</t>
-        </is>
-      </c>
       <c r="D316" t="inlineStr">
         <is>
           <t>1659/60</t>
@@ -11878,7 +11874,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -11886,24 +11882,28 @@
           <t>Thomas Doling</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>"over against Somerset House, hearing the noise of guns, we landed"</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>100316</t>
+          <t>100315</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
+          <t>the_strand</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
           <t>mrs_johnson_house</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>home_axe_yard</t>
-        </is>
-      </c>
       <c r="D317" t="inlineStr">
         <is>
           <t>1659/60</t>
@@ -11920,27 +11920,27 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>"went home on foot"</t>
-        </is>
-      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Thomas Doling</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>100317</t>
+          <t>100316</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>mrs_johnson_house</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -11960,22 +11960,26 @@
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>"went home on foot"</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>100317</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
           <t>harpers_tavern</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -12000,17 +12004,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>100319</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -12022,7 +12026,7 @@
         <v>2</v>
       </c>
       <c r="F320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -12035,17 +12039,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>100320</t>
+          <t>100319</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
           <t>harpers_tavern</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>st_jamess_park</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -12070,17 +12074,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>100321</t>
+          <t>100320</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>st_jamess_park</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>guard_chamber_whitehall</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -12105,17 +12109,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>100321</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
+          <t>st_james_park</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
           <t>guard_chamber_whitehall</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -12140,17 +12144,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>100323</t>
+          <t>100322</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
+          <t>guard_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
           <t>office_exchequer</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>house_of_commons</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -12169,26 +12173,18 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>Jane Turner; Joyce Norton</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>"shewed them the manner of the Houses sitting"</t>
-        </is>
-      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>100324</t>
+          <t>100323</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>house_of_commons</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12219,7 +12215,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>"we took him out of the Hall"</t>
+          <t>"shewed them the manner of the Houses sitting"</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12466,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>st_jamess_park</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -12504,7 +12500,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>st_jamess_park</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12717,7 +12713,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Mr Swan; Captain Stone</t>
+          <t>William Swan; Captain Stone</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -12735,7 +12731,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>swan_house</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -12756,7 +12752,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -12769,7 +12765,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>swan_house</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12795,7 +12791,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -12838,7 +12834,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -12877,10 +12873,14 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Mr Swan; acquaintance of Sotherton Ellis</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr"/>
+          <t>William Swan; unknown man</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>acquaintance of Sotherton Ellis</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>lord_widdrington_house</t>
+          <t>thomas_widdrington_house</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>lord_widdrington_house</t>
+          <t>thomas_widdrington_house</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Mr Andrews</t>
+          <t>John Andrews</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Mr Andrews</t>
+          <t>John Andrews</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Mr Hawly</t>
+          <t>John Hawly</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>new_palace_yard_westminster</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>new_palace_yard_westminster</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>captain_stone_lodgings</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>captain_stone_lodgings</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Captain Stone</t>
+          <t>Captain John Stone</t>
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Mr Fossan</t>
+          <t>Thomas Fossan</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Mr Carter; Captain Lidcott</t>
+          <t>Charles Carter; Captain Robert Lidcott</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>captain_stone_lodgings</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>captain_stone_lodgings</t>
+          <t>john_stone_office</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Mr Carter; Mr Butler</t>
+          <t>Charles Carter; Mr Butler</t>
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Mr Carter; Mr Butler</t>
+          <t>Charles Carter; Mr Butler; William Howell</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>wheeler_house</t>
+          <t>william_wheeler_house</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>wheeler_house</t>
+          <t>william_wheeler_house</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>phelps_house</t>
+          <t>john_phelps_house</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>phelps_house</t>
+          <t>john_phelps_house</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Mr Pierce</t>
+          <t>James Pierce</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>swan_house</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>swan_house</t>
+          <t>william_swan_house</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I411" t="inlineStr"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Mr Swan</t>
+          <t>William Swan</t>
         </is>
       </c>
       <c r="I412" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Mr Lenard</t>
+          <t>John Leonard</t>
         </is>
       </c>
       <c r="I414" t="inlineStr"/>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Mr Moore</t>
+          <t>Henry Moore</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Mr Moore</t>
+          <t>Henry Moore</t>
         </is>
       </c>
       <c r="I419" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Mr Chetwind</t>
+          <t>James Chetwind</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>the_rolls</t>
+          <t>rolls_office_chancery</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Mr Chetwind</t>
+          <t>James Chetwind</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
@@ -16070,12 +16070,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>the_rolls</t>
+          <t>rolls_office_chancery</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>chetwind_office</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Mr Chetwind</t>
+          <t>James Chetwind</t>
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>chetwind_office</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Mr Chetwind</t>
+          <t>James Chetwind</t>
         </is>
       </c>
       <c r="I428" t="inlineStr"/>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Mr Chetwind; friend of Mr Chetwind</t>
+          <t>James Chetwind; friend of Mr Chetwind</t>
         </is>
       </c>
       <c r="I429" t="inlineStr"/>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Mr Chetwind; friend of Mr Chetwind</t>
+          <t>James Chetwind; friend of Mr Chetwind</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Mr Lock</t>
+          <t>Matthew Lock</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>merchant_house_unknown_1</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -16336,16 +16336,8 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>Mr Lock; Mr Chetwind</t>
-        </is>
-      </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>"a merchant's house hard by"</t>
-        </is>
-      </c>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -16355,12 +16347,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>merchant_house_unknown_1</t>
+          <t>james_chetwind_office</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>star_tavern</t>
+          <t>alehouse_unknown_5</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -16381,7 +16373,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Mr Lock; Mr Chetwind</t>
+          <t>James Chetwind</t>
         </is>
       </c>
       <c r="I434" t="inlineStr"/>
@@ -16394,12 +16386,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>star_tavern</t>
+          <t>alehouse_unknown_5</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>chequers_inn</t>
+          <t>merchant_house_unknown_1</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -16420,12 +16412,12 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Mr Chetwind</t>
+          <t>Matthew Lock; James Chetwind</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>"we came to the Chequers at Charing Cross"</t>
+          <t>"a merchant's house hard by"</t>
         </is>
       </c>
     </row>
@@ -16437,12 +16429,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>chequers_inn</t>
+          <t>merchant_house_unknown_1</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>star_tavern</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -16461,7 +16453,11 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>James Chetwind</t>
+        </is>
+      </c>
       <c r="I436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -16472,12 +16468,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>star_tavern</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>new_exchange</t>
+          <t>chequers_inn</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -16498,12 +16494,12 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Elizabeth Pepys</t>
+          <t>James Chetwind</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>"after walking as far as the Exchange" - read as the New Exchange in the Strand, not the Royal Exchange in the City, on the walking distance from Axe Yard; network4 reads it the same way. FLAG</t>
+          <t>"we came to the Chequers at Charing Cross"</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16511,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>new_exchange</t>
+          <t>chequers_inn</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -16539,11 +16535,7 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
+      <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -16559,7 +16551,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>new_exchange</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -16571,7 +16563,7 @@
         <v>2</v>
       </c>
       <c r="F439" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -16580,10 +16572,14 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Mr Pierce</t>
-        </is>
-      </c>
-      <c r="I439" t="inlineStr"/>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>"after walking as far as the Exchange" - read as the New Exchange in the Strand, not the Royal Exchange in the City, on the walking distance from Axe Yard; network4 reads it the same way. FLAG</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -16593,7 +16589,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>new_exchange</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -16610,14 +16606,18 @@
         <v>2</v>
       </c>
       <c r="F440" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>st_jamess_park</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -16654,14 +16654,10 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Thomas Pepys; partner of Thomas Pepys</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>"before dinner we went and took a walk round the park"</t>
-        </is>
-      </c>
+          <t>James Pierce</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -16671,7 +16667,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>st_jamess_park</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -16695,11 +16691,7 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>Thomas Pepys; partner of Thomas Pepys</t>
-        </is>
-      </c>
+      <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
     </row>
     <row r="443">
@@ -16715,7 +16707,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>moorfields</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -16741,7 +16733,7 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>"we three went into London together"</t>
+          <t>"before dinner we went and took a walk round the park"</t>
         </is>
       </c>
     </row>
@@ -16753,12 +16745,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>moorfields</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>st_pauls_churchyard</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -16777,12 +16769,12 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>"Here I took leave of them, and so to Paul's"</t>
-        </is>
-      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Thomas Pepys; partner of Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -16792,12 +16784,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>st_pauls_churchyard</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>turner_house</t>
+          <t>moorfields</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -16816,8 +16808,16 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Thomas Pepys; partner of Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>"we three went into London together"</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16827,12 +16827,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>turner_house</t>
+          <t>moorfields</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>st_pauls_churchyard</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -16851,12 +16851,12 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>"Here I took leave of them, and so to Paul's"</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -16866,12 +16866,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>st_pauls_churchyard</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>turner_house</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -16890,11 +16890,7 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
+      <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -16905,12 +16901,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>turner_house</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -16922,14 +16918,18 @@
         <v>2</v>
       </c>
       <c r="F448" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I448" t="inlineStr"/>
     </row>
     <row r="449">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -16957,14 +16957,18 @@
         <v>2</v>
       </c>
       <c r="F449" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I449" t="inlineStr"/>
     </row>
     <row r="450">
@@ -16980,7 +16984,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -17000,11 +17004,7 @@
         </is>
       </c>
       <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>"in the way met with Catan on foot in the street" - no node, met in passing</t>
-        </is>
-      </c>
+      <c r="I450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>playfords_shop</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -17073,12 +17073,12 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
-      <c r="I452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>"in the way met with Catan on foot in the street" - no node, met in passing</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>playfords_shop</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -17112,27 +17112,23 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
+      <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>100453</t>
+          <t>100454</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>cumberland_lodgings</t>
+          <t>john_playford_shop</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -17151,18 +17147,22 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>100454</t>
+          <t>100455</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>cumberland_lodgings</t>
+          <t>john_playford_shop</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -17186,17 +17186,17 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>"I returned"</t>
-        </is>
-      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>100455</t>
+          <t>100456</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>valentine_fage_house</t>
+          <t>richard_cumberland_lodgings</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -17226,21 +17226,17 @@
         </is>
       </c>
       <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>"I went to Mr. Fage from my father's" - stated at the end of the entry, placed here on the sequence it describes</t>
-        </is>
-      </c>
+      <c r="I456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>100456</t>
+          <t>100457</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>valentine_fage_house</t>
+          <t>richard_cumberland_lodgings</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -17265,12 +17261,16 @@
         </is>
       </c>
       <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>"I returned"</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>100458</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>valentine_fage_house</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -17299,27 +17299,27 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>"I went to Mr. Fage from my father's" - stated at the end of the entry, placed here on the sequence it describes</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>100458</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>valentine_fage_house</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -17331,34 +17331,30 @@
         <v>2</v>
       </c>
       <c r="F459" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>Mr Moore</t>
-        </is>
-      </c>
+      <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100460</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>swan_inn</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -17370,7 +17366,7 @@
         <v>2</v>
       </c>
       <c r="F460" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -17379,7 +17375,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Mr Moore</t>
+          <t>Elizabeth Pepys</t>
         </is>
       </c>
       <c r="I460" t="inlineStr"/>
@@ -17387,17 +17383,17 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>100460</t>
+          <t>100461</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>swan_inn</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -17416,23 +17412,27 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Henry Moore</t>
+        </is>
+      </c>
       <c r="I461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>100461</t>
+          <t>100462</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>swan_inn</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Mr Hill</t>
+          <t>Henry Moore</t>
         </is>
       </c>
       <c r="I462" t="inlineStr"/>
@@ -17461,17 +17461,17 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>100462</t>
+          <t>100463</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>swan_inn</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -17496,17 +17496,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>100463</t>
+          <t>100464</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -17525,23 +17525,31 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Mr Hill</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Mr Hill of Worcestershire, presumably a client of Pepys</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>100464</t>
+          <t>100465</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -17566,17 +17574,17 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>100465</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -17601,17 +17609,17 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>100467</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -17636,17 +17644,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>100467</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -17671,17 +17679,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100469</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -17706,17 +17714,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>100469</t>
+          <t>100470</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -17728,34 +17736,30 @@
         <v>2</v>
       </c>
       <c r="F470" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>Captain Holland; Captain Cuttance</t>
-        </is>
-      </c>
+      <c r="H470" t="inlineStr"/>
       <c r="I470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>100471</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -17767,7 +17771,7 @@
         <v>2</v>
       </c>
       <c r="F471" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -17780,17 +17784,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>100471</t>
+          <t>100472</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -17811,7 +17815,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Mr Hill</t>
+          <t>Captain Philip Holland; Captain Roger Cuttance</t>
         </is>
       </c>
       <c r="I472" t="inlineStr"/>
@@ -17819,17 +17823,17 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>100472</t>
+          <t>100473</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -17854,17 +17858,17 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>100473</t>
+          <t>100474</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>hering_house</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -17883,23 +17887,27 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Mr Hill</t>
+        </is>
+      </c>
       <c r="I474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>100474</t>
+          <t>100475</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>hering_house</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>st_pauls_churchyard</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -17924,17 +17932,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>100475</t>
+          <t>100476</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>st_pauls_churchyard</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -17959,17 +17967,17 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>100476</t>
+          <t>100477</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>st_pauls_churchyard</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -17989,26 +17997,22 @@
         </is>
       </c>
       <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr">
-        <is>
-          <t>"my Lady Wright's"</t>
-        </is>
-      </c>
+      <c r="I477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>100477</t>
+          <t>100478</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>anne_wright_house</t>
+          <t>st_pauls_churchyard</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -18033,17 +18037,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -18063,10 +18067,84 @@
         </is>
       </c>
       <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>"my Lady Wright's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>100480</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>2</v>
+      </c>
+      <c r="F480" t="n">
+        <v>15</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>100481</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>2</v>
+      </c>
+      <c r="F481" t="n">
+        <v>15</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I479"/>
+  <autoFilter ref="A1:I481"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10258,7 +10258,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>peter_gunning_church</t>
+          <t>exeter_house_chapel</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>peter_gunning_church</t>
+          <t>exeter_house_chapel</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>downings_counsellor_chamber</t>
+          <t>stephens_chamber_temple</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>downings_counsellor_chamber</t>
+          <t>stephens_chamber_temple</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>chequers_inn</t>
+          <t>exchequer_tavern_charing_cross</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>chequers_inn</t>
+          <t>exchequer_tavern_charing_cross</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">

--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="edges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$481</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$597</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I481"/>
+  <dimension ref="A1:I597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18143,8 +18143,4524 @@
       <c r="H481" t="inlineStr"/>
       <c r="I481" t="inlineStr"/>
     </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>100483</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>2</v>
+      </c>
+      <c r="F482" t="n">
+        <v>16</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>100484</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>2</v>
+      </c>
+      <c r="F483" t="n">
+        <v>16</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>"sealed my letter at Will's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>100485</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>the_sun_tavern</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>2</v>
+      </c>
+      <c r="F484" t="n">
+        <v>16</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Nicholas Osborne; Mr Shaw; Mr Spicer</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>"we went to the Sun Tavern in expectation of a dinner" - taken to be the_sun_tavern, Chancery Lane, the only Sun in the node list. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>100486</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>the_sun_tavern</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>2</v>
+      </c>
+      <c r="F485" t="n">
+        <v>16</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>100487</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>2</v>
+      </c>
+      <c r="F486" t="n">
+        <v>17</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>100488</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>2</v>
+      </c>
+      <c r="F487" t="n">
+        <v>17</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>John Hawly</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>"brought Mr. Hawly home with me to dinner"</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>100489</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>2</v>
+      </c>
+      <c r="F488" t="n">
+        <v>17</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>"went to Mr. Gunning's to his weekly fast"</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>100490</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>st_james_park</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>2</v>
+      </c>
+      <c r="F489" t="n">
+        <v>17</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>"we went and walked in the park till it was dark"</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>100491</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>st_james_park</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>jacobs_alehouse</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>2</v>
+      </c>
+      <c r="F490" t="n">
+        <v>17</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>100492</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>jacobs_alehouse</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>2</v>
+      </c>
+      <c r="F491" t="n">
+        <v>17</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>100493</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>2</v>
+      </c>
+      <c r="F492" t="n">
+        <v>17</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>100494</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>2</v>
+      </c>
+      <c r="F493" t="n">
+        <v>17</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>100495</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>2</v>
+      </c>
+      <c r="F494" t="n">
+        <v>17</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>100496</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>2</v>
+      </c>
+      <c r="F495" t="n">
+        <v>18</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>100497</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>2</v>
+      </c>
+      <c r="F496" t="n">
+        <v>18</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>100498</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>2</v>
+      </c>
+      <c r="F497" t="n">
+        <v>18</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>100499</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>2</v>
+      </c>
+      <c r="F498" t="n">
+        <v>18</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>"went to my Lord's lodgings to my turret there and took away most of my books"</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>100500</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>the_half_moon_alehouse</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>2</v>
+      </c>
+      <c r="F499" t="n">
+        <v>18</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Captain Holland; Mr Southorne</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>100501</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>the_half_moon_alehouse</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>mitre_tavern</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>2</v>
+      </c>
+      <c r="F500" t="n">
+        <v>18</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Captain Holland; Mr Southorne</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>100502</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>mitre_tavern</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>wotton_shop</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>2</v>
+      </c>
+      <c r="F501" t="n">
+        <v>18</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>100503</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>wotton_shop</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_6</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>2</v>
+      </c>
+      <c r="F502" t="n">
+        <v>18</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Mr Wotton</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>100504</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_6</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>clerks_room_whitehall</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>2</v>
+      </c>
+      <c r="F503" t="n">
+        <v>18</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>"to Whitehall, where I met with Luellin and in the clerk's chamber wrote a letter to my Lord"</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>100505</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>clerks_room_whitehall</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>2</v>
+      </c>
+      <c r="F504" t="n">
+        <v>18</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>100506</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>2</v>
+      </c>
+      <c r="F505" t="n">
+        <v>19</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>"to drink a draft of purle"</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>100507</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>2</v>
+      </c>
+      <c r="F506" t="n">
+        <v>19</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>intended St Bartholomew's, "but it raining very hard we went to Mr. Gunning's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>100508</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>2</v>
+      </c>
+      <c r="F507" t="n">
+        <v>19</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Henry Moore</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>"went home with him to dinner" - Moore's dinner taken to be at Mr Crew's, where the secluded members came in to Mr Crew after it</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>100509</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>2</v>
+      </c>
+      <c r="F508" t="n">
+        <v>19</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>100510</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>robert_mossum_church</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>2</v>
+      </c>
+      <c r="F509" t="n">
+        <v>19</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>"brought my wife to Mr. Mossum's to hear him"</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>100511</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>robert_mossum_church</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>2</v>
+      </c>
+      <c r="F510" t="n">
+        <v>19</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>100512</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>2</v>
+      </c>
+      <c r="F511" t="n">
+        <v>19</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>100513</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>2</v>
+      </c>
+      <c r="F512" t="n">
+        <v>19</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>100514</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>2</v>
+      </c>
+      <c r="F513" t="n">
+        <v>19</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>100515</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>2</v>
+      </c>
+      <c r="F514" t="n">
+        <v>20</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>100516</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>2</v>
+      </c>
+      <c r="F515" t="n">
+        <v>20</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Pepys's office partner</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>"Took him home to dinner with me"</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>100517</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>2</v>
+      </c>
+      <c r="F516" t="n">
+        <v>20</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>John Pepys the younger</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>"I took him to my study at home and at my Lord's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>100518</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>2</v>
+      </c>
+      <c r="F517" t="n">
+        <v>20</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>100519</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>2</v>
+      </c>
+      <c r="F518" t="n">
+        <v>20</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>James Chetwind; William Simons; Mr Gregory</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>100520</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>turks_head_coffee_house</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>2</v>
+      </c>
+      <c r="F519" t="n">
+        <v>20</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>William Simons</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>"Simons and I to the Coffee Club" - the Rota Club met at the Turk's Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>100521</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>turks_head_coffee_house</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>2</v>
+      </c>
+      <c r="F520" t="n">
+        <v>20</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Dick Vines</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>100522</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>2</v>
+      </c>
+      <c r="F521" t="n">
+        <v>20</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>100523</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>2</v>
+      </c>
+      <c r="F522" t="n">
+        <v>21</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>100524</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>2</v>
+      </c>
+      <c r="F523" t="n">
+        <v>21</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>"Mr. Crew saw me, and bid me come to his house"</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>100525</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>2</v>
+      </c>
+      <c r="F524" t="n">
+        <v>21</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>John Crew</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>"I back to Westminster Hall with him in his coach"</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>100526</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>turks_head_coffee_house</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>2</v>
+      </c>
+      <c r="F525" t="n">
+        <v>21</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Mr Lock; Henry Purcell</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>"to the Coffee House, into a room next the water"</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>100527</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>turks_head_coffee_house</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>2</v>
+      </c>
+      <c r="F526" t="n">
+        <v>21</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>100528</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>2</v>
+      </c>
+      <c r="F527" t="n">
+        <v>22</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>intended Mr Crew's, "but it raining I forbore"</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>100529</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>2</v>
+      </c>
+      <c r="F528" t="n">
+        <v>22</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>100530</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>2</v>
+      </c>
+      <c r="F529" t="n">
+        <v>22</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>100531</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>2</v>
+      </c>
+      <c r="F530" t="n">
+        <v>22</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>100532</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>2</v>
+      </c>
+      <c r="F531" t="n">
+        <v>22</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>100533</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>2</v>
+      </c>
+      <c r="F532" t="n">
+        <v>22</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>100534</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>2</v>
+      </c>
+      <c r="F533" t="n">
+        <v>22</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>100535</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>2</v>
+      </c>
+      <c r="F534" t="n">
+        <v>22</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>"so to Mrs. Jemimah, who now hath her instrument about her neck"</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>100536</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>2</v>
+      </c>
+      <c r="F535" t="n">
+        <v>22</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>100537</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>2</v>
+      </c>
+      <c r="F536" t="n">
+        <v>22</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>100538</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>2</v>
+      </c>
+      <c r="F537" t="n">
+        <v>22</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>"Home for my lanthorn"</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>100539</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>2</v>
+      </c>
+      <c r="F538" t="n">
+        <v>22</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>100540</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>2</v>
+      </c>
+      <c r="F539" t="n">
+        <v>22</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>"At past 9 o'clock my wife and I went home"</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>100541</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>2</v>
+      </c>
+      <c r="F540" t="n">
+        <v>23</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>100542</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_7</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>2</v>
+      </c>
+      <c r="F541" t="n">
+        <v>23</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Mr Fuller; Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>"thence I took them to drink"</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>100543</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_7</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>2</v>
+      </c>
+      <c r="F542" t="n">
+        <v>23</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Mr Fuller</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>"so put off my uncle. So with Mr. Fuller home to my house"</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>100544</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>scotland_yard_stable</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>2</v>
+      </c>
+      <c r="F543" t="n">
+        <v>23</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>"I was to see my horse which Mr. Garthwayt lends me to-morrow"</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>100545</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>scotland_yard_stable</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>2</v>
+      </c>
+      <c r="F544" t="n">
+        <v>23</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>100546</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>2</v>
+      </c>
+      <c r="F545" t="n">
+        <v>23</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>100547</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>2</v>
+      </c>
+      <c r="F546" t="n">
+        <v>23</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>John Crew; Mr Anslow</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>"He brought me in the coach home"</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>100548</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>2</v>
+      </c>
+      <c r="F547" t="n">
+        <v>23</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>"I back to the Hall"</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>100549</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>mrs_michells_shop</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>2</v>
+      </c>
+      <c r="F548" t="n">
+        <v>23</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>100550</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>mrs_michells_shop</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>2</v>
+      </c>
+      <c r="F549" t="n">
+        <v>23</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>100551</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>scotland_yard_stable</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>2</v>
+      </c>
+      <c r="F550" t="n">
+        <v>24</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>100552</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>scotland_yard_stable</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>james_pearse_house</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>2</v>
+      </c>
+      <c r="F551" t="n">
+        <v>24</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>"taking horse at Scotland Yard ... I rode to Mr. Pierces"</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>100553</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>james_pearse_house</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>ware</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>2</v>
+      </c>
+      <c r="F552" t="n">
+        <v>24</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>James Pierce</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>"the day and the way very foul"</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>100554</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>ware</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>puckeridge</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>2</v>
+      </c>
+      <c r="F553" t="n">
+        <v>24</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>James Pierce; Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>"About Ware we overtook Mr. Blayton ... who went thenceforwards with us"</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>100555</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>puckeridge</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>chequer_inn_foulmere</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>2</v>
+      </c>
+      <c r="F554" t="n">
+        <v>24</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>James Pierce; Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>"my mare being almost tired"; Pepys lodged here overnight</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>100556</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>chequer_inn_foulmere</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>2</v>
+      </c>
+      <c r="F555" t="n">
+        <v>25</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>"we two come to Cambridge by eight o'clock in the morning" - described at the end of the 24 February entry, dated here to the morning it happened. Mr Pierce left the party at Foulmere for Hinchingbrooke</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>100557</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>christs_college_cambridge</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>2</v>
+      </c>
+      <c r="F556" t="n">
+        <v>25</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>John Pepys; John Pepys the younger</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>"to Mr. Widdririgton, at Christ's College ... caused my brother to be admitted"</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>100558</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>christs_college_cambridge</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>2</v>
+      </c>
+      <c r="F557" t="n">
+        <v>25</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>100559</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>2</v>
+      </c>
+      <c r="F558" t="n">
+        <v>25</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>"to my Inn again, where I dined ... at an ordinary"</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>100560</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>angier_house_cambridge</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>2</v>
+      </c>
+      <c r="F559" t="n">
+        <v>25</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>John Pepys</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>100561</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>angier_house_cambridge</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>mertons_shop_cambridge</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>2</v>
+      </c>
+      <c r="F560" t="n">
+        <v>25</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>100562</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>mertons_shop_cambridge</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>three_tuns_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>2</v>
+      </c>
+      <c r="F561" t="n">
+        <v>25</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Mr Fairbrother; Cousin Angier; Mr Zanchy</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>100563</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>three_tuns_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>2</v>
+      </c>
+      <c r="F562" t="n">
+        <v>25</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Mr Zanchy</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>"a very handsome supper at Mr. Hill's chambers"</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>100564</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>2</v>
+      </c>
+      <c r="F563" t="n">
+        <v>25</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>100565</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>kings_college_cambridge</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>2</v>
+      </c>
+      <c r="F564" t="n">
+        <v>26</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>John Pepys</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>"walked out in the fields behind King's College, and in King's College Chapel Yard"</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>100566</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>kings_college_cambridge</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>st_botolphs_church_cambridge</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>2</v>
+      </c>
+      <c r="F565" t="n">
+        <v>26</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>John Pepys; Mr Fairbrother</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>100567</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>st_botolphs_church_cambridge</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>christs_college_cambridge</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>2</v>
+      </c>
+      <c r="F566" t="n">
+        <v>26</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>John Pepys</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>"to Mr. Widdrington's chamber to dinner"</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>100568</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>christs_college_cambridge</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>2</v>
+      </c>
+      <c r="F567" t="n">
+        <v>26</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>John Pepys</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>"Mr. Pierces man came to tell me that his master was come to town"</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>100569</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>2</v>
+      </c>
+      <c r="F568" t="n">
+        <v>26</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>"to get the certificate of the College for my brother's entrance"</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>100570</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>magdalene_college_cambridge</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>rose_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>2</v>
+      </c>
+      <c r="F569" t="n">
+        <v>26</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Mr Zanchy</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>100571</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>rose_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>2</v>
+      </c>
+      <c r="F570" t="n">
+        <v>26</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Mr Zanchy</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>100572</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>rose_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>2</v>
+      </c>
+      <c r="F571" t="n">
+        <v>26</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Mr Zanchy; John Pepys; James Pierce; Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>"not telling them that we had been there before"</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>100573</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>rose_tavern_cambridge</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>angier_house_cambridge</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>2</v>
+      </c>
+      <c r="F572" t="n">
+        <v>26</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>John Pepys; Mr Zanchy</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>100574</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>angier_house_cambridge</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>2</v>
+      </c>
+      <c r="F573" t="n">
+        <v>26</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>100575</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>falcon_inn_cambridge</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>white_hart_saffron_walden</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>2</v>
+      </c>
+      <c r="F574" t="n">
+        <v>27</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>"Up by four o'clock ... took my leave of my father"</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>100576</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>white_hart_saffron_walden</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>audley_end_house</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>2</v>
+      </c>
+      <c r="F575" t="n">
+        <v>27</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Mr Blayton; master of the White Hart</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>"took the master of the house to shew us Audley End House, who took us on foot through the park"</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>100577</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>audley_end_house</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>almshouse_saffron_walden</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>2</v>
+      </c>
+      <c r="F576" t="n">
+        <v>27</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Mr Blayton; master of the White Hart</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>"In our going, my landlord carried us through a very old hospital or almshouse"</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>100578</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>almshouse_saffron_walden</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>white_hart_saffron_walden</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>2</v>
+      </c>
+      <c r="F577" t="n">
+        <v>27</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Mr Blayton; master of the White Hart</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>100579</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>white_hart_saffron_walden</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>inn_epping</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>2</v>
+      </c>
+      <c r="F578" t="n">
+        <v>27</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>"the road pretty good, but the weather rainy"</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>100580</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>inn_epping</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>royal_exchange</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>2</v>
+      </c>
+      <c r="F579" t="n">
+        <v>28</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>"for London through the forest"; "the militia of the red regiment in arms at the Old Exchange" - the Old Exchange is the Royal Exchange, as against the New Exchange in the Strand</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>100581</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>royal_exchange</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>st_pauls_cathedral</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>2</v>
+      </c>
+      <c r="F580" t="n">
+        <v>28</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Mr Blayton</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>"At Paul's I light, Mr. Blayton holding my horse"</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>100582</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>st_pauls_cathedral</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>2</v>
+      </c>
+      <c r="F581" t="n">
+        <v>28</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>100583</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>2</v>
+      </c>
+      <c r="F582" t="n">
+        <v>28</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>"Shifted myself"</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>100584</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>2</v>
+      </c>
+      <c r="F583" t="n">
+        <v>28</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>"where I found my Lord at dinner"</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>100585</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>2</v>
+      </c>
+      <c r="F584" t="n">
+        <v>28</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Will Howe</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>"calling in my way and saw my mother"</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>100586</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>plough_fleet_street</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>2</v>
+      </c>
+      <c r="F585" t="n">
+        <v>28</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Will Howe</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>"to buy a hat ... at the Plough in Fleet Street by my Lord's direction"</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>100587</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>plough_fleet_street</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>greyhound_tavern</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>2</v>
+      </c>
+      <c r="F586" t="n">
+        <v>28</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Will Howe; James Pierce</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>100588</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>greyhound_tavern</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>2</v>
+      </c>
+      <c r="F587" t="n">
+        <v>28</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>"he to Mr. Crew's and I to Mrs. Jem"</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>100589</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>2</v>
+      </c>
+      <c r="F588" t="n">
+        <v>28</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>100590</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>2</v>
+      </c>
+      <c r="F589" t="n">
+        <v>29</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>100591</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>2</v>
+      </c>
+      <c r="F590" t="n">
+        <v>29</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Henry Moore</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>100592</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>2</v>
+      </c>
+      <c r="F591" t="n">
+        <v>29</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>100593</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>city_of_london</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>2</v>
+      </c>
+      <c r="F592" t="n">
+        <v>29</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>"my wife and I by water to London" - landing place not named</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>100594</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>city_of_london</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>michael_hering_house</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>2</v>
+      </c>
+      <c r="F593" t="n">
+        <v>29</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>"Herring's, the merchant in Coleman Street"</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>100595</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>michael_hering_house</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>2</v>
+      </c>
+      <c r="F594" t="n">
+        <v>29</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>"So to my mother's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>100596</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>2</v>
+      </c>
+      <c r="F595" t="n">
+        <v>29</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>"of whom I took leave ... because she was to go out of town to-morrow"</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>100597</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>turner_house</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>2</v>
+      </c>
+      <c r="F596" t="n">
+        <v>29</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>"To my mother's and supped there"</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>100598</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>2</v>
+      </c>
+      <c r="F597" t="n">
+        <v>29</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I481"/>
+  <autoFilter ref="A1:I597"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -11426,11 +11426,7 @@
           <t>Gammer East; James the porter</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>"took Gammer East, and James the porter, a soldier, to my Lord's lodgings"</t>
-        </is>
-      </c>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11679,11 +11675,7 @@
           <t>Thomas Doling; Peter Llewellyn</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>Luellin met on the way</t>
-        </is>
-      </c>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11809,7 +11801,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>100482</t>
+          <t>100314</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -11848,7 +11840,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>100314</t>
+          <t>100315</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -11882,16 +11874,12 @@
           <t>Thomas Doling</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>"over against Somerset House, hearing the noise of guns, we landed"</t>
-        </is>
-      </c>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>100315</t>
+          <t>100316</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -11930,7 +11918,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>100316</t>
+          <t>100317</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -11960,16 +11948,12 @@
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>"went home on foot"</t>
-        </is>
-      </c>
+      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>100317</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12004,7 +11988,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>100319</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -12039,7 +12023,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>100319</t>
+          <t>100320</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -12074,7 +12058,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>100320</t>
+          <t>100321</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -12109,7 +12093,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>100321</t>
+          <t>100322</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -12144,7 +12128,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>100323</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -12179,7 +12163,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>100323</t>
+          <t>100324</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -12213,11 +12197,7 @@
           <t>Jane Turner; Joyce Norton</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>"shewed them the manner of the Houses sitting"</t>
-        </is>
-      </c>
+      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12408,11 +12388,7 @@
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>"went to hear news"</t>
-        </is>
-      </c>
+      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12447,11 +12423,7 @@
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>"I returned"</t>
-        </is>
-      </c>
+      <c r="I331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12529,11 +12501,7 @@
           <t>Elizabeth Pepys; Jane Turner; Joyce Norton; Theophila Turner</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>"I set them as far as Charing Cross, and there left them and my wife"</t>
-        </is>
-      </c>
+      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12794,11 +12762,7 @@
           <t>William Swan</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>"took him out by water to the Counsellor at the Temple"</t>
-        </is>
-      </c>
+      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12919,11 +12883,7 @@
           <t>William Swan</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>"leaving Swan at his master's, my Lord Widdrington"</t>
-        </is>
-      </c>
+      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12958,11 +12918,7 @@
         </is>
       </c>
       <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>"I met with Spicer, Washington, and D. Vines in Lincoln's Inn Court"</t>
-        </is>
-      </c>
+      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12997,11 +12953,7 @@
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>"to Mrs. Crew's"</t>
-        </is>
-      </c>
+      <c r="I345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -13036,11 +12988,7 @@
         </is>
       </c>
       <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>"Sir Harry Wright's"</t>
-        </is>
-      </c>
+      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -13223,11 +13171,7 @@
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>"I returned and called at the Chequers"</t>
-        </is>
-      </c>
+      <c r="I351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13301,11 +13245,7 @@
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>"To their church in the afternoon"</t>
-        </is>
-      </c>
+      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -13496,11 +13436,7 @@
           <t>John Andrews</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>"So back to Westminster and walked with him thither"</t>
-        </is>
-      </c>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13539,11 +13475,7 @@
           <t>John Andrews</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>"At the Hall we parted"</t>
-        </is>
-      </c>
+      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13726,11 +13658,7 @@
         </is>
       </c>
       <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>"I to Mrs. Ann"</t>
-        </is>
-      </c>
+      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13835,11 +13763,7 @@
         </is>
       </c>
       <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>"to give Mr. Hawly notice of my being forced to go into London"</t>
-        </is>
-      </c>
+      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13878,11 +13802,7 @@
           <t>John Hawly</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>"he and I walked as far as the Temple"</t>
-        </is>
-      </c>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13952,11 +13872,7 @@
         </is>
       </c>
       <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>"it being too soon, went and drank my morning draft with my cozen Tom Pepys the turner, and saw his house and shop"</t>
-        </is>
-      </c>
+      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13991,11 +13907,7 @@
         </is>
       </c>
       <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>"thence to school"</t>
-        </is>
-      </c>
+      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -14030,11 +13942,7 @@
         </is>
       </c>
       <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>"I went straight home and dined"</t>
-        </is>
-      </c>
+      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -14178,11 +14086,7 @@
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>"Thence back on foot home"</t>
-        </is>
-      </c>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14252,11 +14156,7 @@
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>"calling upon Mrs. Ann"</t>
-        </is>
-      </c>
+      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -14330,11 +14230,7 @@
           <t>Thomas Fossan</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>"the Swan in the Palace yard"</t>
-        </is>
-      </c>
+      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14408,11 +14304,7 @@
           <t>Charles Carter; Captain Robert Lidcott</t>
         </is>
       </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>"in the way I met with Captain Lidcott"</t>
-        </is>
-      </c>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14482,11 +14374,7 @@
         </is>
       </c>
       <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>"I returned to Mr. Carter"</t>
-        </is>
-      </c>
+      <c r="I384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -14603,11 +14491,7 @@
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>"in my way delivering a letter ... to Sir N. Wheeler"</t>
-        </is>
-      </c>
+      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14677,11 +14561,7 @@
         </is>
       </c>
       <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr">
-        <is>
-          <t>"I called in my way upon Mrs. Jem"</t>
-        </is>
-      </c>
+      <c r="I389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14786,11 +14666,7 @@
         </is>
       </c>
       <c r="H392" t="inlineStr"/>
-      <c r="I392" t="inlineStr">
-        <is>
-          <t>"in Fleet Street, received a great jostle"</t>
-        </is>
-      </c>
+      <c r="I392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -15004,11 +14880,7 @@
         </is>
       </c>
       <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>"I went to my office ... after I had been at the Upper Bench"</t>
-        </is>
-      </c>
+      <c r="I398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -15078,11 +14950,7 @@
         </is>
       </c>
       <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr">
-        <is>
-          <t>"her Aunt Wright's, but she was gone, so I went thither"</t>
-        </is>
-      </c>
+      <c r="I400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -15156,11 +15024,7 @@
           <t>James Pierce</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>"Mr. Pierce the surgeon, who would needs take me home"</t>
-        </is>
-      </c>
+      <c r="I402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -15269,11 +15133,7 @@
           <t>William Swan</t>
         </is>
       </c>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>"by water to the Temple to our Counsel"</t>
-        </is>
-      </c>
+      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -15386,11 +15246,7 @@
         </is>
       </c>
       <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>"so by coach home. I called at Mr. Harper's"</t>
-        </is>
-      </c>
+      <c r="I408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -15756,11 +15612,7 @@
           <t>Henry Moore</t>
         </is>
       </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>"with him went into London to Mr. Fage"</t>
-        </is>
-      </c>
+      <c r="I418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -15974,11 +15826,7 @@
         </is>
       </c>
       <c r="H424" t="inlineStr"/>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>"I went then down into the Hall"</t>
-        </is>
-      </c>
+      <c r="I424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -16017,11 +15865,7 @@
           <t>James Chetwind</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr">
-        <is>
-          <t>"calling at two or three shops, but could have no dinner"</t>
-        </is>
-      </c>
+      <c r="I425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -16216,11 +16060,7 @@
           <t>James Chetwind; friend of Mr Chetwind</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>"not liking the wine we went to an alehouse"</t>
-        </is>
-      </c>
+      <c r="I430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -16255,11 +16095,7 @@
         </is>
       </c>
       <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>"I went alone"</t>
-        </is>
-      </c>
+      <c r="I431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -16415,11 +16251,7 @@
           <t>Matthew Lock; James Chetwind</t>
         </is>
       </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>"a merchant's house hard by"</t>
-        </is>
-      </c>
+      <c r="I435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -16497,11 +16329,7 @@
           <t>James Chetwind</t>
         </is>
       </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>"we came to the Chequers at Charing Cross"</t>
-        </is>
-      </c>
+      <c r="I437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -16731,11 +16559,7 @@
           <t>Thomas Pepys; partner of Thomas Pepys</t>
         </is>
       </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>"before dinner we went and took a walk round the park"</t>
-        </is>
-      </c>
+      <c r="I443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -16813,11 +16637,7 @@
           <t>Thomas Pepys; partner of Thomas Pepys</t>
         </is>
       </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>"we three went into London together"</t>
-        </is>
-      </c>
+      <c r="I445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16852,11 +16672,7 @@
         </is>
       </c>
       <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>"Here I took leave of them, and so to Paul's"</t>
-        </is>
-      </c>
+      <c r="I446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -17118,7 +16934,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>100454</t>
+          <t>100453</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -17157,7 +16973,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>100455</t>
+          <t>100454</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -17196,7 +17012,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>100456</t>
+          <t>100455</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -17231,7 +17047,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>100456</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -17261,16 +17077,12 @@
         </is>
       </c>
       <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>"I returned"</t>
-        </is>
-      </c>
+      <c r="I457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>100458</t>
+          <t>100457</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -17300,16 +17112,12 @@
         </is>
       </c>
       <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>"I went to Mr. Fage from my father's" - stated at the end of the entry, placed here on the sequence it describes</t>
-        </is>
-      </c>
+      <c r="I458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100458</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -17344,7 +17152,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>100460</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -17383,7 +17191,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>100461</t>
+          <t>100460</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -17422,7 +17230,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>100462</t>
+          <t>100461</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -17461,7 +17269,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>100463</t>
+          <t>100462</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -17496,7 +17304,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>100464</t>
+          <t>100463</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -17539,7 +17347,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>100465</t>
+          <t>100464</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -17574,7 +17382,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>100465</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -17609,7 +17417,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>100467</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -17644,7 +17452,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100467</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -17679,7 +17487,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>100469</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -17714,7 +17522,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>100469</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -17749,7 +17557,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>100471</t>
+          <t>100470</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -17784,7 +17592,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>100472</t>
+          <t>100471</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -17823,7 +17631,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>100473</t>
+          <t>100472</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -17858,7 +17666,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>100474</t>
+          <t>100473</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -17897,7 +17705,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>100475</t>
+          <t>100474</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -17932,7 +17740,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>100476</t>
+          <t>100475</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -17967,7 +17775,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>100477</t>
+          <t>100476</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -18002,7 +17810,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>100477</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -18037,7 +17845,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>100479</t>
+          <t>100478</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -18067,16 +17875,12 @@
         </is>
       </c>
       <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr">
-        <is>
-          <t>"my Lady Wright's"</t>
-        </is>
-      </c>
+      <c r="I479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>100480</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -18111,7 +17915,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>100481</t>
+          <t>100480</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -18146,7 +17950,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>100483</t>
+          <t>100481</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -18181,7 +17985,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>100482</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -18211,16 +18015,12 @@
         </is>
       </c>
       <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr">
-        <is>
-          <t>"sealed my letter at Will's"</t>
-        </is>
-      </c>
+      <c r="I483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>100485</t>
+          <t>100483</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -18230,7 +18030,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>the_sun_tavern</t>
+          <t>sun_tavern_king_street</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -18251,24 +18051,24 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Nicholas Osborne; Mr Shaw; Mr Spicer</t>
+          <t>Nicholas Osborne; Robin Shaw; Jack Spicer</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>"we went to the Sun Tavern in expectation of a dinner" - taken to be the_sun_tavern, Chancery Lane, the only Sun in the node list. FLAG</t>
+          <t>"we went to the Sun Tavern in expectation of a dinner"</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>100486</t>
+          <t>100484</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>the_sun_tavern</t>
+          <t>sun_tavern_king_street</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -18293,12 +18093,16 @@
         </is>
       </c>
       <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>"we went to the Sun Tavern in expectation of a dinner"</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>100485</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -18333,7 +18137,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>100488</t>
+          <t>100486</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -18367,16 +18171,12 @@
           <t>John Hawly</t>
         </is>
       </c>
-      <c r="I487" t="inlineStr">
-        <is>
-          <t>"brought Mr. Hawly home with me to dinner"</t>
-        </is>
-      </c>
+      <c r="I487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>100489</t>
+          <t>100487</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -18406,16 +18206,12 @@
         </is>
       </c>
       <c r="H488" t="inlineStr"/>
-      <c r="I488" t="inlineStr">
-        <is>
-          <t>"went to Mr. Gunning's to his weekly fast"</t>
-        </is>
-      </c>
+      <c r="I488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>100490</t>
+          <t>100488</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -18425,7 +18221,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>st_james_park</t>
+          <t>park_unknown_1</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -18458,12 +18254,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>100491</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>st_james_park</t>
+          <t>park_unknown_1</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -18492,12 +18288,16 @@
           <t>Mr Butler</t>
         </is>
       </c>
-      <c r="I490" t="inlineStr"/>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>"we went and walked in the park till it was dark"</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>100492</t>
+          <t>100490</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -18536,7 +18336,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>100493</t>
+          <t>100491</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -18575,7 +18375,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>100494</t>
+          <t>100492</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -18614,7 +18414,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>100495</t>
+          <t>100493</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -18649,7 +18449,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>100494</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -18684,7 +18484,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>100497</t>
+          <t>100495</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -18719,7 +18519,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>100498</t>
+          <t>100496</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -18754,7 +18554,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>100499</t>
+          <t>100497</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -18784,16 +18584,12 @@
         </is>
       </c>
       <c r="H498" t="inlineStr"/>
-      <c r="I498" t="inlineStr">
-        <is>
-          <t>"went to my Lord's lodgings to my turret there and took away most of my books"</t>
-        </is>
-      </c>
+      <c r="I498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>100500</t>
+          <t>100498</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -18824,7 +18620,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Captain Holland; Mr Southorne</t>
+          <t>Captain Philip Holland; James Southorne</t>
         </is>
       </c>
       <c r="I499" t="inlineStr"/>
@@ -18832,7 +18628,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>100501</t>
+          <t>100499</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -18863,7 +18659,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Captain Holland; Mr Southorne</t>
+          <t>Captain Philip Holland; James Southorne</t>
         </is>
       </c>
       <c r="I500" t="inlineStr"/>
@@ -18871,7 +18667,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>100502</t>
+          <t>100500</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -18881,7 +18677,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>wotton_shop</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -18906,12 +18702,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>100503</t>
+          <t>100501</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>wotton_shop</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -18937,7 +18733,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Mr Wotton</t>
+          <t>William Wotton</t>
         </is>
       </c>
       <c r="I502" t="inlineStr"/>
@@ -18945,7 +18741,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>100504</t>
+          <t>100502</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -18975,16 +18771,12 @@
         </is>
       </c>
       <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr">
-        <is>
-          <t>"to Whitehall, where I met with Luellin and in the clerk's chamber wrote a letter to my Lord"</t>
-        </is>
-      </c>
+      <c r="I503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>100505</t>
+          <t>100503</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19019,7 +18811,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>100506</t>
+          <t>100504</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -19049,16 +18841,12 @@
         </is>
       </c>
       <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr">
-        <is>
-          <t>"to drink a draft of purle"</t>
-        </is>
-      </c>
+      <c r="I505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>100505</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -19092,16 +18880,12 @@
           <t>Mr Butler</t>
         </is>
       </c>
-      <c r="I506" t="inlineStr">
-        <is>
-          <t>intended St Bartholomew's, "but it raining very hard we went to Mr. Gunning's"</t>
-        </is>
-      </c>
+      <c r="I506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>100508</t>
+          <t>100506</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -19144,7 +18928,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>100509</t>
+          <t>100507</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -19179,7 +18963,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>100508</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -19213,16 +18997,12 @@
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I509" t="inlineStr">
-        <is>
-          <t>"brought my wife to Mr. Mossum's to hear him"</t>
-        </is>
-      </c>
+      <c r="I509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>100511</t>
+          <t>100509</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -19261,7 +19041,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>100512</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -19290,13 +19070,17 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>100513</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -19325,13 +19109,17 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr"/>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>100514</t>
+          <t>100512</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -19370,7 +19158,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>100515</t>
+          <t>100513</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -19405,7 +19193,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>100516</t>
+          <t>100514</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -19439,16 +19227,12 @@
           <t>Pepys's office partner</t>
         </is>
       </c>
-      <c r="I515" t="inlineStr">
-        <is>
-          <t>"Took him home to dinner with me"</t>
-        </is>
-      </c>
+      <c r="I515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>100517</t>
+          <t>100515</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -19482,16 +19266,12 @@
           <t>John Pepys the younger</t>
         </is>
       </c>
-      <c r="I516" t="inlineStr">
-        <is>
-          <t>"I took him to my study at home and at my Lord's"</t>
-        </is>
-      </c>
+      <c r="I516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>100516</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -19526,7 +19306,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>100519</t>
+          <t>100517</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -19557,7 +19337,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>James Chetwind; William Simons; Mr Gregory</t>
+          <t>James Chetwind; William Simons; John Gregory</t>
         </is>
       </c>
       <c r="I518" t="inlineStr"/>
@@ -19565,7 +19345,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>100518</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -19608,7 +19388,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>100519</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -19647,7 +19427,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>100522</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -19682,7 +19462,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>100523</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -19717,7 +19497,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>100524</t>
+          <t>100522</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -19746,17 +19526,17 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr"/>
-      <c r="I523" t="inlineStr">
-        <is>
-          <t>"Mr. Crew saw me, and bid me come to his house"</t>
-        </is>
-      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>John Crew</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>100525</t>
+          <t>100523</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -19790,16 +19570,12 @@
           <t>John Crew</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>"I back to Westminster Hall with him in his coach"</t>
-        </is>
-      </c>
+      <c r="I524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>100526</t>
+          <t>100524</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -19830,19 +19606,15 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Mr Lock; Henry Purcell</t>
-        </is>
-      </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>"to the Coffee House, into a room next the water"</t>
-        </is>
-      </c>
+          <t>Matthew Locke; Henry Purcell</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>100527</t>
+          <t>100525</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -19877,7 +19649,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>100528</t>
+          <t>100526</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -19916,7 +19688,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>100529</t>
+          <t>100527</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -19951,7 +19723,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>100530</t>
+          <t>100528</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -19986,7 +19758,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>100531</t>
+          <t>100529</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -20021,7 +19793,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>100532</t>
+          <t>100530</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -20056,7 +19828,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>100533</t>
+          <t>100531</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -20091,7 +19863,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>100534</t>
+          <t>100532</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -20126,7 +19898,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>100535</t>
+          <t>100533</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -20156,16 +19928,12 @@
         </is>
       </c>
       <c r="H534" t="inlineStr"/>
-      <c r="I534" t="inlineStr">
-        <is>
-          <t>"so to Mrs. Jemimah, who now hath her instrument about her neck"</t>
-        </is>
-      </c>
+      <c r="I534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>100534</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -20200,7 +19968,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>100537</t>
+          <t>100535</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -20235,7 +20003,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>100538</t>
+          <t>100536</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -20265,16 +20033,12 @@
         </is>
       </c>
       <c r="H537" t="inlineStr"/>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>"Home for my lanthorn"</t>
-        </is>
-      </c>
+      <c r="I537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>100539</t>
+          <t>100537</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -20309,7 +20073,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>100540</t>
+          <t>100538</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -20343,16 +20107,12 @@
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I539" t="inlineStr">
-        <is>
-          <t>"At past 9 o'clock my wife and I went home"</t>
-        </is>
-      </c>
+      <c r="I539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>100539</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -20387,7 +20147,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>100542</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -20418,19 +20178,15 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Mr Fuller; Thomas Pepys</t>
-        </is>
-      </c>
-      <c r="I541" t="inlineStr">
-        <is>
-          <t>"thence I took them to drink"</t>
-        </is>
-      </c>
+          <t>William Fuller; Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>100543</t>
+          <t>100541</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -20461,19 +20217,15 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Mr Fuller</t>
-        </is>
-      </c>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>"so put off my uncle. So with Mr. Fuller home to my house"</t>
-        </is>
-      </c>
+          <t>William Fuller</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>100544</t>
+          <t>100542</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -20503,16 +20255,12 @@
         </is>
       </c>
       <c r="H543" t="inlineStr"/>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>"I was to see my horse which Mr. Garthwayt lends me to-morrow"</t>
-        </is>
-      </c>
+      <c r="I543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>100545</t>
+          <t>100543</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -20547,7 +20295,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>100546</t>
+          <t>100544</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -20582,7 +20330,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>100547</t>
+          <t>100545</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -20613,19 +20361,15 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>John Crew; Mr Anslow</t>
-        </is>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>"He brought me in the coach home"</t>
-        </is>
-      </c>
+          <t>John Crew; Arthur Annesley</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>100548</t>
+          <t>100546</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -20655,16 +20399,12 @@
         </is>
       </c>
       <c r="H547" t="inlineStr"/>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>"I back to the Hall"</t>
-        </is>
-      </c>
+      <c r="I547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>100549</t>
+          <t>100547</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -20674,7 +20414,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>mrs_michells_shop</t>
+          <t>anne_michell_shop</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -20699,12 +20439,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>100550</t>
+          <t>100548</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>mrs_michells_shop</t>
+          <t>anne_michell_shop</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -20734,7 +20474,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>100551</t>
+          <t>100549</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -20769,7 +20509,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>100552</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -20799,16 +20539,12 @@
         </is>
       </c>
       <c r="H551" t="inlineStr"/>
-      <c r="I551" t="inlineStr">
-        <is>
-          <t>"taking horse at Scotland Yard ... I rode to Mr. Pierces"</t>
-        </is>
-      </c>
+      <c r="I551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>100553</t>
+          <t>100551</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -20818,7 +20554,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>ware</t>
+          <t>ware_hertfordshire</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -20842,26 +20578,22 @@
           <t>James Pierce</t>
         </is>
       </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>"the day and the way very foul"</t>
-        </is>
-      </c>
+      <c r="I552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>100554</t>
+          <t>100552</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>ware</t>
+          <t>ware_hertfordshire</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>puckeridge</t>
+          <t>puckeridge_hertfordshire</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -20882,29 +20614,25 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>James Pierce; Mr Blayton</t>
-        </is>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>"About Ware we overtook Mr. Blayton ... who went thenceforwards with us"</t>
-        </is>
-      </c>
+          <t>James Pierce; Thomas Blayton</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>100555</t>
+          <t>100553</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>puckeridge</t>
+          <t>puckeridge_hertfordshire</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>chequer_inn_foulmere</t>
+          <t>chequer_inn_fowlmere</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -20928,21 +20656,17 @@
           <t>James Pierce; Mr Blayton</t>
         </is>
       </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>"my mare being almost tired"; Pepys lodged here overnight</t>
-        </is>
-      </c>
+      <c r="I554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>100554</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>chequer_inn_foulmere</t>
+          <t>chequer_inn_fowlmere</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -20968,7 +20692,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Mr Blayton</t>
+          <t>Thomas Blayton</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -20980,7 +20704,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>100557</t>
+          <t>100555</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -21014,16 +20738,12 @@
           <t>John Pepys; John Pepys the younger</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>"to Mr. Widdririgton, at Christ's College ... caused my brother to be admitted"</t>
-        </is>
-      </c>
+      <c r="I556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>100558</t>
+          <t>100556</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -21058,7 +20778,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>100559</t>
+          <t>100557</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -21088,16 +20808,12 @@
         </is>
       </c>
       <c r="H558" t="inlineStr"/>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>"to my Inn again, where I dined ... at an ordinary"</t>
-        </is>
-      </c>
+      <c r="I558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>100560</t>
+          <t>100558</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -21107,7 +20823,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>angier_house_cambridge</t>
+          <t>john_angier_house_cambridge</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -21136,12 +20852,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>100561</t>
+          <t>100559</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>angier_house_cambridge</t>
+          <t>john_angier_house_cambridge</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -21171,7 +20887,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>100560</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -21202,7 +20918,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Mr Fairbrother; Cousin Angier; Mr Zanchy</t>
+          <t>William Fairbrother; John Angier; Clement Sankey</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
@@ -21210,7 +20926,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>100563</t>
+          <t>100561</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -21241,19 +20957,15 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Mr Zanchy</t>
-        </is>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>"a very handsome supper at Mr. Hill's chambers"</t>
-        </is>
-      </c>
+          <t>Clement Sankey</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>100564</t>
+          <t>100562</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -21288,7 +21000,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>100563</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -21322,16 +21034,12 @@
           <t>John Pepys</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>"walked out in the fields behind King's College, and in King's College Chapel Yard"</t>
-        </is>
-      </c>
+      <c r="I564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>100566</t>
+          <t>100564</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -21362,7 +21070,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>John Pepys; Mr Fairbrother</t>
+          <t>John Pepys; William Fairbrother</t>
         </is>
       </c>
       <c r="I565" t="inlineStr"/>
@@ -21370,7 +21078,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>100567</t>
+          <t>100565</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -21404,16 +21112,12 @@
           <t>John Pepys</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr">
-        <is>
-          <t>"to Mr. Widdrington's chamber to dinner"</t>
-        </is>
-      </c>
+      <c r="I566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>100568</t>
+          <t>100566</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -21447,16 +21151,12 @@
           <t>John Pepys</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>"Mr. Pierces man came to tell me that his master was come to town"</t>
-        </is>
-      </c>
+      <c r="I567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>100569</t>
+          <t>100567</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -21486,16 +21186,12 @@
         </is>
       </c>
       <c r="H568" t="inlineStr"/>
-      <c r="I568" t="inlineStr">
-        <is>
-          <t>"to get the certificate of the College for my brother's entrance"</t>
-        </is>
-      </c>
+      <c r="I568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>100570</t>
+          <t>100568</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -21526,7 +21222,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Mr Zanchy</t>
+          <t>Clement Sankey</t>
         </is>
       </c>
       <c r="I569" t="inlineStr"/>
@@ -21534,7 +21230,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>100571</t>
+          <t>100569</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -21565,7 +21261,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Mr Zanchy</t>
+          <t>Clement Sankey</t>
         </is>
       </c>
       <c r="I570" t="inlineStr"/>
@@ -21573,7 +21269,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>100572</t>
+          <t>100570</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -21604,19 +21300,15 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Mr Zanchy; John Pepys; James Pierce; Mr Blayton</t>
-        </is>
-      </c>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t>"not telling them that we had been there before"</t>
-        </is>
-      </c>
+          <t>Clement Sankey; John Pepys; James Pierce; Thomas Blayton</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>100573</t>
+          <t>100571</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -21626,7 +21318,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>angier_house_cambridge</t>
+          <t>john_angier_house_cambridge</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -21647,7 +21339,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>John Pepys; Mr Zanchy</t>
+          <t>John Pepys; Clement Sankey</t>
         </is>
       </c>
       <c r="I572" t="inlineStr"/>
@@ -21655,12 +21347,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>100574</t>
+          <t>100572</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>angier_house_cambridge</t>
+          <t>john_angier_house_cambridge</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -21690,7 +21382,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>100575</t>
+          <t>100573</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -21721,19 +21413,15 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Mr Blayton</t>
-        </is>
-      </c>
-      <c r="I574" t="inlineStr">
-        <is>
-          <t>"Up by four o'clock ... took my leave of my father"</t>
-        </is>
-      </c>
+          <t>Thomas Blayton</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>100576</t>
+          <t>100574</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -21764,19 +21452,15 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Mr Blayton; master of the White Hart</t>
-        </is>
-      </c>
-      <c r="I575" t="inlineStr">
-        <is>
-          <t>"took the master of the house to shew us Audley End House, who took us on foot through the park"</t>
-        </is>
-      </c>
+          <t>Thomas Blayton; Master of the White Hart</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>100575</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -21807,19 +21491,15 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Mr Blayton; master of the White Hart</t>
-        </is>
-      </c>
-      <c r="I576" t="inlineStr">
-        <is>
-          <t>"In our going, my landlord carried us through a very old hospital or almshouse"</t>
-        </is>
-      </c>
+          <t>Thomas Blayton; Master of the White Hart</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>100576</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -21850,7 +21530,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Mr Blayton; master of the White Hart</t>
+          <t>Thomas Blayton; Master of the White Hart</t>
         </is>
       </c>
       <c r="I577" t="inlineStr"/>
@@ -21858,7 +21538,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>100579</t>
+          <t>100577</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -21889,19 +21569,15 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Mr Blayton</t>
-        </is>
-      </c>
-      <c r="I578" t="inlineStr">
-        <is>
-          <t>"the road pretty good, but the weather rainy"</t>
-        </is>
-      </c>
+          <t>Thomas Blayton</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>100580</t>
+          <t>100578</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -21932,7 +21608,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Mr Blayton</t>
+          <t>Thomas Blayton</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -21944,7 +21620,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>100581</t>
+          <t>100579</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -21975,19 +21651,15 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Mr Blayton</t>
-        </is>
-      </c>
-      <c r="I580" t="inlineStr">
-        <is>
-          <t>"At Paul's I light, Mr. Blayton holding my horse"</t>
-        </is>
-      </c>
+          <t>Thomas Blayton</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>100582</t>
+          <t>100580</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -22022,7 +21694,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>100583</t>
+          <t>100581</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -22052,16 +21724,12 @@
         </is>
       </c>
       <c r="H582" t="inlineStr"/>
-      <c r="I582" t="inlineStr">
-        <is>
-          <t>"Shifted myself"</t>
-        </is>
-      </c>
+      <c r="I582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>100584</t>
+          <t>100582</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -22091,16 +21759,12 @@
         </is>
       </c>
       <c r="H583" t="inlineStr"/>
-      <c r="I583" t="inlineStr">
-        <is>
-          <t>"where I found my Lord at dinner"</t>
-        </is>
-      </c>
+      <c r="I583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>100585</t>
+          <t>100583</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -22131,19 +21795,15 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Will Howe</t>
-        </is>
-      </c>
-      <c r="I584" t="inlineStr">
-        <is>
-          <t>"calling in my way and saw my mother"</t>
-        </is>
-      </c>
+          <t>William Howe</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>100584</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -22174,19 +21834,15 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Will Howe</t>
-        </is>
-      </c>
-      <c r="I585" t="inlineStr">
-        <is>
-          <t>"to buy a hat ... at the Plough in Fleet Street by my Lord's direction"</t>
-        </is>
-      </c>
+          <t>William Howe</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>100587</t>
+          <t>100585</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -22217,7 +21873,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Will Howe; James Pierce</t>
+          <t>William Howe; James Pierce</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
@@ -22225,7 +21881,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>100588</t>
+          <t>100586</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -22255,16 +21911,12 @@
         </is>
       </c>
       <c r="H587" t="inlineStr"/>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>"he to Mr. Crew's and I to Mrs. Jem"</t>
-        </is>
-      </c>
+      <c r="I587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>100589</t>
+          <t>100587</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -22299,7 +21951,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>100590</t>
+          <t>100588</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -22334,7 +21986,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>100591</t>
+          <t>100589</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -22373,7 +22025,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>100592</t>
+          <t>100590</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -22408,7 +22060,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>100593</t>
+          <t>100591</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -22451,7 +22103,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>100594</t>
+          <t>100592</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -22494,7 +22146,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>100595</t>
+          <t>100593</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -22528,16 +22180,12 @@
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>"So to my mother's"</t>
-        </is>
-      </c>
+      <c r="I594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>100596</t>
+          <t>100594</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -22571,16 +22219,12 @@
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I595" t="inlineStr">
-        <is>
-          <t>"of whom I took leave ... because she was to go out of town to-morrow"</t>
-        </is>
-      </c>
+      <c r="I595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>100597</t>
+          <t>100595</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -22614,16 +22258,12 @@
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I596" t="inlineStr">
-        <is>
-          <t>"To my mother's and supped there"</t>
-        </is>
-      </c>
+      <c r="I596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>100598</t>
+          <t>100596</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">

--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="edges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$597</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$725</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I597"/>
+  <dimension ref="A1:I725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22299,8 +22299,4944 @@
       </c>
       <c r="I597" t="inlineStr"/>
     </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>100597</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>3</v>
+      </c>
+      <c r="F598" t="n">
+        <v>1</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>100598</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>3</v>
+      </c>
+      <c r="F599" t="n">
+        <v>1</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>100599</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>3</v>
+      </c>
+      <c r="F600" t="n">
+        <v>1</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Edward Shipley</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>100600</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>laxton_apothecary</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>3</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Edward Shipley</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>"into London"</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>100601</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>laxton_apothecary</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>sun_tavern_king_street</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>3</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Edward Shipley</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>"so by water to Westminster, where at the Sun [tavern]"</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>100602</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>sun_tavern_king_street</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>3</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>100603</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>3</v>
+      </c>
+      <c r="F604" t="n">
+        <v>2</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>"I went early to my Lord at Mr. Crew's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>100604</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>3</v>
+      </c>
+      <c r="F605" t="n">
+        <v>2</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>100605</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>leg_tavern</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>3</v>
+      </c>
+      <c r="F606" t="n">
+        <v>2</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Mr Eglin; James Chetwind; Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>100606</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>leg_tavern</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>3</v>
+      </c>
+      <c r="F607" t="n">
+        <v>2</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Mr Eglin; James Chetwind; Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>"After that to the Swan tavern" - taken as swan_inn, New Palace Yard. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>3</v>
+      </c>
+      <c r="F608" t="n">
+        <v>2</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Henry Moore</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Mrs Jem taken to be still at Scott's, as in February. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>100608</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>3</v>
+      </c>
+      <c r="F609" t="n">
+        <v>2</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>100609</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>3</v>
+      </c>
+      <c r="F610" t="n">
+        <v>2</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>100610</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>3</v>
+      </c>
+      <c r="F611" t="n">
+        <v>3</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>100611</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>3</v>
+      </c>
+      <c r="F612" t="n">
+        <v>3</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Mr Pierce the purser; Lieutenant Lambert; John Creed; William Howe</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>"Mr. Pierce the purser" is a different man from Mr Pierce the surgeon. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>100612</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>3</v>
+      </c>
+      <c r="F613" t="n">
+        <v>3</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>100613</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>3</v>
+      </c>
+      <c r="F614" t="n">
+        <v>3</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>100614</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>warwick_house</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>3</v>
+      </c>
+      <c r="F615" t="n">
+        <v>3</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>100615</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>warwick_house</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>3</v>
+      </c>
+      <c r="F616" t="n">
+        <v>3</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>100616</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>michael_hering_house</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>3</v>
+      </c>
+      <c r="F617" t="n">
+        <v>3</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr"/>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>"went by appointment to Hering, the merchant, but missed of my money"</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>100617</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>michael_hering_house</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_8</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>3</v>
+      </c>
+      <c r="F618" t="n">
+        <v>3</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Mr Gifford</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>100618</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_8</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_9</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>3</v>
+      </c>
+      <c r="F619" t="n">
+        <v>3</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Tom Harper</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>100619</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_9</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>3</v>
+      </c>
+      <c r="F620" t="n">
+        <v>3</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>100620</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>3</v>
+      </c>
+      <c r="F621" t="n">
+        <v>4</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr"/>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>"to Mr. Gunning's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>100621</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>exeter_house_chapel</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>3</v>
+      </c>
+      <c r="F622" t="n">
+        <v>4</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>"to my mother"</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>100622</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>robert_mossum_church</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>3</v>
+      </c>
+      <c r="F623" t="n">
+        <v>4</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Jane Birch</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>"we three to Mr. Messum's" - the third taken to be the maid, Jane Birch. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>100623</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>robert_mossum_church</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>3</v>
+      </c>
+      <c r="F624" t="n">
+        <v>4</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Jane Birch</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>100624</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>3</v>
+      </c>
+      <c r="F625" t="n">
+        <v>4</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Jane Birch</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>100625</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>3</v>
+      </c>
+      <c r="F626" t="n">
+        <v>5</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>100626</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>salutation_tavern</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>3</v>
+      </c>
+      <c r="F627" t="n">
+        <v>5</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Edward Shipley; Mr Pinkney</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>"who took me by water to Billingsgate"</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>100627</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>salutation_tavern</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>pinkney_house</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>3</v>
+      </c>
+      <c r="F628" t="n">
+        <v>5</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Mr Pinkney</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>"so to Westminster by water, only seeing Mr. Pinkney at his own house"</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>100628</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>pinkney_house</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>3</v>
+      </c>
+      <c r="F629" t="n">
+        <v>5</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr"/>
+      <c r="I629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>100629</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>3</v>
+      </c>
+      <c r="F630" t="n">
+        <v>6</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>"my Lord's lodgings at Mr. Crew's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>100630</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>3</v>
+      </c>
+      <c r="F631" t="n">
+        <v>6</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Edward Shipley</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>"he bade us to go home again, and get a fire against an hour after. Which we did at White Hall"</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>100631</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>whitehall_garden</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>3</v>
+      </c>
+      <c r="F632" t="n">
+        <v>6</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>100632</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>whitehall_garden</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>3</v>
+      </c>
+      <c r="F633" t="n">
+        <v>6</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>"I waiting upon him through the garden till he came to the Hall"</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>100633</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>3</v>
+      </c>
+      <c r="F634" t="n">
+        <v>6</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>100634</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>3</v>
+      </c>
+      <c r="F635" t="n">
+        <v>6</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Thomas Pepys</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>100635</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>bell_tavern</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>3</v>
+      </c>
+      <c r="F636" t="n">
+        <v>6</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Mr Day</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>100636</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>bell_tavern</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>3</v>
+      </c>
+      <c r="F637" t="n">
+        <v>6</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>100637</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>3</v>
+      </c>
+      <c r="F638" t="n">
+        <v>6</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>100638</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>3</v>
+      </c>
+      <c r="F639" t="n">
+        <v>6</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>"called at my Lord's for Mr. Sheply"</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>100639</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>lion_tavern</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>3</v>
+      </c>
+      <c r="F640" t="n">
+        <v>6</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>"but found him at the Lion"</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>100640</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>lion_tavern</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>3</v>
+      </c>
+      <c r="F641" t="n">
+        <v>6</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>100641</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>3</v>
+      </c>
+      <c r="F642" t="n">
+        <v>7</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>100642</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>st_jamess_palace</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>3</v>
+      </c>
+      <c r="F643" t="n">
+        <v>7</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>"my Lord overtook me in his coach, and called me in"</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>100643</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>st_jamess_palace</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>st_james_park</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>3</v>
+      </c>
+      <c r="F644" t="n">
+        <v>7</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>"we walked over the Park thither"</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>100644</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>st_james_park</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>3</v>
+      </c>
+      <c r="F645" t="n">
+        <v>7</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>100645</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>3</v>
+      </c>
+      <c r="F646" t="n">
+        <v>7</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>100646</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>3</v>
+      </c>
+      <c r="F647" t="n">
+        <v>7</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>100647</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>angel_tavern</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>3</v>
+      </c>
+      <c r="F648" t="n">
+        <v>7</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>100648</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>angel_tavern</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>michael_hering_house</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>3</v>
+      </c>
+      <c r="F649" t="n">
+        <v>7</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>"by water to London, where I went to Herring's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>100649</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>michael_hering_house</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>popes_head_alley</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>3</v>
+      </c>
+      <c r="F650" t="n">
+        <v>7</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>100650</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>popes_head_alley</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_10</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>3</v>
+      </c>
+      <c r="F651" t="n">
+        <v>7</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Adam Chard</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>100651</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_10</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>sun_tavern_behind_exchange</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>3</v>
+      </c>
+      <c r="F652" t="n">
+        <v>7</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>William Wight</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>"meeting my uncle Wight by the way, took him with me thither"</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>100652</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>sun_tavern_behind_exchange</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>cock_tavern</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>3</v>
+      </c>
+      <c r="F653" t="n">
+        <v>7</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>William Wight; Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>100653</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>cock_tavern</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>fleet_street</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>3</v>
+      </c>
+      <c r="F654" t="n">
+        <v>7</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>William Wight</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>"he and I homewards, parted at Fleet Street"</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>100654</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>fleet_street</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>3</v>
+      </c>
+      <c r="F655" t="n">
+        <v>7</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>"where I found my father newly come home from Brampton"</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>100655</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>william_wotton_shop</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>3</v>
+      </c>
+      <c r="F656" t="n">
+        <v>7</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>"Going home I called at Wotton's and took home a piece of cheese"</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>100656</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>william_wotton_shop</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>3</v>
+      </c>
+      <c r="F657" t="n">
+        <v>7</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>100657</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>3</v>
+      </c>
+      <c r="F658" t="n">
+        <v>8</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>"To Whitehall to bespeak some firing for my father at Short's" - Short's not modelled separately. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>100658</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>3</v>
+      </c>
+      <c r="F659" t="n">
+        <v>8</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>100659</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>commons_lobby</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>3</v>
+      </c>
+      <c r="F660" t="n">
+        <v>8</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>"to bring me to my Lord at the lobby"</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>100660</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>commons_lobby</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>dog_tavern</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>3</v>
+      </c>
+      <c r="F661" t="n">
+        <v>8</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>"This noon I met at the Dog tavern Captain Philip Holland" - narrated at the end of the entry, placed at the noon it describes</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>100661</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>dog_tavern</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>3</v>
+      </c>
+      <c r="F662" t="n">
+        <v>8</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>"Home about two o'clock"</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>100662</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>paternoster_row</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>3</v>
+      </c>
+      <c r="F663" t="n">
+        <v>8</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>"by land"</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>100663</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>paternoster_row</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>3</v>
+      </c>
+      <c r="F664" t="n">
+        <v>8</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>100664</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>3</v>
+      </c>
+      <c r="F665" t="n">
+        <v>8</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Henry Moore</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>"so back to Whitehall again, both of us"</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>100665</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>3</v>
+      </c>
+      <c r="F666" t="n">
+        <v>8</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>100666</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>3</v>
+      </c>
+      <c r="F667" t="n">
+        <v>8</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Mr King</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>100667</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>3</v>
+      </c>
+      <c r="F668" t="n">
+        <v>8</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>return home not stated; the day must close at Axe Yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>100668</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>3</v>
+      </c>
+      <c r="F669" t="n">
+        <v>9</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>100669</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>painted_chamber</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>3</v>
+      </c>
+      <c r="F670" t="n">
+        <v>9</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Edward Montagu; Mr Dudley</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>"came to Westminster with him in the coach"</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>100670</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>painted_chamber</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>3</v>
+      </c>
+      <c r="F671" t="n">
+        <v>9</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>100671</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>3</v>
+      </c>
+      <c r="F672" t="n">
+        <v>9</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>100672</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>navy_office</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>3</v>
+      </c>
+      <c r="F673" t="n">
+        <v>9</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>100673</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>navy_office</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>council_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>3</v>
+      </c>
+      <c r="F674" t="n">
+        <v>9</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>"Then by coach back again, and at White Hall at the Council Chamber"</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>100674</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>council_chamber_whitehall</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>3</v>
+      </c>
+      <c r="F675" t="n">
+        <v>9</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>100675</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>3</v>
+      </c>
+      <c r="F676" t="n">
+        <v>9</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>100676</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>3</v>
+      </c>
+      <c r="F677" t="n">
+        <v>10</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>"whom I took in his cutting house"</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>100677</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>navy_treasurer_office</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>3</v>
+      </c>
+      <c r="F678" t="n">
+        <v>10</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>100678</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>navy_treasurer_office</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>rawlinson_house</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>3</v>
+      </c>
+      <c r="F679" t="n">
+        <v>10</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>100679</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>rawlinson_house</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>sun_tavern_fish_street_hill</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>3</v>
+      </c>
+      <c r="F680" t="n">
+        <v>10</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>100680</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>sun_tavern_fish_street_hill</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>3</v>
+      </c>
+      <c r="F681" t="n">
+        <v>10</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>"Then by coach home"</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>100681</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>3</v>
+      </c>
+      <c r="F682" t="n">
+        <v>10</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>"to see Mrs. Jem and paid her maid L7"</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>100682</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>blackburne_house</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>3</v>
+      </c>
+      <c r="F683" t="n">
+        <v>10</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>100683</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>blackburne_house</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>3</v>
+      </c>
+      <c r="F684" t="n">
+        <v>10</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>"Sir H. Wright's where my Lord dined"</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>100684</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>3</v>
+      </c>
+      <c r="F685" t="n">
+        <v>10</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>William Howe</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>"Hither W. Howe comes to me and so to Westminster ... He went with me to my office"</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>100685</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>office_exchequer</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>3</v>
+      </c>
+      <c r="F686" t="n">
+        <v>10</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>100686</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>whitehall_palace</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>3</v>
+      </c>
+      <c r="F687" t="n">
+        <v>10</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>100687</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>3</v>
+      </c>
+      <c r="F688" t="n">
+        <v>11</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>"At night my wife and I went to my father's to supper"</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>100688</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>3</v>
+      </c>
+      <c r="F689" t="n">
+        <v>11</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>100689</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>new_exchange</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>3</v>
+      </c>
+      <c r="F690" t="n">
+        <v>12</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>"My wife and I to the Exchange, where we bought a great many things" - read as the New Exchange, the Strand shopping arcade. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>100690</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>new_exchange</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>bedells_bookshop</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>3</v>
+      </c>
+      <c r="F691" t="n">
+        <v>12</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>"where I left her and went into London"</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>100691</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>bedells_bookshop</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>wilkinsons_cookshop</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>3</v>
+      </c>
+      <c r="F692" t="n">
+        <v>12</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>"So came back"</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>100692</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>wilkinsons_cookshop</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>white_horse_king_street</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>3</v>
+      </c>
+      <c r="F693" t="n">
+        <v>12</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>100693</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>white_horse_king_street</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>bowyer_house</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>3</v>
+      </c>
+      <c r="F694" t="n">
+        <v>12</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>"I got Mr. Buddle's horse to ride to Huntsmore to Mr. Bowyer's"; "Here I lay"</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>100694</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>bowyer_house</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>3</v>
+      </c>
+      <c r="F695" t="n">
+        <v>13</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>"It rained hard and I got up early, and got to London by 8 o'clock at my Lord's lodgings"</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>100695</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>3</v>
+      </c>
+      <c r="F696" t="n">
+        <v>13</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>100696</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>william_wotton_shop</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>3</v>
+      </c>
+      <c r="F697" t="n">
+        <v>13</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>"and so at my shoemaker's" - Wotton, cf. 18 Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>100697</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>william_wotton_shop</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>roberts_whitehall</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>3</v>
+      </c>
+      <c r="F698" t="n">
+        <v>13</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>"At night to Whitehall"</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>100698</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>roberts_whitehall</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>3</v>
+      </c>
+      <c r="F699" t="n">
+        <v>13</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>100699</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>3</v>
+      </c>
+      <c r="F700" t="n">
+        <v>13</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>100700</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>3</v>
+      </c>
+      <c r="F701" t="n">
+        <v>14</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>100701</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>st_jamess_palace</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>3</v>
+      </c>
+      <c r="F702" t="n">
+        <v>14</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>James Pierce</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>100702</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>st_jamess_palace</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>3</v>
+      </c>
+      <c r="F703" t="n">
+        <v>14</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>James Pierce</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>"he and I to Whitehall, where with Luellin we dined at Marsh's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>100703</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>3</v>
+      </c>
+      <c r="F704" t="n">
+        <v>14</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>100704</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>3</v>
+      </c>
+      <c r="F705" t="n">
+        <v>14</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>100705</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>creeds_chamber</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>3</v>
+      </c>
+      <c r="F706" t="n">
+        <v>14</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>100706</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>creeds_chamber</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>3</v>
+      </c>
+      <c r="F707" t="n">
+        <v>14</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>100707</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>3</v>
+      </c>
+      <c r="F708" t="n">
+        <v>14</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>old Beard</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>"I took him by coach to my Lord's, but he was not at home"</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>100708</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>3</v>
+      </c>
+      <c r="F709" t="n">
+        <v>14</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>old Beard</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>"afterwards I found him out at Sir H. Wright's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>100709</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>3</v>
+      </c>
+      <c r="F710" t="n">
+        <v>14</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>"Thence by coach, it raining hard, to Mrs. Jem"</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>100710</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>3</v>
+      </c>
+      <c r="F711" t="n">
+        <v>14</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>100711</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>3</v>
+      </c>
+      <c r="F712" t="n">
+        <v>15</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>"where I took leave of some of my friends"</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>100712</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>wills_alehouse</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>anne_michell_shop</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>3</v>
+      </c>
+      <c r="F713" t="n">
+        <v>15</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>"in the Hall paid and made even with Mrs. Michell"</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>100713</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>anne_michell_shop</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>axe_brewhouse</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>3</v>
+      </c>
+      <c r="F714" t="n">
+        <v>15</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>"at the Axe paid him this quarter to Ladyday next"</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>100714</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>axe_brewhouse</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>3</v>
+      </c>
+      <c r="F715" t="n">
+        <v>15</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>"Dick Mathews comes to dine"</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>100715</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>3</v>
+      </c>
+      <c r="F716" t="n">
+        <v>15</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Richard Matthews</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>100716</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>harpers_tavern</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>fish_street</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>3</v>
+      </c>
+      <c r="F717" t="n">
+        <v>15</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>"So into London by water"</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>100717</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>fish_street</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>sun_tavern_fish_street_hill</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>3</v>
+      </c>
+      <c r="F718" t="n">
+        <v>15</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>"went to the Sun Tavern and ate it"</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>100718</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>sun_tavern_fish_street_hill</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>3</v>
+      </c>
+      <c r="F719" t="n">
+        <v>15</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>"From thence homewards ... I went to my Lord's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>100719</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>3</v>
+      </c>
+      <c r="F720" t="n">
+        <v>15</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Jemima Montagu</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>"So home with Mrs. Jem by coach"</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>100720</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>scott_house</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>3</v>
+      </c>
+      <c r="F721" t="n">
+        <v>15</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>"and then home to my own house"</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>100721</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>fox_tavern</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>3</v>
+      </c>
+      <c r="F722" t="n">
+        <v>15</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>100722</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>fox_tavern</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>3</v>
+      </c>
+      <c r="F723" t="n">
+        <v>15</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>100723</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>fox_tavern</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>3</v>
+      </c>
+      <c r="F724" t="n">
+        <v>15</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>"To the Fox again"</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>100724</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>fox_tavern</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>3</v>
+      </c>
+      <c r="F725" t="n">
+        <v>15</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>"Home with my wife"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I597"/>
+  <autoFilter ref="A1:I725"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="edges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$723</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I725"/>
+  <dimension ref="A1:I723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4694,7 +4694,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>100294</t>
+          <t>100117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4733,7 +4733,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>100118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>100118</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>100119</t>
+          <t>100120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4838,7 +4838,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>100120</t>
+          <t>100121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>100121</t>
+          <t>100122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4908,7 +4908,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>100122</t>
+          <t>100123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>100123</t>
+          <t>100124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>100124</t>
+          <t>100125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5017,7 +5017,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>100125</t>
+          <t>100126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>100126</t>
+          <t>100127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>100128</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5161,7 +5161,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>100129</t>
+          <t>100130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>100130</t>
+          <t>100131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5235,7 +5235,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>100131</t>
+          <t>100132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>100133</t>
+          <t>100134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5344,7 +5344,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>100134</t>
+          <t>100135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>100135</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>100136</t>
+          <t>100137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5461,7 +5461,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>100137</t>
+          <t>100138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>100138</t>
+          <t>100139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5539,7 +5539,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>100139</t>
+          <t>100140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>100141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>100141</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>100142</t>
+          <t>100143</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>100143</t>
+          <t>100144</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5722,7 +5722,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>100144</t>
+          <t>100145</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>100145</t>
+          <t>100146</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>100146</t>
+          <t>100147</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5827,7 +5827,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>100148</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5862,7 +5862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>100148</t>
+          <t>100149</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>100149</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5932,7 +5932,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>100150</t>
+          <t>100151</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>100151</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>100152</t>
+          <t>100153</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>100153</t>
+          <t>100154</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6076,7 +6076,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>100154</t>
+          <t>100155</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6111,7 +6111,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>100156</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6146,7 +6146,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>100157</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6181,7 +6181,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>100157</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>100158</t>
+          <t>100159</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>100159</t>
+          <t>100160</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6294,7 +6294,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>100161</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6333,7 +6333,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>100161</t>
+          <t>100162</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6368,7 +6368,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>100162</t>
+          <t>100163</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6403,7 +6403,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>100163</t>
+          <t>100164</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6442,7 +6442,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>100164</t>
+          <t>100165</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>100165</t>
+          <t>100166</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6516,7 +6516,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>100166</t>
+          <t>100167</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6551,7 +6551,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>100167</t>
+          <t>100168</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>100168</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>100169</t>
+          <t>100170</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>100170</t>
+          <t>100171</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>100171</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6730,7 +6730,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>100172</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6769,7 +6769,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>100173</t>
+          <t>100174</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>100174</t>
+          <t>100175</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6839,7 +6839,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>100175</t>
+          <t>100176</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6874,7 +6874,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>100176</t>
+          <t>100177</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6913,7 +6913,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>100177</t>
+          <t>100178</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>100179</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6983,7 +6983,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>100179</t>
+          <t>100180</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7018,7 +7018,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>100180</t>
+          <t>100181</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7053,7 +7053,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>100182</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7092,7 +7092,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>100182</t>
+          <t>100183</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7131,7 +7131,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>100183</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7170,7 +7170,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>100184</t>
+          <t>100185</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7209,7 +7209,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>100185</t>
+          <t>100186</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7244,7 +7244,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>100186</t>
+          <t>100187</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7279,7 +7279,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>100187</t>
+          <t>100188</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7314,7 +7314,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>100188</t>
+          <t>100189</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>100189</t>
+          <t>100190</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7384,7 +7384,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>100190</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>100192</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7458,7 +7458,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>100192</t>
+          <t>100193</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7493,7 +7493,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>100193</t>
+          <t>100194</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7532,7 +7532,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>100194</t>
+          <t>100195</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7571,7 +7571,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>100195</t>
+          <t>100196</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>100196</t>
+          <t>100197</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7641,7 +7641,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>100197</t>
+          <t>100198</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7680,7 +7680,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>100198</t>
+          <t>100199</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7715,7 +7715,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>100200</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7750,7 +7750,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>100200</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7785,7 +7785,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>100201</t>
+          <t>100202</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7820,7 +7820,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>100202</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7855,7 +7855,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>100203</t>
+          <t>100204</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>100204</t>
+          <t>100205</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7925,7 +7925,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>100205</t>
+          <t>100206</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>100206</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7995,7 +7995,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>100207</t>
+          <t>100208</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8034,7 +8034,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>100209</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8069,7 +8069,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>100209</t>
+          <t>100210</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>100210</t>
+          <t>100211</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8139,7 +8139,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>100211</t>
+          <t>100212</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8174,7 +8174,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>100212</t>
+          <t>100213</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8209,7 +8209,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>100213</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8248,7 +8248,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>100215</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8287,7 +8287,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>100215</t>
+          <t>100216</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>100216</t>
+          <t>100217</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8365,7 +8365,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>100217</t>
+          <t>100218</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8404,7 +8404,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>100218</t>
+          <t>100219</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>100219</t>
+          <t>100220</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>100220</t>
+          <t>100221</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8509,7 +8509,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>100221</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8544,7 +8544,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>100223</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8579,7 +8579,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>100223</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>100224</t>
+          <t>100225</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8649,7 +8649,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>100225</t>
+          <t>100226</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>100226</t>
+          <t>100227</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8719,7 +8719,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100228</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>100229</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8789,7 +8789,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>100229</t>
+          <t>100230</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8824,7 +8824,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>100230</t>
+          <t>100231</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8859,7 +8859,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>100231</t>
+          <t>100232</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>100232</t>
+          <t>100233</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8933,7 +8933,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>100233</t>
+          <t>100234</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8968,7 +8968,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>100234</t>
+          <t>100235</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -9003,7 +9003,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>100235</t>
+          <t>100236</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9038,7 +9038,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>100236</t>
+          <t>100237</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>100237</t>
+          <t>100238</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9108,7 +9108,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>100238</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9143,7 +9143,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>100239</t>
+          <t>100240</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9178,7 +9178,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100241</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>100241</t>
+          <t>100242</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -9252,7 +9252,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>100242</t>
+          <t>100243</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -9287,7 +9287,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>100243</t>
+          <t>100244</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -9326,7 +9326,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>100244</t>
+          <t>100245</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>100245</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>100246</t>
+          <t>100247</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>100247</t>
+          <t>100248</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -9466,7 +9466,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>100248</t>
+          <t>100249</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>100249</t>
+          <t>100250</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9536,7 +9536,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>100250</t>
+          <t>100251</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9571,7 +9571,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>100251</t>
+          <t>100252</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>100252</t>
+          <t>100253</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9645,7 +9645,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>100253</t>
+          <t>100254</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9680,7 +9680,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>100254</t>
+          <t>100255</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9715,7 +9715,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>100255</t>
+          <t>100256</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9750,7 +9750,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>100256</t>
+          <t>100257</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9785,7 +9785,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>100258</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>100258</t>
+          <t>100259</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9859,7 +9859,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>100259</t>
+          <t>100260</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -9894,7 +9894,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>100261</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -9929,7 +9929,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>100261</t>
+          <t>100262</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -9964,7 +9964,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>100262</t>
+          <t>100263</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10003,7 +10003,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>100263</t>
+          <t>100264</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10038,7 +10038,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>100264</t>
+          <t>100265</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10073,7 +10073,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>100265</t>
+          <t>100266</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10108,7 +10108,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>100266</t>
+          <t>100267</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10143,7 +10143,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>100267</t>
+          <t>100268</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>100268</t>
+          <t>100269</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10213,7 +10213,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>100269</t>
+          <t>100270</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -10248,7 +10248,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>100270</t>
+          <t>100271</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10283,7 +10283,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>100271</t>
+          <t>100272</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>100272</t>
+          <t>100273</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -10357,7 +10357,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>100273</t>
+          <t>100274</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10392,7 +10392,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>100274</t>
+          <t>100275</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10427,7 +10427,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>100275</t>
+          <t>100276</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10462,7 +10462,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>100276</t>
+          <t>100277</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>100277</t>
+          <t>100278</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -10536,7 +10536,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>100279</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -10571,7 +10571,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>100279</t>
+          <t>100280</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -10606,7 +10606,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>100280</t>
+          <t>100281</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10641,7 +10641,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>100281</t>
+          <t>100282</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -10676,7 +10676,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>100282</t>
+          <t>100283</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -10711,7 +10711,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>100283</t>
+          <t>100284</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10746,7 +10746,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>100284</t>
+          <t>100285</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10785,7 +10785,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>100285</t>
+          <t>100286</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10820,7 +10820,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>100286</t>
+          <t>100287</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>100287</t>
+          <t>100288</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -10890,7 +10890,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>100288</t>
+          <t>100289</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -10925,7 +10925,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>100289</t>
+          <t>100290</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>100290</t>
+          <t>100291</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -10995,7 +10995,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>100291</t>
+          <t>100292</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11030,7 +11030,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>100292</t>
+          <t>100293</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>100293</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>laxton_apothecary</t>
+          <t>john_layton_apothecary</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>laxton_apothecary</t>
+          <t>john_layton_apothecary</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>leg_tavern</t>
+          <t>leg_tavern_king_st</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Mr Eglin; James Chetwind; Mr Thomas</t>
+          <t>Samuel Edlin; James Chetwind; Mr Thomas</t>
         </is>
       </c>
       <c r="I606" t="inlineStr"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>leg_tavern</t>
+          <t>leg_tavern_king_st</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Mr Eglin; James Chetwind; Mr Thomas</t>
+          <t>Samuel Edlin; James Chetwind; Mr Thomas</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -22871,12 +22871,12 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Mr Pierce the purser; Lieutenant Lambert; John Creed; William Howe</t>
+          <t>Andrew Pearse; Lieutenant David Lambert; John Creed; William Howe</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>"Mr. Pierce the purser" is a different man from Mr Pierce the surgeon. FLAG</t>
+          <t>"Mr. Pierce the purser" is a different man from Mr Pierce the surgeon.</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Mr Gifford</t>
+          <t>Henry Gifford</t>
         </is>
       </c>
       <c r="I618" t="inlineStr"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Edward Shipley; Mr Pinkney</t>
+          <t>Edward Shipley; George Pinkney</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>pinkney_house</t>
+          <t>george_pinkney_house</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Mr Pinkney</t>
+          <t>George Pinkney</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -23504,7 +23504,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>pinkney_house</t>
+          <t>george_pinkney_house</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -23856,7 +23856,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -23886,12 +23886,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>red_lion_tavern</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -23913,7 +23913,7 @@
       <c r="H639" t="inlineStr"/>
       <c r="I639" t="inlineStr">
         <is>
-          <t>"called at my Lord's for Mr. Sheply"</t>
+          <t>"but found him at the Lion"</t>
         </is>
       </c>
     </row>
@@ -23925,12 +23925,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>red_lion_tavern</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>lion_tavern</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -23950,11 +23950,7 @@
         </is>
       </c>
       <c r="H640" t="inlineStr"/>
-      <c r="I640" t="inlineStr">
-        <is>
-          <t>"but found him at the Lion"</t>
-        </is>
-      </c>
+      <c r="I640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -23964,12 +23960,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>lion_tavern</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -23981,7 +23977,7 @@
         <v>3</v>
       </c>
       <c r="F641" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G641" t="inlineStr">
         <is>
@@ -23999,12 +23995,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>st_jamess_palace</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -24020,11 +24016,19 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H642" t="inlineStr"/>
-      <c r="I642" t="inlineStr"/>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Edward Montagu</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>"my Lord overtook me in his coach, and called me in"</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -24034,12 +24038,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>st_jamess_palace</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>st_jamess_palace</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -24055,7 +24059,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -24065,7 +24069,7 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>"my Lord overtook me in his coach, and called me in"</t>
+          <t>"we walked over the Park thither"</t>
         </is>
       </c>
     </row>
@@ -24077,12 +24081,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>st_jamess_palace</t>
+          <t>st_james_park</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>st_james_park</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -24106,11 +24110,7 @@
           <t>Edward Montagu</t>
         </is>
       </c>
-      <c r="I644" t="inlineStr">
-        <is>
-          <t>"we walked over the Park thither"</t>
-        </is>
-      </c>
+      <c r="I644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -24120,12 +24120,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>st_james_park</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -24144,11 +24144,7 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>Edward Montagu</t>
-        </is>
-      </c>
+      <c r="H645" t="inlineStr"/>
       <c r="I645" t="inlineStr"/>
     </row>
     <row r="646">
@@ -24159,12 +24155,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -24194,12 +24190,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>angel_tavern</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -24229,12 +24225,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>angel_tavern</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>angel_tavern</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -24250,11 +24246,19 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H648" t="inlineStr"/>
-      <c r="I648" t="inlineStr"/>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>mr thomas a govt clerk. "by water to London, where I went to Herring's"</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -24264,12 +24268,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>angel_tavern</t>
+          <t>michael_hering_house</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>michael_hering_house</t>
+          <t>popes_head_alley</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -24285,7 +24289,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -24293,11 +24297,7 @@
           <t>Mr Thomas</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr">
-        <is>
-          <t>"by water to London, where I went to Herring's"</t>
-        </is>
-      </c>
+      <c r="I649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>michael_hering_house</t>
+          <t>popes_head_alley</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>popes_head_alley</t>
+          <t>alehouse_unknown_10</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Mr Thomas</t>
+          <t>Adam Chard; Mr Thomas</t>
         </is>
       </c>
       <c r="I650" t="inlineStr"/>
@@ -24346,12 +24346,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>popes_head_alley</t>
+          <t>alehouse_unknown_10</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>alehouse_unknown_10</t>
+          <t>sun_tavern_threadneedle_st</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -24372,10 +24372,14 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Adam Chard</t>
-        </is>
-      </c>
-      <c r="I651" t="inlineStr"/>
+          <t>William Wight; Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>"meeting my uncle Wight by the way, took him with me thither"</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -24385,12 +24389,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>alehouse_unknown_10</t>
+          <t>sun_tavern_threadneedle_st</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>sun_tavern_behind_exchange</t>
+          <t>cock_tavern</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -24411,14 +24415,10 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>William Wight</t>
-        </is>
-      </c>
-      <c r="I652" t="inlineStr">
-        <is>
-          <t>"meeting my uncle Wight by the way, took him with me thither"</t>
-        </is>
-      </c>
+          <t>William Wight; Mr Thomas</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -24428,12 +24428,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>sun_tavern_behind_exchange</t>
+          <t>cock_tavern</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>cock_tavern</t>
+          <t>fleet_street</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -24454,10 +24454,14 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>William Wight; Mr Thomas</t>
-        </is>
-      </c>
-      <c r="I653" t="inlineStr"/>
+          <t>William Wight</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>"he and I homewards, parted at Fleet Street"</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -24467,12 +24471,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>cock_tavern</t>
+          <t>fleet_street</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>fleet_street</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -24491,14 +24495,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H654" t="inlineStr">
-        <is>
-          <t>William Wight</t>
-        </is>
-      </c>
+      <c r="H654" t="inlineStr"/>
       <c r="I654" t="inlineStr">
         <is>
-          <t>"he and I homewards, parted at Fleet Street"</t>
+          <t>"where I found my father newly come home from Brampton"</t>
         </is>
       </c>
     </row>
@@ -24510,12 +24510,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>fleet_street</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -24537,7 +24537,7 @@
       <c r="H655" t="inlineStr"/>
       <c r="I655" t="inlineStr">
         <is>
-          <t>"where I found my father newly come home from Brampton"</t>
+          <t>"Going home I called at Wotton's and took home a piece of cheese"</t>
         </is>
       </c>
     </row>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>william_wotton_shop</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -24574,11 +24574,7 @@
         </is>
       </c>
       <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr">
-        <is>
-          <t>"Going home I called at Wotton's and took home a piece of cheese"</t>
-        </is>
-      </c>
+      <c r="I656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -24588,12 +24584,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>william_wotton_shop</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>shotts_woodmonger_whitehall</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -24605,7 +24601,7 @@
         <v>3</v>
       </c>
       <c r="F657" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G657" t="inlineStr">
         <is>
@@ -24613,7 +24609,11 @@
         </is>
       </c>
       <c r="H657" t="inlineStr"/>
-      <c r="I657" t="inlineStr"/>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>"To Whitehall to bespeak some firing for my father at Shott's"</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -24623,12 +24623,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>shotts_woodmonger_whitehall</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -24648,11 +24648,7 @@
         </is>
       </c>
       <c r="H658" t="inlineStr"/>
-      <c r="I658" t="inlineStr">
-        <is>
-          <t>"To Whitehall to bespeak some firing for my father at Short's" - Short's not modelled separately. FLAG</t>
-        </is>
-      </c>
+      <c r="I658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -24662,12 +24658,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>dog_tavern</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -24687,7 +24683,11 @@
         </is>
       </c>
       <c r="H659" t="inlineStr"/>
-      <c r="I659" t="inlineStr"/>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>"This noon I met at the Dog tavern Captain Philip Holland" - narrated at the end of the entry, placed at the noon it describes</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -24697,12 +24697,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>dog_tavern</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>commons_lobby</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -24724,7 +24724,7 @@
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr">
         <is>
-          <t>"to bring me to my Lord at the lobby"</t>
+          <t>"Home about two o'clock"</t>
         </is>
       </c>
     </row>
@@ -24736,12 +24736,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>commons_lobby</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>dog_tavern</t>
+          <t>paternoster_row</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -24760,10 +24760,14 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr"/>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>"This noon I met at the Dog tavern Captain Philip Holland" - narrated at the end of the entry, placed at the noon it describes</t>
+          <t>"by land"</t>
         </is>
       </c>
     </row>
@@ -24775,7 +24779,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>dog_tavern</t>
+          <t>paternoster_row</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -24799,12 +24803,12 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr"/>
-      <c r="I662" t="inlineStr">
-        <is>
-          <t>"Home about two o'clock"</t>
-        </is>
-      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -24819,7 +24823,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>paternoster_row</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -24840,12 +24844,12 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Elizabeth Pepys</t>
+          <t>Henry Moore</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>"by land"</t>
+          <t>"so back to Whitehall again, both of us"</t>
         </is>
       </c>
     </row>
@@ -24857,12 +24861,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>paternoster_row</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -24881,11 +24885,7 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H664" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
+      <c r="H664" t="inlineStr"/>
       <c r="I664" t="inlineStr"/>
     </row>
     <row r="665">
@@ -24896,12 +24896,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -24922,12 +24922,12 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Henry Moore</t>
+          <t>William King</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>"so back to Whitehall again, both of us"</t>
+          <t>Clerk to the Treasurers at War 1660</t>
         </is>
       </c>
     </row>
@@ -24939,12 +24939,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -24964,7 +24964,11 @@
         </is>
       </c>
       <c r="H666" t="inlineStr"/>
-      <c r="I666" t="inlineStr"/>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>return home not stated; the day must close at Axe Yard</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -24974,12 +24978,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -24991,19 +24995,19 @@
         <v>3</v>
       </c>
       <c r="F667" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G667" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
-        <is>
-          <t>Mr King</t>
-        </is>
-      </c>
-      <c r="I667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -25013,12 +25017,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>painted_chamber_westminster</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -25030,17 +25034,21 @@
         <v>3</v>
       </c>
       <c r="F668" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H668" t="inlineStr"/>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Edward Montagu; William Dudley</t>
+        </is>
+      </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>return home not stated; the day must close at Axe Yard</t>
+          <t>"came to Westminster with him in the coach"</t>
         </is>
       </c>
     </row>
@@ -25052,12 +25060,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>painted_chamber_westminster</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -25077,11 +25085,7 @@
         </is>
       </c>
       <c r="H669" t="inlineStr"/>
-      <c r="I669" t="inlineStr">
-        <is>
-          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
-        </is>
-      </c>
+      <c r="I669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -25091,12 +25095,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>painted_chamber</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -25112,19 +25116,11 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="H670" t="inlineStr">
-        <is>
-          <t>Edward Montagu; Mr Dudley</t>
-        </is>
-      </c>
-      <c r="I670" t="inlineStr">
-        <is>
-          <t>"came to Westminster with him in the coach"</t>
-        </is>
-      </c>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -25134,12 +25130,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>painted_chamber</t>
+          <t>john_crews_house</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>navy_office</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -25155,10 +25151,14 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H671" t="inlineStr"/>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
       <c r="I671" t="inlineStr"/>
     </row>
     <row r="672">
@@ -25169,12 +25169,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>navy_office</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>council_chamber_whitehall</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -25190,11 +25190,19 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H672" t="inlineStr"/>
-      <c r="I672" t="inlineStr"/>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Mr Butler</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>"Then by coach back again, and at White Hall at the Council Chamber"</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -25204,12 +25212,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>john_crews_house</t>
+          <t>council_chamber_whitehall</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>navy_office</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -25225,7 +25233,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -25243,12 +25251,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>navy_office</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>council_chamber_whitehall</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -25264,19 +25272,11 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="H674" t="inlineStr">
-        <is>
-          <t>Mr Butler</t>
-        </is>
-      </c>
-      <c r="I674" t="inlineStr">
-        <is>
-          <t>"Then by coach back again, and at White Hall at the Council Chamber"</t>
-        </is>
-      </c>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -25286,12 +25286,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>council_chamber_whitehall</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -25303,19 +25303,19 @@
         <v>3</v>
       </c>
       <c r="F675" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G675" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>Mr Butler</t>
-        </is>
-      </c>
-      <c r="I675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>"whom I took in his cutting house"</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -25325,12 +25325,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>navy_treasurer_office</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -25342,7 +25342,7 @@
         <v>3</v>
       </c>
       <c r="F676" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G676" t="inlineStr">
         <is>
@@ -25360,12 +25360,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>navy_treasurer_office</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>daniel_rawlinson_house</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -25385,11 +25385,7 @@
         </is>
       </c>
       <c r="H677" t="inlineStr"/>
-      <c r="I677" t="inlineStr">
-        <is>
-          <t>"whom I took in his cutting house"</t>
-        </is>
-      </c>
+      <c r="I677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -25399,12 +25395,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>daniel_rawlinson_house</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>navy_treasurer_office</t>
+          <t>sun_tavern_fish_street_hill</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -25434,12 +25430,12 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>navy_treasurer_office</t>
+          <t>sun_tavern_fish_street_hill</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>rawlinson_house</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -25455,11 +25451,15 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>coach</t>
         </is>
       </c>
       <c r="H679" t="inlineStr"/>
-      <c r="I679" t="inlineStr"/>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>"Then by coach home"</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -25469,12 +25469,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>rawlinson_house</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>sun_tavern_fish_street_hill</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -25494,7 +25494,11 @@
         </is>
       </c>
       <c r="H680" t="inlineStr"/>
-      <c r="I680" t="inlineStr"/>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>"to see Mrs. Jem and paid her maid L7"</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -25504,12 +25508,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>sun_tavern_fish_street_hill</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>robert_blackborne_house</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -25525,15 +25529,11 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H681" t="inlineStr"/>
-      <c r="I681" t="inlineStr">
-        <is>
-          <t>"Then by coach home"</t>
-        </is>
-      </c>
+      <c r="I681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -25543,12 +25543,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>robert_blackborne_house</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -25570,7 +25570,7 @@
       <c r="H682" t="inlineStr"/>
       <c r="I682" t="inlineStr">
         <is>
-          <t>"to see Mrs. Jem and paid her maid L7"</t>
+          <t>"Sir H. Wright's where my Lord dined"</t>
         </is>
       </c>
     </row>
@@ -25582,12 +25582,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>blackburne_house</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -25606,8 +25606,16 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H683" t="inlineStr"/>
-      <c r="I683" t="inlineStr"/>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>William Howe</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>"Hither W. Howe comes to me and so to Westminster ... He went with me to my office"</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -25617,12 +25625,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>blackburne_house</t>
+          <t>office_exchequer</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>wright_house</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -25642,11 +25650,7 @@
         </is>
       </c>
       <c r="H684" t="inlineStr"/>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>"Sir H. Wright's where my Lord dined"</t>
-        </is>
-      </c>
+      <c r="I684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -25656,12 +25660,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>wright_house</t>
+          <t>whitehall_palace</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -25680,16 +25684,8 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H685" t="inlineStr">
-        <is>
-          <t>William Howe</t>
-        </is>
-      </c>
-      <c r="I685" t="inlineStr">
-        <is>
-          <t>"Hither W. Howe comes to me and so to Westminster ... He went with me to my office"</t>
-        </is>
-      </c>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -25699,12 +25695,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>office_exchequer</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -25716,15 +25712,23 @@
         <v>3</v>
       </c>
       <c r="F686" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G686" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H686" t="inlineStr"/>
-      <c r="I686" t="inlineStr"/>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>"At night my wife and I went to my father's to supper"</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -25734,7 +25738,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>whitehall_palace</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -25751,14 +25755,18 @@
         <v>3</v>
       </c>
       <c r="F687" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G687" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr"/>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I687" t="inlineStr"/>
     </row>
     <row r="688">
@@ -25774,7 +25782,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>new_exchange</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -25786,7 +25794,7 @@
         <v>3</v>
       </c>
       <c r="F688" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G688" t="inlineStr">
         <is>
@@ -25800,7 +25808,7 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>"At night my wife and I went to my father's to supper"</t>
+          <t>"My wife and I to the Exchange, where we bought a great many things" - read as the New Exchange, the Strand shopping arcade. FLAG</t>
         </is>
       </c>
     </row>
@@ -25812,12 +25820,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>new_exchange</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>bedells_bookshop</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -25829,19 +25837,19 @@
         <v>3</v>
       </c>
       <c r="F689" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G689" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H689" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
-      <c r="I689" t="inlineStr"/>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>"where I left her and went into London"</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -25851,12 +25859,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>bedells_bookshop</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>new_exchange</t>
+          <t>wilkinsons_cookshop</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -25875,14 +25883,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H690" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
+      <c r="H690" t="inlineStr"/>
       <c r="I690" t="inlineStr">
         <is>
-          <t>"My wife and I to the Exchange, where we bought a great many things" - read as the New Exchange, the Strand shopping arcade. FLAG</t>
+          <t>"So came back"</t>
         </is>
       </c>
     </row>
@@ -25894,12 +25898,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>new_exchange</t>
+          <t>wilkinsons_cookshop</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>bedells_bookshop</t>
+          <t>white_horse_king_street</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -25919,11 +25923,7 @@
         </is>
       </c>
       <c r="H691" t="inlineStr"/>
-      <c r="I691" t="inlineStr">
-        <is>
-          <t>"where I left her and went into London"</t>
-        </is>
-      </c>
+      <c r="I691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -25933,12 +25933,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>bedells_bookshop</t>
+          <t>white_horse_king_street</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>wilkinsons_cookshop</t>
+          <t>robert_bowyer_house</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -25954,13 +25954,13 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="H692" t="inlineStr"/>
       <c r="I692" t="inlineStr">
         <is>
-          <t>"So came back"</t>
+          <t>"I got Mr. Buddle's horse to ride to Huntsmore to Mr. Bowyer's"; "Here I lay"</t>
         </is>
       </c>
     </row>
@@ -25972,12 +25972,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>wilkinsons_cookshop</t>
+          <t>robert_bowyer_house</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>white_horse_king_street</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -25989,15 +25989,19 @@
         <v>3</v>
       </c>
       <c r="F693" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="H693" t="inlineStr"/>
-      <c r="I693" t="inlineStr"/>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>"It rained hard and I got up early, and got to London by 8 o'clock at my Lord's lodgings"</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -26007,12 +26011,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>white_horse_king_street</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>bowyer_house</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -26024,19 +26028,15 @@
         <v>3</v>
       </c>
       <c r="F694" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H694" t="inlineStr"/>
-      <c r="I694" t="inlineStr">
-        <is>
-          <t>"I got Mr. Buddle's horse to ride to Huntsmore to Mr. Bowyer's"; "Here I lay"</t>
-        </is>
-      </c>
+      <c r="I694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -26046,12 +26046,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>bowyer_house</t>
+          <t>john_pepys_house</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -26067,13 +26067,13 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H695" t="inlineStr"/>
       <c r="I695" t="inlineStr">
         <is>
-          <t>"It rained hard and I got up early, and got to London by 8 o'clock at my Lord's lodgings"</t>
+          <t>"and so at my shoemaker's" - Wotton, cf. 18 Feb</t>
         </is>
       </c>
     </row>
@@ -26085,12 +26085,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>william_wotton_shop</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>roberts_whitehall</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -26110,7 +26110,11 @@
         </is>
       </c>
       <c r="H696" t="inlineStr"/>
-      <c r="I696" t="inlineStr"/>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>"At night to Whitehall"</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -26120,12 +26124,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>john_pepys_house</t>
+          <t>roberts_whitehall</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>william_wotton_shop</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -26145,11 +26149,7 @@
         </is>
       </c>
       <c r="H697" t="inlineStr"/>
-      <c r="I697" t="inlineStr">
-        <is>
-          <t>"and so at my shoemaker's" - Wotton, cf. 18 Feb</t>
-        </is>
-      </c>
+      <c r="I697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>william_wotton_shop</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>roberts_whitehall</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -26184,11 +26184,7 @@
         </is>
       </c>
       <c r="H698" t="inlineStr"/>
-      <c r="I698" t="inlineStr">
-        <is>
-          <t>"At night to Whitehall"</t>
-        </is>
-      </c>
+      <c r="I698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -26198,12 +26194,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>roberts_whitehall</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -26215,7 +26211,7 @@
         <v>3</v>
       </c>
       <c r="F699" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G699" t="inlineStr">
         <is>
@@ -26223,7 +26219,11 @@
         </is>
       </c>
       <c r="H699" t="inlineStr"/>
-      <c r="I699" t="inlineStr"/>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -26233,12 +26233,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>st_jamess_palace</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -26250,14 +26250,18 @@
         <v>3</v>
       </c>
       <c r="F700" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G700" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="H700" t="inlineStr"/>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>James Pierce</t>
+        </is>
+      </c>
       <c r="I700" t="inlineStr"/>
     </row>
     <row r="701">
@@ -26268,12 +26272,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>st_jamess_palace</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>marshes_whitehall</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -26292,10 +26296,14 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H701" t="inlineStr"/>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>James Pierce</t>
+        </is>
+      </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>"my Lord's lodgings" unqualified, taken as the Whitehall lodgings; 6 March distinguishes them from my Lord staying at Mr Crew's. FLAG</t>
+          <t>"he and I to Whitehall, where with Luellin we dined at Marsh's"</t>
         </is>
       </c>
     </row>
@@ -26307,12 +26315,12 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>marshes_whitehall</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>st_jamess_palace</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -26331,11 +26339,7 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H702" t="inlineStr">
-        <is>
-          <t>James Pierce</t>
-        </is>
-      </c>
+      <c r="H702" t="inlineStr"/>
       <c r="I702" t="inlineStr"/>
     </row>
     <row r="703">
@@ -26346,12 +26350,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>st_jamess_palace</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>marshes_whitehall</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -26370,16 +26374,8 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H703" t="inlineStr">
-        <is>
-          <t>James Pierce</t>
-        </is>
-      </c>
-      <c r="I703" t="inlineStr">
-        <is>
-          <t>"he and I to Whitehall, where with Luellin we dined at Marsh's"</t>
-        </is>
-      </c>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -26389,12 +26385,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>marshes_whitehall</t>
+          <t>admiralty</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>john_creed_chamber</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -26424,12 +26420,12 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>john_creed_chamber</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -26459,12 +26455,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>admiralty</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>creeds_chamber</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -26480,11 +26476,19 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H706" t="inlineStr"/>
-      <c r="I706" t="inlineStr"/>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Mr Beard</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>"I took him by coach to my Lord's, but he was not at home"</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -26494,12 +26498,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>creeds_chamber</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -26518,8 +26522,16 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H707" t="inlineStr"/>
-      <c r="I707" t="inlineStr"/>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Mr Beard</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>"afterwards I found him out at Sir H. Wright's"</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -26529,12 +26541,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>wright_house</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -26553,14 +26565,10 @@
           <t>coach</t>
         </is>
       </c>
-      <c r="H708" t="inlineStr">
-        <is>
-          <t>old Beard</t>
-        </is>
-      </c>
+      <c r="H708" t="inlineStr"/>
       <c r="I708" t="inlineStr">
         <is>
-          <t>"I took him by coach to my Lord's, but he was not at home"</t>
+          <t>"Thence by coach, it raining hard, to Mrs. Jem"</t>
         </is>
       </c>
     </row>
@@ -26572,12 +26580,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>wright_house</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -26596,16 +26604,8 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H709" t="inlineStr">
-        <is>
-          <t>old Beard</t>
-        </is>
-      </c>
-      <c r="I709" t="inlineStr">
-        <is>
-          <t>"afterwards I found him out at Sir H. Wright's"</t>
-        </is>
-      </c>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -26615,12 +26615,12 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>wright_house</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -26632,17 +26632,17 @@
         <v>3</v>
       </c>
       <c r="F710" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="H710" t="inlineStr"/>
       <c r="I710" t="inlineStr">
         <is>
-          <t>"Thence by coach, it raining hard, to Mrs. Jem"</t>
+          <t>"where I took leave of some of my friends"</t>
         </is>
       </c>
     </row>
@@ -26654,12 +26654,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>wills_alehouse</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>anne_michell_shop</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -26671,7 +26671,7 @@
         <v>3</v>
       </c>
       <c r="F711" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G711" t="inlineStr">
         <is>
@@ -26679,7 +26679,11 @@
         </is>
       </c>
       <c r="H711" t="inlineStr"/>
-      <c r="I711" t="inlineStr"/>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>"in the Hall paid and made even with Mrs. Michell"</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -26689,12 +26693,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>anne_michell_shop</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>axe_brewhouse</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -26716,7 +26720,7 @@
       <c r="H712" t="inlineStr"/>
       <c r="I712" t="inlineStr">
         <is>
-          <t>"where I took leave of some of my friends"</t>
+          <t>"at the Axe paid him this quarter to Ladyday next"</t>
         </is>
       </c>
     </row>
@@ -26728,12 +26732,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>wills_alehouse</t>
+          <t>axe_brewhouse</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>anne_michell_shop</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -26755,7 +26759,7 @@
       <c r="H713" t="inlineStr"/>
       <c r="I713" t="inlineStr">
         <is>
-          <t>"in the Hall paid and made even with Mrs. Michell"</t>
+          <t>"Dick Mathews comes to dine"</t>
         </is>
       </c>
     </row>
@@ -26767,12 +26771,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>anne_michell_shop</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>axe_brewhouse</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -26791,12 +26795,12 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H714" t="inlineStr"/>
-      <c r="I714" t="inlineStr">
-        <is>
-          <t>"at the Axe paid him this quarter to Ladyday next"</t>
-        </is>
-      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Richard Matthews</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -26806,12 +26810,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>axe_brewhouse</t>
+          <t>harpers_tavern</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>fish_street_london</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -26827,13 +26831,17 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H715" t="inlineStr"/>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>"Dick Mathews comes to dine"</t>
+          <t>"So into London by water"</t>
         </is>
       </c>
     </row>
@@ -26845,12 +26853,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>fish_street_london</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>sun_tavern_fish_street_hill</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -26871,10 +26879,14 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Richard Matthews</t>
-        </is>
-      </c>
-      <c r="I716" t="inlineStr"/>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>"went to the Sun Tavern and ate it"</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -26884,12 +26896,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>harpers_tavern</t>
+          <t>sun_tavern_fish_street_hill</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>fish_street</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -26905,17 +26917,13 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>boat</t>
-        </is>
-      </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>Elizabeth Pepys</t>
-        </is>
-      </c>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr"/>
       <c r="I717" t="inlineStr">
         <is>
-          <t>"So into London by water"</t>
+          <t>"From thence homewards ... I went to my Lord's"</t>
         </is>
       </c>
     </row>
@@ -26927,12 +26935,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>fish_street</t>
+          <t>sandwich_lodgings</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>sun_tavern_fish_street_hill</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -26948,17 +26956,17 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>coach</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Elizabeth Pepys</t>
+          <t>Jemima Montagu</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>"went to the Sun Tavern and ate it"</t>
+          <t>"So home with Mrs. Jem by coach"</t>
         </is>
       </c>
     </row>
@@ -26970,12 +26978,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>sun_tavern_fish_street_hill</t>
+          <t>scott_house</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -26997,7 +27005,7 @@
       <c r="H719" t="inlineStr"/>
       <c r="I719" t="inlineStr">
         <is>
-          <t>"From thence homewards ... I went to my Lord's"</t>
+          <t>"and then home to my own house"</t>
         </is>
       </c>
     </row>
@@ -27009,12 +27017,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>sandwich_lodgings</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>fox_tavern</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -27030,19 +27038,11 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>coach</t>
-        </is>
-      </c>
-      <c r="H720" t="inlineStr">
-        <is>
-          <t>Jemima Montagu</t>
-        </is>
-      </c>
-      <c r="I720" t="inlineStr">
-        <is>
-          <t>"So home with Mrs. Jem by coach"</t>
-        </is>
-      </c>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -27052,12 +27052,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>scott_house</t>
+          <t>fox_tavern</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -27077,11 +27077,7 @@
         </is>
       </c>
       <c r="H721" t="inlineStr"/>
-      <c r="I721" t="inlineStr">
-        <is>
-          <t>"and then home to my own house"</t>
-        </is>
-      </c>
+      <c r="I721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -27091,7 +27087,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>home_axe_yard</t>
+          <t>westminster_hall</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -27116,7 +27112,11 @@
         </is>
       </c>
       <c r="H722" t="inlineStr"/>
-      <c r="I722" t="inlineStr"/>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>"To the Fox again"</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>westminster_hall</t>
+          <t>home_axe_yard</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -27150,93 +27150,19 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr"/>
-      <c r="I723" t="inlineStr"/>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>100723</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>westminster_hall</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>fox_tavern</t>
-        </is>
-      </c>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>1659/60</t>
-        </is>
-      </c>
-      <c r="E724" t="n">
-        <v>3</v>
-      </c>
-      <c r="F724" t="n">
-        <v>15</v>
-      </c>
-      <c r="G724" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H724" t="inlineStr"/>
-      <c r="I724" t="inlineStr">
-        <is>
-          <t>"To the Fox again"</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>100724</t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>fox_tavern</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>home_axe_yard</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>1659/60</t>
-        </is>
-      </c>
-      <c r="E725" t="n">
-        <v>3</v>
-      </c>
-      <c r="F725" t="n">
-        <v>15</v>
-      </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>walk</t>
-        </is>
-      </c>
-      <c r="H725" t="inlineStr">
+      <c r="H723" t="inlineStr">
         <is>
           <t>Elizabeth Pepys</t>
         </is>
       </c>
-      <c r="I725" t="inlineStr">
+      <c r="I723" t="inlineStr">
         <is>
           <t>"Home with my wife"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I725"/>
+  <autoFilter ref="A1:I723"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edge-list.xlsx
+++ b/edge-list.xlsx
@@ -10,7 +10,7 @@
     <sheet name="edges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'edges'!$A$1:$I$790</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I723"/>
+  <dimension ref="A1:I790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -27161,8 +27161,2613 @@
         </is>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>100723</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>3</v>
+      </c>
+      <c r="F724" t="n">
+        <v>16</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>"Then to Mr. Sheply, to the Rhenish Tavern House"</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>100724</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>priors_rhenish_wine_house</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>3</v>
+      </c>
+      <c r="F725" t="n">
+        <v>16</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>100725</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>3</v>
+      </c>
+      <c r="F726" t="n">
+        <v>16</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>"with my wife to London, we dined at my father's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>100726</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>rolls_office_chancery</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>3</v>
+      </c>
+      <c r="F727" t="n">
+        <v>16</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>"In my way home I went to the Chapel in Chancery Lane to bespeak papers ... against my voyage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>100727</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>rolls_office_chancery</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>3</v>
+      </c>
+      <c r="F728" t="n">
+        <v>16</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>100728</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>3</v>
+      </c>
+      <c r="F729" t="n">
+        <v>16</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>100729</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>3</v>
+      </c>
+      <c r="F730" t="n">
+        <v>16</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>"so home again"</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>100730</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>3</v>
+      </c>
+      <c r="F731" t="n">
+        <v>16</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>"where I heard how the Parliament had this day dissolved themselves"</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>100731</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>3</v>
+      </c>
+      <c r="F732" t="n">
+        <v>16</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>100732</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>3</v>
+      </c>
+      <c r="F733" t="n">
+        <v>17</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>Eliezer</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>"went to my Lord's with my boy Eliezer to my Lord's lodging at Mr. Crew's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>100733</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>3</v>
+      </c>
+      <c r="F734" t="n">
+        <v>17</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>Henry Moore</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>100734</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>chequer_inn_holborn</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>3</v>
+      </c>
+      <c r="F735" t="n">
+        <v>17</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>Elizabeth Pepys; Henry Moore</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>"took my wife by coach to the Chequer in Holborn, where, after we had drank, &amp;c., she took coach and so farewell"</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>100735</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>chequer_inn_holborn</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>3</v>
+      </c>
+      <c r="F736" t="n">
+        <v>17</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>John Hawly</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>100736</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>3</v>
+      </c>
+      <c r="F737" t="n">
+        <v>17</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>"all things were put up into the dining-room and locked up, and my wife took the keys along with her"</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>100737</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>3</v>
+      </c>
+      <c r="F738" t="n">
+        <v>17</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>100738</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>3</v>
+      </c>
+      <c r="F739" t="n">
+        <v>17</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Laud Crisp</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>"went by coach taking Mr. Crips with me to my Lord"</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>100739</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>3</v>
+      </c>
+      <c r="F740" t="n">
+        <v>17</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>Laud Crisp</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>3</v>
+      </c>
+      <c r="F741" t="n">
+        <v>17</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>Laud Crisp</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>"I went home with him to his mother's house by me in Axe Yard"</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>100741</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>jervas_barber</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>3</v>
+      </c>
+      <c r="F742" t="n">
+        <v>18</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>100742</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>jervas_barber</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>3</v>
+      </c>
+      <c r="F743" t="n">
+        <v>18</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>"Then to my Lord's lodging where I found Captain Williamson"</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>100743</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>3</v>
+      </c>
+      <c r="F744" t="n">
+        <v>18</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>100744</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>3</v>
+      </c>
+      <c r="F745" t="n">
+        <v>18</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>"then to dinner with Mr. Shepley at my Lord's lodgings"</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>100745</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>robert_mossum_church</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>3</v>
+      </c>
+      <c r="F746" t="n">
+        <v>18</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>"a very gallant sermon upon 'Pray for the life of the King and the King's son'"</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>100746</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>robert_mossum_church</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>3</v>
+      </c>
+      <c r="F747" t="n">
+        <v>18</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>"but my Lord not being within I did not stay"</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>100747</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_11</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>3</v>
+      </c>
+      <c r="F748" t="n">
+        <v>18</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Mr Woodfine</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>100748</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>alehouse_unknown_11</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>blagrave_house</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>3</v>
+      </c>
+      <c r="F749" t="n">
+        <v>18</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>100749</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>blagrave_house</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>3</v>
+      </c>
+      <c r="F750" t="n">
+        <v>18</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>100750</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>3</v>
+      </c>
+      <c r="F751" t="n">
+        <v>19</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>"Early to my Lord, where infinity of business"</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>100751</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>3</v>
+      </c>
+      <c r="F752" t="n">
+        <v>19</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>100752</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>wilkinsons_cookshop</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>3</v>
+      </c>
+      <c r="F753" t="n">
+        <v>19</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>100753</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>wilkinsons_cookshop</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>3</v>
+      </c>
+      <c r="F754" t="n">
+        <v>19</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>"Thence with some sea officers to the Swan" - the officers are not named</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>100754</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>swan_inn</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>3</v>
+      </c>
+      <c r="F755" t="n">
+        <v>19</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>Crockford</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>"Going home the water was high, and so I got Crockford to carry me over it" - a named waterman, per README principle 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>100755</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>3</v>
+      </c>
+      <c r="F756" t="n">
+        <v>19</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>100756</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>roberts_whitehall</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>3</v>
+      </c>
+      <c r="F757" t="n">
+        <v>19</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>"then to Tony Robins's" - taken to be the same house as "Roberts at Whitehall", 13 Mar. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>100757</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>roberts_whitehall</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>3</v>
+      </c>
+      <c r="F758" t="n">
+        <v>19</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>100758</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>3</v>
+      </c>
+      <c r="F759" t="n">
+        <v>20</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>"went to my house to put things in a little order against my going"</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>100759</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>3</v>
+      </c>
+      <c r="F760" t="n">
+        <v>20</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>100760</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>3</v>
+      </c>
+      <c r="F761" t="n">
+        <v>20</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>Captain Isham</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>100761</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>3</v>
+      </c>
+      <c r="F762" t="n">
+        <v>20</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>Captain Isham; James Chetwind; Thomas Doling; Peter Llewellyn</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>100762</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>marshes_whitehall</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>bull_head_tavern</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>3</v>
+      </c>
+      <c r="F763" t="n">
+        <v>20</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>Captain Isham; James Chetwind; Thomas Doling; Peter Llewellyn</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>"I gave them my foy against my going to sea" - a farewell feast</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>100763</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>bull_head_tavern</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>3</v>
+      </c>
+      <c r="F764" t="n">
+        <v>20</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>the coach to London and the leave-taking of his parents are dated to the 21st, where Pepys corrects himself: "which by a mistake I have put down yesterday"</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>100764</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>3</v>
+      </c>
+      <c r="F765" t="n">
+        <v>20</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>"the water was so high that there was boats rowed in King Street and all our yard was drowned, that one could not go to my house"</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>100765</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>3</v>
+      </c>
+      <c r="F766" t="n">
+        <v>20</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>Edward Shipley; William Howe</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>"went with our swords to bring my Lord home from Sir H. Wright's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>100766</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>wright_house</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>3</v>
+      </c>
+      <c r="F767" t="n">
+        <v>20</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>Edward Montagu; Edward Shipley</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>100767</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>3</v>
+      </c>
+      <c r="F768" t="n">
+        <v>20</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>100768</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>3</v>
+      </c>
+      <c r="F769" t="n">
+        <v>21</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>"but the wind very high against us, and the weather bad we could not go to-day"</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>100769</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>thomas_widdrington_house</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>3</v>
+      </c>
+      <c r="F770" t="n">
+        <v>21</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>"with his desire that he might have the disposal of the writs of the Cinque Ports"</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>100770</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>thomas_widdrington_house</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>tavern_unknown_1</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>3</v>
+      </c>
+      <c r="F771" t="n">
+        <v>21</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>Judge Advocate Fowler; Mr Burr</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>100771</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>tavern_unknown_1</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>3</v>
+      </c>
+      <c r="F772" t="n">
+        <v>21</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>"to Mr. Crew's again"</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>100772</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>3</v>
+      </c>
+      <c r="F773" t="n">
+        <v>21</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>"about my business to take leave of my father and mother, which by a mistake I have put down yesterday" - dated here on Pepys's own correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>100773</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>john_pepys_house</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>3</v>
+      </c>
+      <c r="F774" t="n">
+        <v>21</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>"Thence to Westminster to Crisp's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>100774</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>crisp_house</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>3</v>
+      </c>
+      <c r="F775" t="n">
+        <v>22</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>"Up very early and set things in order at my house"; the leave-takings of Mrs Crisp and Mrs Hunt are in Axe Yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>100775</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>home_axe_yard</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>john_hunt_house</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>3</v>
+      </c>
+      <c r="F776" t="n">
+        <v>22</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>"took leave of Mrs. Crispe and her daughter (who was in bed) and of Mrs. Hunt" - all three houses stand in Axe Yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>100776</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>john_hunt_house</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>3</v>
+      </c>
+      <c r="F777" t="n">
+        <v>22</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>"Then to my Lord's lodging at the gate"</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>100777</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>3</v>
+      </c>
+      <c r="F778" t="n">
+        <v>22</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>John Hawly</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>"I gave him the key of my house to keep, and he went with me to Mr. Crew's"</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>100778</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>john_crews_house</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>popes_head_tavern_chancery_lane</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>3</v>
+      </c>
+      <c r="F779" t="n">
+        <v>22</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>William Wotton; Mr Brigden</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>100779</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>popes_head_tavern_chancery_lane</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>3</v>
+      </c>
+      <c r="F780" t="n">
+        <v>22</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>took leave of Kate Sterpin, Mr George Montagu and Mr Blackburne, and received his warrant as Secretary to the two Generals of the Fleet; no place is given for any of the three. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>100780</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>westminster_hall</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>george_montagu_house</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>3</v>
+      </c>
+      <c r="F781" t="n">
+        <v>22</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>"took leave of Kate Sterpin ... and after that of Mr. George Mountagu"; no place is given for Kate Sterpin. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>100781</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>george_montagu_house</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>3</v>
+      </c>
+      <c r="F782" t="n">
+        <v>22</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>"received my warrant of Mr. Blackburne, to be Secretary to the two Generals of the Fleet" - Blackburne was Secretary to the Admiralty</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>100782</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>admiralty</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>clerks_room_whitehall</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>3</v>
+      </c>
+      <c r="F783" t="n">
+        <v>22</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>"Then to take my leave of the Clerks of the Council"</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>100783</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>clerks_room_whitehall</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>mounts_chamber</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>3</v>
+      </c>
+      <c r="F784" t="n">
+        <v>22</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Thomas Doling; Peter Llewellyn</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>100784</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>mounts_chamber</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>3</v>
+      </c>
+      <c r="F785" t="n">
+        <v>22</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>"So to my Lord ... where I lay all night with Mr. Andrews" - unqualified, so the Whitehall lodgings per section 6 ruling 1, though Mr Andrews is elsewhere met at Mr Crew's. FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>100785</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>william_montagu_chamber</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>3</v>
+      </c>
+      <c r="F786" t="n">
+        <v>23</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>"carried my Lord's will in a black box to Mr. William Montagu"</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>100786</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>william_montagu_chamber</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>jervas_barber</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>3</v>
+      </c>
+      <c r="F787" t="n">
+        <v>23</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr"/>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>"Then to the barber's and put on my cravat there"</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>100787</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>jervas_barber</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>3</v>
+      </c>
+      <c r="F788" t="n">
+        <v>23</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr"/>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>"So to my Lord again, who was almost ready to be gone". Shelston brought his wife to the Ship tavern hard by for Pepys to see, "but I could not go" - no edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>100788</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>sandwich_lodgings</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>tower_of_london</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>3</v>
+      </c>
+      <c r="F789" t="n">
+        <v>23</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>Edward Montagu; Captain Isham; Mr Thomas; John Crew; William Howe</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>"my Lord in Sir H. Wright's coach ... and I in a Hackney to the Tower, where the barges staid for us" - two vehicles, one party</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>100789</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>tower_of_london</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>swiftsure</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>1659/60</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>3</v>
+      </c>
+      <c r="F790" t="n">
+        <v>23</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>boat</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>William Howe</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>"my Lord and the Captain in one, and W. Howe and I, &amp;c., in the other, to the Long Reach, where the Swiftsure lay at anchor" - Long Reach is where she lay, not a node (section 7 ruling 2)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I723"/>
+  <autoFilter ref="A1:I790"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>